--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\Fund-Site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB08219-F58C-4F1D-A888-806F4DEB7D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FADF95-CF39-41BE-8381-E20F354129CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,53 @@
       </rPr>
       <t>: iron condors, VOO, 30 days +- 5 days, deltas ~20 +-2, add puts and calls $15 each way, atleast 1/3 price to risk on entry</t>
     </r>
+  </si>
+  <si>
+    <t>Crows</t>
+  </si>
+  <si>
+    <t>Demons</t>
+  </si>
+  <si>
+    <t>Cats</t>
+  </si>
+  <si>
+    <t>Giants</t>
+  </si>
+  <si>
+    <t>Saints</t>
+  </si>
+  <si>
+    <t>Comesana</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: backing the favourite @ 20% above starting, first to 4 games in first set</t>
+    </r>
+  </si>
+  <si>
+    <t>Betfair take 6% in fees</t>
+  </si>
+  <si>
+    <t>Griekspoor</t>
   </si>
 </sst>
 </file>
@@ -257,7 +304,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +356,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +497,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -461,15 +514,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -509,9 +556,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -522,12 +566,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -602,13 +640,52 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -951,7 +1028,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K12"/>
+  <dimension ref="B2:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" customWidth="1"/>
@@ -967,43 +1044,43 @@
       <c r="C2"/>
     </row>
     <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>55.55</v>
       </c>
-      <c r="K3" s="10"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1011,35 +1088,35 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="23">
         <v>1.34</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="51">
         <f>1/D5</f>
         <v>0.74626865671641784</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="21">
         <f>E5-0.2</f>
         <v>0.54626865671641789</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="22">
         <f>1/F5</f>
         <v>1.8306010928961749</v>
       </c>
-      <c r="H5" s="26">
-        <v>0</v>
-      </c>
-      <c r="I5" s="26" t="s">
+      <c r="H5" s="23">
+        <v>0</v>
+      </c>
+      <c r="I5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="24">
         <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="25">
         <f>J5*J$3</f>
         <v>0</v>
       </c>
@@ -1048,35 +1125,35 @@
       <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="64">
         <v>1.77</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="52">
         <f>1/D6</f>
         <v>0.56497175141242939</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <f>E6-0.2</f>
         <v>0.36497175141242938</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="65">
         <f>1/F6</f>
         <v>2.7399380804953561</v>
       </c>
-      <c r="H6" s="28">
-        <v>0</v>
-      </c>
-      <c r="I6" s="28" t="s">
+      <c r="H6" s="64">
+        <v>0</v>
+      </c>
+      <c r="I6" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="26">
         <f t="shared" ref="J6:J12" si="0">IF(H6=0,0,IF(I6="WON",(G6-1)*0.95,-1))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="27">
         <f t="shared" ref="K6:K12" si="1">J6*J$3</f>
         <v>0</v>
       </c>
@@ -1085,34 +1162,34 @@
       <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="64">
         <v>1.91</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="52">
         <f t="shared" ref="E7:E12" si="2">1/D7</f>
         <v>0.52356020942408377</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <f t="shared" ref="F7:F12" si="3">E7-0.2</f>
         <v>0.32356020942408376</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="65">
         <v>3.1</v>
       </c>
-      <c r="H7" s="28">
-        <v>0</v>
-      </c>
-      <c r="I7" s="28" t="s">
+      <c r="H7" s="64">
+        <v>0</v>
+      </c>
+      <c r="I7" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1121,35 +1198,35 @@
       <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="64">
         <v>1.44</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="52">
         <f t="shared" si="2"/>
         <v>0.69444444444444442</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <f t="shared" si="3"/>
         <v>0.49444444444444441</v>
       </c>
-      <c r="G8" s="27">
-        <f t="shared" ref="G8:G12" si="4">1/F8</f>
+      <c r="G8" s="65">
+        <f t="shared" ref="G8:G11" si="4">1/F8</f>
         <v>2.0224719101123596</v>
       </c>
-      <c r="H8" s="28">
-        <v>0</v>
-      </c>
-      <c r="I8" s="28" t="s">
+      <c r="H8" s="64">
+        <v>0</v>
+      </c>
+      <c r="I8" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1158,33 +1235,35 @@
       <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="64">
+        <v>1.19</v>
+      </c>
+      <c r="E9" s="52">
         <f t="shared" si="2"/>
-        <v>0.82644628099173556</v>
-      </c>
-      <c r="F9" s="7">
+        <v>0.84033613445378152</v>
+      </c>
+      <c r="F9" s="6">
         <f t="shared" si="3"/>
-        <v>0.62644628099173549</v>
-      </c>
-      <c r="G9" s="27">
+        <v>0.64033613445378146</v>
+      </c>
+      <c r="G9" s="65">
         <f t="shared" si="4"/>
-        <v>1.5963060686015833</v>
-      </c>
-      <c r="H9" s="28">
-        <v>0</v>
-      </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="31">
+        <v>1.5616797900262469</v>
+      </c>
+      <c r="H9" s="64">
+        <v>0</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1193,68 +1272,72 @@
       <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5">
-        <v>1.37</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="64">
+        <v>1.38</v>
+      </c>
+      <c r="E10" s="52">
         <f t="shared" si="2"/>
-        <v>0.72992700729927007</v>
-      </c>
-      <c r="F10" s="7">
+        <v>0.7246376811594204</v>
+      </c>
+      <c r="F10" s="6">
         <f t="shared" si="3"/>
-        <v>0.52992700729927011</v>
-      </c>
-      <c r="G10" s="27">
+        <v>0.52463768115942044</v>
+      </c>
+      <c r="G10" s="65">
         <f t="shared" si="4"/>
-        <v>1.887052341597796</v>
-      </c>
-      <c r="H10" s="28">
-        <v>0</v>
-      </c>
-      <c r="I10" s="28"/>
-      <c r="J10" s="31">
+        <v>1.9060773480662978</v>
+      </c>
+      <c r="H10" s="64">
+        <v>1</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="32">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="64">
         <v>1.02</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="52">
         <f t="shared" si="2"/>
         <v>0.98039215686274506</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <f t="shared" si="3"/>
         <v>0.78039215686274499</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="65">
         <f t="shared" si="4"/>
         <v>1.2814070351758795</v>
       </c>
-      <c r="H11" s="28">
-        <v>0</v>
-      </c>
-      <c r="I11" s="28"/>
-      <c r="J11" s="31">
+      <c r="H11" s="64">
+        <v>0</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1263,34 +1346,314 @@
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="13">
-        <v>1.64</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="D12" s="9">
+        <v>1.74</v>
+      </c>
+      <c r="E12" s="53">
         <f t="shared" si="2"/>
-        <v>0.6097560975609756</v>
-      </c>
-      <c r="F12" s="12">
+        <v>0.57471264367816088</v>
+      </c>
+      <c r="F12" s="10">
         <f t="shared" si="3"/>
-        <v>0.40975609756097559</v>
-      </c>
-      <c r="G12" s="14">
-        <f t="shared" si="4"/>
-        <v>2.4404761904761907</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="34">
+        <v>0.37471264367816087</v>
+      </c>
+      <c r="G12" s="12">
+        <v>2.68</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" s="28">
+        <f>IF(H12=0,0,IF(I12="WON",(G12-1)*0.94,-1))</f>
+        <v>1.5792000000000002</v>
+      </c>
+      <c r="K12" s="29">
         <f t="shared" si="1"/>
+        <v>87.724560000000011</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="54">
+        <v>9</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="52" t="e">
+        <f t="shared" ref="E13:E21" si="5">1/D13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F13" s="6" t="e">
+        <f t="shared" ref="F13:F21" si="6">E13-0.2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="59" t="e">
+        <f t="shared" ref="G13:G21" si="7">1/F13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="26">
+        <f>IF(H13=0,0,IF(I13="WON",(G13-1)*0.95,-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="27">
+        <f t="shared" ref="K13:K21" si="8">J13*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="54">
+        <v>10</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F14" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="26">
+        <f t="shared" ref="J13:J21" si="9">IF(H14=0,0,IF(I14="WON",(G14-1)*0.95,-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="54">
+        <v>11</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F15" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="54">
+        <v>12</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="54">
+        <v>13</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F17" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="54">
+        <v>14</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F18" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="54">
+        <v>15</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F19" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="54">
+        <v>16</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="52" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F20" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G20" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="55">
+        <v>17</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="10" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="60" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="27">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1302,93 +1665,165 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:K5"/>
+  <dimension ref="B2:L7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="I3" s="9" t="s">
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>55.55</v>
       </c>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="23" t="e">
+      <c r="C5" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="31">
+        <v>1.78</v>
+      </c>
+      <c r="E5" s="20">
         <f>1/D5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="24" t="e">
+        <v>0.5617977528089888</v>
+      </c>
+      <c r="F5" s="21">
         <f>E5-0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="25" t="e">
+        <v>0.36179775280898879</v>
+      </c>
+      <c r="G5" s="22">
         <f>1/F5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H5" s="35">
+        <v>2.7639751552795029</v>
+      </c>
+      <c r="H5" s="30">
         <v>1</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="17" t="e">
-        <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="30" t="e">
-        <f>J5*J$3</f>
-        <v>#DIV/0!</v>
+      <c r="J5" s="15">
+        <f>IF(H5=0,0,IF(I5="WON",(G5-1),-1))</f>
+        <v>1.7639751552795029</v>
+      </c>
+      <c r="K5" s="25">
+        <f>J5*J$3*0.94-0.21</f>
+        <v>91.8994906832298</v>
+      </c>
+      <c r="L5" s="63"/>
+    </row>
+    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="31">
+        <v>1.56</v>
+      </c>
+      <c r="E6" s="20">
+        <f>1/D6</f>
+        <v>0.64102564102564097</v>
+      </c>
+      <c r="F6" s="21">
+        <f>E6-0.2</f>
+        <v>0.44102564102564096</v>
+      </c>
+      <c r="G6" s="22">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="H6" s="30">
+        <v>1</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="15">
+        <f>IF(H6=0,0,IF(I6="WON",(G6-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K6" s="25">
+        <f>J6*J$3</f>
+        <v>-55.55</v>
+      </c>
+      <c r="L6" s="63"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="20" t="e">
+        <f>1/D7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F7" s="21" t="e">
+        <f>E7-0.2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="22" t="e">
+        <f t="shared" ref="G6:G7" si="0">1/F7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H7" s="30"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="15">
+        <f>IF(H7=0,0,IF(I7="WON",(G7-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
+        <f>J7*J$3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1413,43 +1848,43 @@
     <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>55.55</v>
       </c>
-      <c r="K3" s="10"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1457,33 +1892,33 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="23" t="e">
+      <c r="D5" s="31"/>
+      <c r="E5" s="20" t="e">
         <f>1/D5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F5" s="24" t="e">
+      <c r="F5" s="21" t="e">
         <f>E5-0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G5" s="25" t="e">
+      <c r="G5" s="22" t="e">
         <f>1/F5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="30">
         <v>1</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="17" t="e">
+      <c r="J5" s="15" t="e">
         <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K5" s="30" t="e">
+      <c r="K5" s="25" t="e">
         <f>J5*J$3</f>
         <v>#DIV/0!</v>
       </c>
@@ -1507,43 +1942,43 @@
     <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>55.55</v>
       </c>
-      <c r="K3" s="10"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1551,33 +1986,33 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="23" t="e">
+      <c r="D5" s="31"/>
+      <c r="E5" s="20" t="e">
         <f>1/D5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F5" s="24" t="e">
+      <c r="F5" s="21" t="e">
         <f>E5-0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G5" s="25" t="e">
+      <c r="G5" s="22" t="e">
         <f>1/F5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="30">
         <v>1</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="17" t="e">
+      <c r="J5" s="15" t="e">
         <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K5" s="30" t="e">
+      <c r="K5" s="25" t="e">
         <f>J5*J$3</f>
         <v>#DIV/0!</v>
       </c>
@@ -1601,43 +2036,43 @@
     <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>55.55</v>
       </c>
-      <c r="K3" s="10"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1645,33 +2080,33 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="23" t="e">
+      <c r="D5" s="31"/>
+      <c r="E5" s="20" t="e">
         <f>1/D5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F5" s="24" t="e">
+      <c r="F5" s="21" t="e">
         <f>E5-0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G5" s="25" t="e">
+      <c r="G5" s="22" t="e">
         <f>1/F5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="30">
         <v>1</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="17" t="e">
+      <c r="J5" s="15" t="e">
         <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K5" s="30" t="e">
+      <c r="K5" s="25" t="e">
         <f>J5*J$3</f>
         <v>#DIV/0!</v>
       </c>
@@ -1683,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821F4CAB-11EC-4DB3-9BD6-AF06D08A4FD3}">
-  <dimension ref="B2:M9"/>
+  <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="13" width="10.6640625" customWidth="1"/>
@@ -1698,42 +2133,42 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1741,174 +2176,106 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="35">
         <v>555</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="35">
         <v>570</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="35">
         <v>630</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="35">
         <v>645</v>
       </c>
-      <c r="G5" s="43">
-        <v>3</v>
-      </c>
-      <c r="H5" s="44">
-        <v>600</v>
-      </c>
-      <c r="I5" s="43">
+      <c r="G5" s="38">
+        <v>5</v>
+      </c>
+      <c r="H5" s="39">
+        <v>562</v>
+      </c>
+      <c r="I5" s="38">
         <f>IF(AND(H5&lt;=E5,H5&gt;=D5),0,IF(H5&lt;D5,MAX(H5-D5,C5-D5),MAX(E5-H5,E5-F5)))</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="53">
-        <v>15</v>
-      </c>
-      <c r="K5" s="49">
+        <v>-8</v>
+      </c>
+      <c r="J5" s="49">
+        <v>4</v>
+      </c>
+      <c r="K5" s="44">
         <f>(G5+I5)*100-J5</f>
-        <v>285</v>
+        <v>-304</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="41">
+        <v>1</v>
+      </c>
+      <c r="C6" s="36">
         <v>555</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="36">
         <v>570</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="36">
         <v>630</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="36">
         <v>645</v>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="40">
+        <v>5</v>
+      </c>
+      <c r="H6" s="41">
+        <v>615</v>
+      </c>
+      <c r="I6" s="40">
+        <f t="shared" ref="I6:I7" si="0">IF(AND(H6&lt;=E6,H6&gt;=D6),0,IF(H6&lt;D6,MAX(H6-D6,C6-D6),MAX(E6-H6,E6-F6)))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="48">
         <v>4</v>
       </c>
-      <c r="H6" s="46">
-        <v>633.23</v>
-      </c>
-      <c r="I6" s="45">
-        <f t="shared" ref="I6:I9" si="0">IF(AND(H6&lt;=E6,H6&gt;=D6),0,IF(H6&lt;D6,MAX(H6-D6,C6-D6),MAX(E6-H6,E6-F6)))</f>
-        <v>-3.2300000000000182</v>
-      </c>
-      <c r="J6" s="54">
-        <v>15</v>
-      </c>
-      <c r="K6" s="50">
-        <f t="shared" ref="K6:K9" si="1">(G6+I6)*100-J6</f>
-        <v>61.999999999998181</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
-        <v>3</v>
-      </c>
-      <c r="C7" s="41">
+      <c r="K6" s="45">
+        <f t="shared" ref="K6:K7" si="1">(G6+I6)*100-J6</f>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="37">
         <v>555</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="37">
         <v>570</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="37">
         <v>630</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="37">
         <v>645</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="42">
         <v>5</v>
       </c>
-      <c r="H7" s="46">
-        <v>720</v>
-      </c>
-      <c r="I7" s="45">
+      <c r="H7" s="43">
+        <v>580</v>
+      </c>
+      <c r="I7" s="42">
         <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-      <c r="J7" s="54">
-        <v>15</v>
-      </c>
-      <c r="K7" s="50">
+        <v>0</v>
+      </c>
+      <c r="J7" s="50">
+        <v>4</v>
+      </c>
+      <c r="K7" s="46">
         <f t="shared" si="1"/>
-        <v>-1015</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-      <c r="C8" s="41">
-        <v>555</v>
-      </c>
-      <c r="D8" s="41">
-        <v>570</v>
-      </c>
-      <c r="E8" s="41">
-        <v>630</v>
-      </c>
-      <c r="F8" s="41">
-        <v>645</v>
-      </c>
-      <c r="G8" s="45">
-        <v>6</v>
-      </c>
-      <c r="H8" s="46">
-        <v>500</v>
-      </c>
-      <c r="I8" s="45">
-        <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-      <c r="J8" s="54">
-        <v>15</v>
-      </c>
-      <c r="K8" s="50">
-        <f t="shared" si="1"/>
-        <v>-915</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="4">
-        <v>5</v>
-      </c>
-      <c r="C9" s="42">
-        <v>555</v>
-      </c>
-      <c r="D9" s="42">
-        <v>570</v>
-      </c>
-      <c r="E9" s="42">
-        <v>630</v>
-      </c>
-      <c r="F9" s="42">
-        <v>645</v>
-      </c>
-      <c r="G9" s="47">
-        <v>7</v>
-      </c>
-      <c r="H9" s="48">
-        <v>568.6</v>
-      </c>
-      <c r="I9" s="47">
-        <f t="shared" si="0"/>
-        <v>-1.3999999999999773</v>
-      </c>
-      <c r="J9" s="55">
-        <v>15</v>
-      </c>
-      <c r="K9" s="51">
-        <f t="shared" si="1"/>
-        <v>545.00000000000227</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K5:K200">
+  <conditionalFormatting sqref="K5:K114">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\Fund-Site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FADF95-CF39-41BE-8381-E20F354129CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C772EBF9-E712-48B2-ACA6-80F0B7DB6579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="5" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -497,7 +497,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -604,49 +604,19 @@
     <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1088,13 +1058,13 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="46" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="23">
         <v>1.34</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="41">
         <f>1/D5</f>
         <v>0.74626865671641784</v>
       </c>
@@ -1125,13 +1095,13 @@
       <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="54">
         <v>1.77</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="42">
         <f>1/D6</f>
         <v>0.56497175141242939</v>
       </c>
@@ -1139,18 +1109,18 @@
         <f>E6-0.2</f>
         <v>0.36497175141242938</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="55">
         <f>1/F6</f>
         <v>2.7399380804953561</v>
       </c>
-      <c r="H6" s="64">
-        <v>0</v>
-      </c>
-      <c r="I6" s="64" t="s">
+      <c r="H6" s="54">
+        <v>0</v>
+      </c>
+      <c r="I6" s="54" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="26">
-        <f t="shared" ref="J6:J12" si="0">IF(H6=0,0,IF(I6="WON",(G6-1)*0.95,-1))</f>
+        <f t="shared" ref="J6:J11" si="0">IF(H6=0,0,IF(I6="WON",(G6-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K6" s="27">
@@ -1162,13 +1132,13 @@
       <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="64">
+      <c r="D7" s="54">
         <v>1.91</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="42">
         <f t="shared" ref="E7:E12" si="2">1/D7</f>
         <v>0.52356020942408377</v>
       </c>
@@ -1176,13 +1146,13 @@
         <f t="shared" ref="F7:F12" si="3">E7-0.2</f>
         <v>0.32356020942408376</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="55">
         <v>3.1</v>
       </c>
-      <c r="H7" s="64">
-        <v>0</v>
-      </c>
-      <c r="I7" s="64" t="s">
+      <c r="H7" s="54">
+        <v>0</v>
+      </c>
+      <c r="I7" s="54" t="s">
         <v>7</v>
       </c>
       <c r="J7" s="26">
@@ -1198,13 +1168,13 @@
       <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D8" s="54">
         <v>1.44</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="42">
         <f t="shared" si="2"/>
         <v>0.69444444444444442</v>
       </c>
@@ -1212,14 +1182,14 @@
         <f t="shared" si="3"/>
         <v>0.49444444444444441</v>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="55">
         <f t="shared" ref="G8:G11" si="4">1/F8</f>
         <v>2.0224719101123596</v>
       </c>
-      <c r="H8" s="64">
-        <v>0</v>
-      </c>
-      <c r="I8" s="64" t="s">
+      <c r="H8" s="54">
+        <v>0</v>
+      </c>
+      <c r="I8" s="54" t="s">
         <v>7</v>
       </c>
       <c r="J8" s="26">
@@ -1235,13 +1205,13 @@
       <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="54">
         <v>1.19</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="42">
         <f t="shared" si="2"/>
         <v>0.84033613445378152</v>
       </c>
@@ -1249,14 +1219,14 @@
         <f t="shared" si="3"/>
         <v>0.64033613445378146</v>
       </c>
-      <c r="G9" s="65">
+      <c r="G9" s="55">
         <f t="shared" si="4"/>
         <v>1.5616797900262469</v>
       </c>
-      <c r="H9" s="64">
-        <v>0</v>
-      </c>
-      <c r="I9" s="64" t="s">
+      <c r="H9" s="54">
+        <v>0</v>
+      </c>
+      <c r="I9" s="54" t="s">
         <v>7</v>
       </c>
       <c r="J9" s="26">
@@ -1272,13 +1242,13 @@
       <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="54">
         <v>1.38</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="42">
         <f t="shared" si="2"/>
         <v>0.7246376811594204</v>
       </c>
@@ -1286,14 +1256,14 @@
         <f t="shared" si="3"/>
         <v>0.52463768115942044</v>
       </c>
-      <c r="G10" s="65">
+      <c r="G10" s="55">
         <f t="shared" si="4"/>
         <v>1.9060773480662978</v>
       </c>
-      <c r="H10" s="64">
+      <c r="H10" s="54">
         <v>1</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="54" t="s">
         <v>11</v>
       </c>
       <c r="J10" s="26">
@@ -1309,13 +1279,13 @@
       <c r="B11" s="3">
         <v>7</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="54">
         <v>1.02</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="42">
         <f t="shared" si="2"/>
         <v>0.98039215686274506</v>
       </c>
@@ -1323,14 +1293,14 @@
         <f t="shared" si="3"/>
         <v>0.78039215686274499</v>
       </c>
-      <c r="G11" s="65">
+      <c r="G11" s="55">
         <f t="shared" si="4"/>
         <v>1.2814070351758795</v>
       </c>
-      <c r="H11" s="64">
-        <v>0</v>
-      </c>
-      <c r="I11" s="64" t="s">
+      <c r="H11" s="54">
+        <v>0</v>
+      </c>
+      <c r="I11" s="54" t="s">
         <v>7</v>
       </c>
       <c r="J11" s="26">
@@ -1346,13 +1316,13 @@
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="48" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="9">
         <v>1.74</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="43">
         <f t="shared" si="2"/>
         <v>0.57471264367816088</v>
       </c>
@@ -1379,14 +1349,14 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="54">
+      <c r="B13" s="44">
         <v>9</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="44" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="52" t="e">
+      <c r="E13" s="42" t="e">
         <f t="shared" ref="E13:E21" si="5">1/D13</f>
         <v>#DIV/0!</v>
       </c>
@@ -1394,12 +1364,12 @@
         <f t="shared" ref="F13:F21" si="6">E13-0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G13" s="59" t="e">
+      <c r="G13" s="49" t="e">
         <f t="shared" ref="G13:G21" si="7">1/F13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
       <c r="J13" s="26">
         <f>IF(H13=0,0,IF(I13="WON",(G13-1)*0.95,-1))</f>
         <v>0</v>
@@ -1410,14 +1380,14 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="54">
+      <c r="B14" s="44">
         <v>10</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="44" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="5"/>
-      <c r="E14" s="52" t="e">
+      <c r="E14" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1425,14 +1395,14 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G14" s="59" t="e">
+      <c r="G14" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
       <c r="J14" s="26">
-        <f t="shared" ref="J13:J21" si="9">IF(H14=0,0,IF(I14="WON",(G14-1)*0.95,-1))</f>
+        <f t="shared" ref="J14:J21" si="9">IF(H14=0,0,IF(I14="WON",(G14-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K14" s="27">
@@ -1441,14 +1411,14 @@
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="54">
+      <c r="B15" s="44">
         <v>11</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="44" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="52" t="e">
+      <c r="E15" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1456,12 +1426,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="59" t="e">
+      <c r="G15" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
       <c r="J15" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1472,14 +1442,14 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="54">
+      <c r="B16" s="44">
         <v>12</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="44" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="52" t="e">
+      <c r="E16" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1487,12 +1457,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="59" t="e">
+      <c r="G16" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
       <c r="J16" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1503,14 +1473,14 @@
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="54">
+      <c r="B17" s="44">
         <v>13</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="44" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="52" t="e">
+      <c r="E17" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1518,12 +1488,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="59" t="e">
+      <c r="G17" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
       <c r="J17" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1534,14 +1504,14 @@
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="54">
+      <c r="B18" s="44">
         <v>14</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="44" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="52" t="e">
+      <c r="E18" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1549,12 +1519,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="59" t="e">
+      <c r="G18" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
       <c r="J18" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1565,14 +1535,14 @@
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="54">
+      <c r="B19" s="44">
         <v>15</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="44" t="s">
         <v>36</v>
       </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="52" t="e">
+      <c r="E19" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1580,12 +1550,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="59" t="e">
+      <c r="G19" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
       <c r="J19" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1596,14 +1566,14 @@
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="54">
+      <c r="B20" s="44">
         <v>16</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="44" t="s">
         <v>37</v>
       </c>
       <c r="D20" s="5"/>
-      <c r="E20" s="52" t="e">
+      <c r="E20" s="42" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1611,12 +1581,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="59" t="e">
+      <c r="G20" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
       <c r="J20" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1627,14 +1597,14 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="55">
+      <c r="B21" s="45">
         <v>17</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="45" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="11"/>
-      <c r="E21" s="53" t="e">
+      <c r="E21" s="43" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -1642,12 +1612,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="60" t="e">
+      <c r="G21" s="50" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
       <c r="J21" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1758,7 +1728,7 @@
         <f>J5*J$3*0.94-0.21</f>
         <v>91.8994906832298</v>
       </c>
-      <c r="L5" s="63"/>
+      <c r="L5" s="53"/>
     </row>
     <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
@@ -1795,7 +1765,7 @@
         <f>J6*J$3</f>
         <v>-55.55</v>
       </c>
-      <c r="L6" s="63"/>
+      <c r="L6" s="53"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -1812,7 +1782,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G7" s="22" t="e">
-        <f t="shared" ref="G6:G7" si="0">1/F7</f>
+        <f t="shared" ref="G7" si="0">1/F7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H7" s="30"/>
@@ -2118,7 +2088,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821F4CAB-11EC-4DB3-9BD6-AF06D08A4FD3}">
-  <dimension ref="B2:M7"/>
+  <dimension ref="B2:M15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="13" width="10.6640625" customWidth="1"/>
@@ -2137,8 +2107,8 @@
         <v>30</v>
       </c>
       <c r="K3" s="7"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
     </row>
     <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="13" t="s">
@@ -2172,7 +2142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2188,94 +2158,366 @@
       <c r="F5" s="35">
         <v>645</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H5" s="37">
+        <v>571</v>
+      </c>
+      <c r="I5" s="36">
+        <f>IF(AND(H5&lt;=E5,H5&gt;=D5),0,IF(H5&lt;D5,MAX(H5-D5,C5-D5),MAX(E5-H5,E5-F5)))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K5" s="38">
+        <f>(G5+I5)*100-J5</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="35">
+        <v>555</v>
+      </c>
+      <c r="D6" s="35">
+        <v>570</v>
+      </c>
+      <c r="E6" s="35">
+        <v>630</v>
+      </c>
+      <c r="F6" s="35">
+        <v>645</v>
+      </c>
+      <c r="G6" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H6" s="37">
+        <v>572</v>
+      </c>
+      <c r="I6" s="36">
+        <f>IF(AND(H6&lt;=E6,H6&gt;=D6),0,IF(H6&lt;D6,MAX(H6-D6,C6-D6),MAX(E6-H6,E6-F6)))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K6" s="38">
+        <f>(G6+I6)*100-J6</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="35">
+        <v>555</v>
+      </c>
+      <c r="D7" s="35">
+        <v>570</v>
+      </c>
+      <c r="E7" s="35">
+        <v>630</v>
+      </c>
+      <c r="F7" s="35">
+        <v>645</v>
+      </c>
+      <c r="G7" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H7" s="37">
+        <v>573</v>
+      </c>
+      <c r="I7" s="36">
+        <f>IF(AND(H7&lt;=E7,H7&gt;=D7),0,IF(H7&lt;D7,MAX(H7-D7,C7-D7),MAX(E7-H7,E7-F7)))</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="38">
+        <f>(G7+I7)*100-J7</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="35">
+        <v>555</v>
+      </c>
+      <c r="D8" s="35">
+        <v>570</v>
+      </c>
+      <c r="E8" s="35">
+        <v>630</v>
+      </c>
+      <c r="F8" s="35">
+        <v>645</v>
+      </c>
+      <c r="G8" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H8" s="37">
+        <v>574</v>
+      </c>
+      <c r="I8" s="36">
+        <f>IF(AND(H8&lt;=E8,H8&gt;=D8),0,IF(H8&lt;D8,MAX(H8-D8,C8-D8),MAX(E8-H8,E8-F8)))</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K8" s="38">
+        <f>(G8+I8)*100-J8</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="H5" s="39">
-        <v>562</v>
-      </c>
-      <c r="I5" s="38">
-        <f>IF(AND(H5&lt;=E5,H5&gt;=D5),0,IF(H5&lt;D5,MAX(H5-D5,C5-D5),MAX(E5-H5,E5-F5)))</f>
-        <v>-8</v>
-      </c>
-      <c r="J5" s="49">
-        <v>4</v>
-      </c>
-      <c r="K5" s="44">
-        <f>(G5+I5)*100-J5</f>
-        <v>-304</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="36">
+      <c r="C9" s="35">
         <v>555</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D9" s="35">
         <v>570</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E9" s="35">
         <v>630</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F9" s="35">
         <v>645</v>
       </c>
-      <c r="G6" s="40">
-        <v>5</v>
-      </c>
-      <c r="H6" s="41">
-        <v>615</v>
-      </c>
-      <c r="I6" s="40">
-        <f t="shared" ref="I6:I7" si="0">IF(AND(H6&lt;=E6,H6&gt;=D6),0,IF(H6&lt;D6,MAX(H6-D6,C6-D6),MAX(E6-H6,E6-F6)))</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="48">
-        <v>4</v>
-      </c>
-      <c r="K6" s="45">
-        <f t="shared" ref="K6:K7" si="1">(G6+I6)*100-J6</f>
-        <v>496</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="37">
+      <c r="G9" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H9" s="37">
+        <v>545</v>
+      </c>
+      <c r="I9" s="36">
+        <f>IF(AND(H9&lt;=E9,H9&gt;=D9),0,IF(H9&lt;D9,MAX(H9-D9,C9-D9),MAX(E9-H9,E9-F9)))</f>
+        <v>-15</v>
+      </c>
+      <c r="J9" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K9" s="38">
+        <f>(G9+I9)*100-J9</f>
+        <v>-1404.3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="2">
+        <v>6</v>
+      </c>
+      <c r="C10" s="35">
         <v>555</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D10" s="35">
         <v>570</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E10" s="35">
         <v>630</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F10" s="35">
         <v>645</v>
       </c>
-      <c r="G7" s="42">
-        <v>5</v>
-      </c>
-      <c r="H7" s="43">
+      <c r="G10" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H10" s="37">
+        <v>576</v>
+      </c>
+      <c r="I10" s="36">
+        <f>IF(AND(H10&lt;=E10,H10&gt;=D10),0,IF(H10&lt;D10,MAX(H10-D10,C10-D10),MAX(E10-H10,E10-F10)))</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K10" s="38">
+        <f>(G10+I10)*100-J10</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>7</v>
+      </c>
+      <c r="C11" s="35">
+        <v>555</v>
+      </c>
+      <c r="D11" s="35">
+        <v>570</v>
+      </c>
+      <c r="E11" s="35">
+        <v>630</v>
+      </c>
+      <c r="F11" s="35">
+        <v>645</v>
+      </c>
+      <c r="G11" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H11" s="37">
+        <v>577</v>
+      </c>
+      <c r="I11" s="36">
+        <f>IF(AND(H11&lt;=E11,H11&gt;=D11),0,IF(H11&lt;D11,MAX(H11-D11,C11-D11),MAX(E11-H11,E11-F11)))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K11" s="38">
+        <f>(G11+I11)*100-J11</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>8</v>
+      </c>
+      <c r="C12" s="35">
+        <v>555</v>
+      </c>
+      <c r="D12" s="35">
+        <v>570</v>
+      </c>
+      <c r="E12" s="35">
+        <v>630</v>
+      </c>
+      <c r="F12" s="35">
+        <v>645</v>
+      </c>
+      <c r="G12" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H12" s="37">
+        <v>578</v>
+      </c>
+      <c r="I12" s="36">
+        <f>IF(AND(H12&lt;=E12,H12&gt;=D12),0,IF(H12&lt;D12,MAX(H12-D12,C12-D12),MAX(E12-H12,E12-F12)))</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K12" s="38">
+        <f>(G12+I12)*100-J12</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>9</v>
+      </c>
+      <c r="C13" s="35">
+        <v>555</v>
+      </c>
+      <c r="D13" s="35">
+        <v>570</v>
+      </c>
+      <c r="E13" s="35">
+        <v>630</v>
+      </c>
+      <c r="F13" s="35">
+        <v>645</v>
+      </c>
+      <c r="G13" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H13" s="37">
+        <v>579</v>
+      </c>
+      <c r="I13" s="36">
+        <f>IF(AND(H13&lt;=E13,H13&gt;=D13),0,IF(H13&lt;D13,MAX(H13-D13,C13-D13),MAX(E13-H13,E13-F13)))</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="38">
+        <f>(G13+I13)*100-J13</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>10</v>
+      </c>
+      <c r="C14" s="35">
+        <v>555</v>
+      </c>
+      <c r="D14" s="35">
+        <v>570</v>
+      </c>
+      <c r="E14" s="35">
+        <v>630</v>
+      </c>
+      <c r="F14" s="35">
+        <v>645</v>
+      </c>
+      <c r="G14" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H14" s="37">
         <v>580</v>
       </c>
-      <c r="I7" s="42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="50">
-        <v>4</v>
-      </c>
-      <c r="K7" s="46">
-        <f t="shared" si="1"/>
-        <v>496</v>
+      <c r="I14" s="36">
+        <f>IF(AND(H14&lt;=E14,H14&gt;=D14),0,IF(H14&lt;D14,MAX(H14-D14,C14-D14),MAX(E14-H14,E14-F14)))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="38">
+        <f>(G14+I14)*100-J14</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="35">
+        <v>555</v>
+      </c>
+      <c r="D15" s="35">
+        <v>570</v>
+      </c>
+      <c r="E15" s="35">
+        <v>630</v>
+      </c>
+      <c r="F15" s="35">
+        <v>645</v>
+      </c>
+      <c r="G15" s="36">
+        <v>0.96</v>
+      </c>
+      <c r="H15" s="37">
+        <v>581</v>
+      </c>
+      <c r="I15" s="36">
+        <f>IF(AND(H15&lt;=E15,H15&gt;=D15),0,IF(H15&lt;D15,MAX(H15-D15,C15-D15),MAX(E15-H15,E15-F15)))</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K15" s="38">
+        <f>(G15+I15)*100-J15</f>
+        <v>95.7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K5:K114">
+  <conditionalFormatting sqref="K5:K112">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\Fund-Site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C772EBF9-E712-48B2-ACA6-80F0B7DB6579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77AE056-9BED-4B09-A113-E61DC5F25C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="5" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="696" yWindow="3024" windowWidth="18432" windowHeight="10680" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -1355,21 +1355,27 @@
       <c r="C13" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="42" t="e">
+      <c r="D13" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="E13" s="42">
         <f t="shared" ref="E13:E21" si="5">1/D13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F13" s="6" t="e">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F13" s="6">
         <f t="shared" ref="F13:F21" si="6">E13-0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="49" t="e">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="G13" s="49">
         <f t="shared" ref="G13:G21" si="7">1/F13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
+        <v>1.5789473684210527</v>
+      </c>
+      <c r="H13" s="54">
+        <v>0</v>
+      </c>
+      <c r="I13" s="54" t="s">
+        <v>7</v>
+      </c>
       <c r="J13" s="26">
         <f>IF(H13=0,0,IF(I13="WON",(G13-1)*0.95,-1))</f>
         <v>0</v>
@@ -1386,28 +1392,34 @@
       <c r="C14" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="42" t="e">
+      <c r="D14" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="E14" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="6" t="e">
+        <v>0.65789473684210531</v>
+      </c>
+      <c r="F14" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="49" t="e">
+        <v>0.4578947368421053</v>
+      </c>
+      <c r="G14" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
+        <v>2.1839080459770113</v>
+      </c>
+      <c r="H14" s="54">
+        <v>1</v>
+      </c>
+      <c r="I14" s="54" t="s">
+        <v>7</v>
+      </c>
       <c r="J14" s="26">
-        <f t="shared" ref="J14:J21" si="9">IF(H14=0,0,IF(I14="WON",(G14-1)*0.95,-1))</f>
-        <v>0</v>
+        <f>IF(H14=0,0,IF(I14="WON",(G14-1)*0.94,-1))</f>
+        <v>1.1128735632183906</v>
       </c>
       <c r="K14" s="27">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>61.820126436781592</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
@@ -1433,7 +1445,7 @@
       <c r="H15" s="51"/>
       <c r="I15" s="51"/>
       <c r="J15" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J14:J21" si="9">IF(H15=0,0,IF(I15="WON",(G15-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K15" s="27">
@@ -2165,14 +2177,14 @@
         <v>571</v>
       </c>
       <c r="I5" s="36">
-        <f>IF(AND(H5&lt;=E5,H5&gt;=D5),0,IF(H5&lt;D5,MAX(H5-D5,C5-D5),MAX(E5-H5,E5-F5)))</f>
+        <f t="shared" ref="I5:I15" si="0">IF(AND(H5&lt;=E5,H5&gt;=D5),0,IF(H5&lt;D5,MAX(H5-D5,C5-D5),MAX(E5-H5,E5-F5)))</f>
         <v>0</v>
       </c>
       <c r="J5" s="40">
         <v>0.3</v>
       </c>
       <c r="K5" s="38">
-        <f>(G5+I5)*100-J5</f>
+        <f t="shared" ref="K5:K15" si="1">(G5+I5)*100-J5</f>
         <v>95.7</v>
       </c>
     </row>
@@ -2199,14 +2211,14 @@
         <v>572</v>
       </c>
       <c r="I6" s="36">
-        <f>IF(AND(H6&lt;=E6,H6&gt;=D6),0,IF(H6&lt;D6,MAX(H6-D6,C6-D6),MAX(E6-H6,E6-F6)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J6" s="40">
         <v>0.3</v>
       </c>
       <c r="K6" s="38">
-        <f>(G6+I6)*100-J6</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2233,14 +2245,14 @@
         <v>573</v>
       </c>
       <c r="I7" s="36">
-        <f>IF(AND(H7&lt;=E7,H7&gt;=D7),0,IF(H7&lt;D7,MAX(H7-D7,C7-D7),MAX(E7-H7,E7-F7)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7" s="40">
         <v>0.3</v>
       </c>
       <c r="K7" s="38">
-        <f>(G7+I7)*100-J7</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2267,14 +2279,14 @@
         <v>574</v>
       </c>
       <c r="I8" s="36">
-        <f>IF(AND(H8&lt;=E8,H8&gt;=D8),0,IF(H8&lt;D8,MAX(H8-D8,C8-D8),MAX(E8-H8,E8-F8)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="40">
         <v>0.3</v>
       </c>
       <c r="K8" s="38">
-        <f>(G8+I8)*100-J8</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2301,14 +2313,14 @@
         <v>545</v>
       </c>
       <c r="I9" s="36">
-        <f>IF(AND(H9&lt;=E9,H9&gt;=D9),0,IF(H9&lt;D9,MAX(H9-D9,C9-D9),MAX(E9-H9,E9-F9)))</f>
+        <f t="shared" si="0"/>
         <v>-15</v>
       </c>
       <c r="J9" s="40">
         <v>0.3</v>
       </c>
       <c r="K9" s="38">
-        <f>(G9+I9)*100-J9</f>
+        <f t="shared" si="1"/>
         <v>-1404.3</v>
       </c>
     </row>
@@ -2335,14 +2347,14 @@
         <v>576</v>
       </c>
       <c r="I10" s="36">
-        <f>IF(AND(H10&lt;=E10,H10&gt;=D10),0,IF(H10&lt;D10,MAX(H10-D10,C10-D10),MAX(E10-H10,E10-F10)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J10" s="40">
         <v>0.3</v>
       </c>
       <c r="K10" s="38">
-        <f>(G10+I10)*100-J10</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2369,14 +2381,14 @@
         <v>577</v>
       </c>
       <c r="I11" s="36">
-        <f>IF(AND(H11&lt;=E11,H11&gt;=D11),0,IF(H11&lt;D11,MAX(H11-D11,C11-D11),MAX(E11-H11,E11-F11)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J11" s="40">
         <v>0.3</v>
       </c>
       <c r="K11" s="38">
-        <f>(G11+I11)*100-J11</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2403,14 +2415,14 @@
         <v>578</v>
       </c>
       <c r="I12" s="36">
-        <f>IF(AND(H12&lt;=E12,H12&gt;=D12),0,IF(H12&lt;D12,MAX(H12-D12,C12-D12),MAX(E12-H12,E12-F12)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J12" s="40">
         <v>0.3</v>
       </c>
       <c r="K12" s="38">
-        <f>(G12+I12)*100-J12</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2437,14 +2449,14 @@
         <v>579</v>
       </c>
       <c r="I13" s="36">
-        <f>IF(AND(H13&lt;=E13,H13&gt;=D13),0,IF(H13&lt;D13,MAX(H13-D13,C13-D13),MAX(E13-H13,E13-F13)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J13" s="40">
         <v>0.3</v>
       </c>
       <c r="K13" s="38">
-        <f>(G13+I13)*100-J13</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2471,14 +2483,14 @@
         <v>580</v>
       </c>
       <c r="I14" s="36">
-        <f>IF(AND(H14&lt;=E14,H14&gt;=D14),0,IF(H14&lt;D14,MAX(H14-D14,C14-D14),MAX(E14-H14,E14-F14)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J14" s="40">
         <v>0.3</v>
       </c>
       <c r="K14" s="38">
-        <f>(G14+I14)*100-J14</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>
@@ -2505,14 +2517,14 @@
         <v>581</v>
       </c>
       <c r="I15" s="36">
-        <f>IF(AND(H15&lt;=E15,H15&gt;=D15),0,IF(H15&lt;D15,MAX(H15-D15,C15-D15),MAX(E15-H15,E15-F15)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J15" s="40">
         <v>0.3</v>
       </c>
       <c r="K15" s="38">
-        <f>(G15+I15)*100-J15</f>
+        <f t="shared" si="1"/>
         <v>95.7</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\Fund-Site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77AE056-9BED-4B09-A113-E61DC5F25C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A17BB3-F107-4CAE-BF07-B7F23A84D9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="3024" windowWidth="18432" windowHeight="10680" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>Griekspoor</t>
+  </si>
+  <si>
+    <t>Noskova</t>
+  </si>
+  <si>
+    <t>Alcaraz</t>
+  </si>
+  <si>
+    <t>Andreeva</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L7"/>
+  <dimension ref="B2:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -1779,33 +1788,115 @@
       </c>
       <c r="L6" s="53"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="20" t="e">
+      <c r="C7" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="31">
+        <v>1.25</v>
+      </c>
+      <c r="E7" s="20">
         <f>1/D7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F7" s="21" t="e">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="21">
         <f>E7-0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="22" t="e">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G7" s="22">
         <f t="shared" ref="G7" si="0">1/F7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="31"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="H7" s="30">
+        <v>1</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>11</v>
+      </c>
       <c r="J7" s="15">
         <f>IF(H7=0,0,IF(I7="WON",(G7-1),-1))</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K7" s="25">
         <f>J7*J$3</f>
-        <v>0</v>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="31">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E8" s="20">
+        <f t="shared" ref="E8:E9" si="1">1/D8</f>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" ref="F8:F9" si="2">E8-0.2</f>
+        <v>0.70090090090090085</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" ref="G8:G9" si="3">1/F8</f>
+        <v>1.4267352185089976</v>
+      </c>
+      <c r="H8" s="30">
+        <v>1</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" ref="J8:J9" si="4">IF(H8=0,0,IF(I8="WON",(G8-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K8" s="25">
+        <f t="shared" ref="K8:K9" si="5">J8*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="31">
+        <v>1.42</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="1"/>
+        <v>0.70422535211267612</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="2"/>
+        <v>0.50422535211267605</v>
+      </c>
+      <c r="G9" s="22">
+        <f t="shared" si="3"/>
+        <v>1.9832402234636872</v>
+      </c>
+      <c r="H9" s="30">
+        <v>1</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="4"/>
+        <v>-1</v>
+      </c>
+      <c r="K9" s="25">
+        <f t="shared" si="5"/>
+        <v>-55.55</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\Fund-Site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A17BB3-F107-4CAE-BF07-B7F23A84D9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ED6FB63-8E07-7847-832E-3A56A62888BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="5660" yWindow="1460" windowWidth="24800" windowHeight="14860" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -221,6 +221,24 @@
     <t>Comesana</t>
   </si>
   <si>
+    <t>Betfair take 6% in fees</t>
+  </si>
+  <si>
+    <t>Griekspoor</t>
+  </si>
+  <si>
+    <t>Alcaraz</t>
+  </si>
+  <si>
+    <t>Andreeva</t>
+  </si>
+  <si>
+    <t>Jovic</t>
+  </si>
+  <si>
+    <t>Kostyuk</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -240,23 +258,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: backing the favourite @ 20% above starting, first to 4 games in first set</t>
+      <t>: backing the favourite @ 20% above starting, first to 5 games in first set</t>
     </r>
-  </si>
-  <si>
-    <t>Betfair take 6% in fees</t>
-  </si>
-  <si>
-    <t>Griekspoor</t>
-  </si>
-  <si>
-    <t>Noskova</t>
-  </si>
-  <si>
-    <t>Alcaraz</t>
-  </si>
-  <si>
-    <t>Andreeva</t>
   </si>
 </sst>
 </file>
@@ -264,11 +267,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +311,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -504,9 +514,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -529,7 +539,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -610,22 +620,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -660,11 +670,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1008,21 +1021,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:K21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="11" width="10.109375" customWidth="1"/>
+    <col min="4" max="11" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2"/>
     </row>
-    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
@@ -1031,7 +1044,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1076,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1100,7 +1113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>2</v>
       </c>
@@ -1137,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>3</v>
       </c>
@@ -1173,7 +1186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>4</v>
       </c>
@@ -1210,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3">
         <v>5</v>
       </c>
@@ -1247,7 +1260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3">
         <v>6</v>
       </c>
@@ -1284,7 +1297,7 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>7</v>
       </c>
@@ -1321,7 +1334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1357,7 +1370,7 @@
         <v>87.724560000000011</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="44">
         <v>9</v>
       </c>
@@ -1394,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="44">
         <v>10</v>
       </c>
@@ -1431,59 +1444,71 @@
         <v>61.820126436781592</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="44">
         <v>11</v>
       </c>
       <c r="C15" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="42" t="e">
+      <c r="D15" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E15" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="6" t="e">
+        <v>0.86956521739130443</v>
+      </c>
+      <c r="F15" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="49" t="e">
+        <v>0.66956521739130448</v>
+      </c>
+      <c r="G15" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
+        <v>1.4935064935064932</v>
+      </c>
+      <c r="H15" s="54">
+        <v>1</v>
+      </c>
+      <c r="I15" s="54" t="s">
+        <v>7</v>
+      </c>
       <c r="J15" s="26">
-        <f t="shared" ref="J14:J21" si="9">IF(H15=0,0,IF(I15="WON",(G15-1)*0.95,-1))</f>
-        <v>0</v>
+        <f t="shared" ref="J15:J21" si="9">IF(H15=0,0,IF(I15="WON",(G15-1)*0.95,-1))</f>
+        <v>0.46883116883116854</v>
       </c>
       <c r="K15" s="27">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+        <v>26.043571428571411</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="44">
         <v>12</v>
       </c>
       <c r="C16" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="42" t="e">
+      <c r="D16" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="E16" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="6" t="e">
+        <v>0.78740157480314954</v>
+      </c>
+      <c r="F16" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="49" t="e">
+        <v>0.58740157480314958</v>
+      </c>
+      <c r="G16" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
+        <v>1.7024128686327078</v>
+      </c>
+      <c r="H16" s="54">
+        <v>0</v>
+      </c>
+      <c r="I16" s="54" t="s">
+        <v>7</v>
+      </c>
       <c r="J16" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1493,27 +1518,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="44">
         <v>13</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="42" t="e">
+      <c r="D17" s="5">
+        <v>1.77</v>
+      </c>
+      <c r="E17" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="6" t="e">
+        <v>0.56497175141242939</v>
+      </c>
+      <c r="F17" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G17" s="49" t="e">
+        <v>0.36497175141242938</v>
+      </c>
+      <c r="G17" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H17" s="51"/>
+        <v>2.7399380804953561</v>
+      </c>
+      <c r="H17" s="51">
+        <v>0</v>
+      </c>
       <c r="I17" s="51"/>
       <c r="J17" s="26">
         <f t="shared" si="9"/>
@@ -1524,27 +1553,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="44">
         <v>14</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="42" t="e">
+      <c r="D18" s="5">
+        <v>1.72</v>
+      </c>
+      <c r="E18" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" s="6" t="e">
+        <v>0.58139534883720934</v>
+      </c>
+      <c r="F18" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" s="49" t="e">
+        <v>0.38139534883720932</v>
+      </c>
+      <c r="G18" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H18" s="51"/>
+        <v>2.6219512195121948</v>
+      </c>
+      <c r="H18" s="51">
+        <v>0</v>
+      </c>
       <c r="I18" s="51"/>
       <c r="J18" s="26">
         <f t="shared" si="9"/>
@@ -1555,25 +1588,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="44">
         <v>15</v>
       </c>
       <c r="C19" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="42" t="e">
+      <c r="D19" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E19" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="6" t="e">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="F19" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="49" t="e">
+        <v>0.71743119266055033</v>
+      </c>
+      <c r="G19" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>1.3938618925831205</v>
       </c>
       <c r="H19" s="51"/>
       <c r="I19" s="51"/>
@@ -1586,25 +1621,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="44">
         <v>16</v>
       </c>
       <c r="C20" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="42" t="e">
+      <c r="D20" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E20" s="42">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" s="6" t="e">
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="F20" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G20" s="49" t="e">
+        <v>0.69285714285714284</v>
+      </c>
+      <c r="G20" s="49">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>1.4432989690721649</v>
       </c>
       <c r="H20" s="51"/>
       <c r="I20" s="51"/>
@@ -1617,25 +1654,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="45">
         <v>17</v>
       </c>
       <c r="C21" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="43" t="e">
+      <c r="D21" s="11">
+        <v>1.76</v>
+      </c>
+      <c r="E21" s="43">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="10" t="e">
+        <v>0.56818181818181823</v>
+      </c>
+      <c r="F21" s="10">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="50" t="e">
+        <v>0.36818181818181822</v>
+      </c>
+      <c r="G21" s="50">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>2.716049382716049</v>
       </c>
       <c r="H21" s="52"/>
       <c r="I21" s="52"/>
@@ -1656,22 +1695,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:L10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>9</v>
@@ -1681,7 +1721,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -1713,7 +1753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1751,12 +1791,12 @@
       </c>
       <c r="L5" s="53"/>
     </row>
-    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="31">
         <v>1.56</v>
@@ -1788,115 +1828,152 @@
       </c>
       <c r="L6" s="53"/>
     </row>
-    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>43</v>
+      <c r="C7" s="56" t="s">
+        <v>42</v>
       </c>
       <c r="D7" s="31">
-        <v>1.25</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E7" s="20">
-        <f>1/D7</f>
-        <v>0.8</v>
+        <f t="shared" ref="E7:E10" si="0">1/D7</f>
+        <v>0.9009009009009008</v>
       </c>
       <c r="F7" s="21">
-        <f>E7-0.2</f>
-        <v>0.60000000000000009</v>
+        <f t="shared" ref="F7:F10" si="1">E7-0.2</f>
+        <v>0.70090090090090085</v>
       </c>
       <c r="G7" s="22">
-        <f t="shared" ref="G7" si="0">1/F7</f>
-        <v>1.6666666666666665</v>
+        <f t="shared" ref="G7:G8" si="2">1/F7</f>
+        <v>1.4267352185089976</v>
       </c>
       <c r="H7" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J7" s="15">
-        <f>IF(H7=0,0,IF(I7="WON",(G7-1),-1))</f>
-        <v>-1</v>
+        <f t="shared" ref="J7:J8" si="3">IF(H7=0,0,IF(I7="WON",(G7-1),-1))</f>
+        <v>0</v>
       </c>
       <c r="K7" s="25">
-        <f>J7*J$3</f>
-        <v>-55.55</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="K7:K10" si="4">J7*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>44</v>
+      <c r="C8" s="56" t="s">
+        <v>43</v>
       </c>
       <c r="D8" s="31">
-        <v>1.1100000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="E8" s="20">
-        <f t="shared" ref="E8:E9" si="1">1/D8</f>
-        <v>0.9009009009009008</v>
+        <f t="shared" si="0"/>
+        <v>0.70422535211267612</v>
       </c>
       <c r="F8" s="21">
-        <f t="shared" ref="F8:F9" si="2">E8-0.2</f>
-        <v>0.70090090090090085</v>
+        <f t="shared" si="1"/>
+        <v>0.50422535211267605</v>
       </c>
       <c r="G8" s="22">
-        <f t="shared" ref="G8:G9" si="3">1/F8</f>
-        <v>1.4267352185089976</v>
+        <f t="shared" si="2"/>
+        <v>1.9832402234636872</v>
       </c>
       <c r="H8" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" ref="J8:J9" si="4">IF(H8=0,0,IF(I8="WON",(G8-1),-1))</f>
-        <v>-1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="K8" s="25">
-        <f t="shared" ref="K8:K9" si="5">J8*J$3</f>
-        <v>-55.55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>45</v>
+      <c r="C9" s="56" t="s">
+        <v>44</v>
       </c>
       <c r="D9" s="31">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="E9" s="20">
+        <f t="shared" si="0"/>
+        <v>0.75187969924812026</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="1"/>
-        <v>0.70422535211267612</v>
-      </c>
-      <c r="F9" s="21">
-        <f t="shared" si="2"/>
-        <v>0.50422535211267605</v>
+        <v>0.5518796992481203</v>
       </c>
       <c r="G9" s="22">
-        <f t="shared" si="3"/>
-        <v>1.9832402234636872</v>
+        <f t="shared" ref="G9:G10" si="5">1/F9</f>
+        <v>1.8119891008174387</v>
       </c>
       <c r="H9" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>11</v>
       </c>
       <c r="J9" s="15">
+        <f t="shared" ref="J9:J10" si="6">IF(H9=0,0,IF(I9="WON",(G9-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="25">
         <f t="shared" si="4"/>
-        <v>-1</v>
-      </c>
-      <c r="K9" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="2">
+        <v>6</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1.33</v>
+      </c>
+      <c r="E10" s="20">
+        <f t="shared" si="0"/>
+        <v>0.75187969924812026</v>
+      </c>
+      <c r="F10" s="21">
+        <f t="shared" si="1"/>
+        <v>0.5518796992481203</v>
+      </c>
+      <c r="G10" s="22">
         <f t="shared" si="5"/>
-        <v>-55.55</v>
+        <v>1.8119891008174387</v>
+      </c>
+      <c r="H10" s="30">
+        <v>0</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1908,17 +1985,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E6120F-3D79-45D2-9E7F-690D79FF71F4}">
   <dimension ref="B2:K5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="I3" s="7" t="s">
@@ -1929,7 +2006,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +2038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2005,14 +2082,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90ADAF7-1BB4-48D6-89E7-0AED41AA649D}">
   <dimension ref="B2:K5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="I3" s="7" t="s">
@@ -2023,7 +2100,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -2055,7 +2132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2099,14 +2176,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BA0578-228A-4ECA-BD97-9526260EC85E}">
   <dimension ref="B2:K5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="I3" s="7" t="s">
@@ -2117,7 +2194,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -2149,7 +2226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2192,17 +2269,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821F4CAB-11EC-4DB3-9BD6-AF06D08A4FD3}">
   <dimension ref="B2:M15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="13" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -2213,7 +2290,7 @@
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
     </row>
-    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +2322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2279,7 +2356,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -2313,7 +2390,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -2347,7 +2424,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -2381,7 +2458,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -2415,7 +2492,7 @@
         <v>-1404.3</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -2449,7 +2526,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -2483,7 +2560,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -2517,7 +2594,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -2551,7 +2628,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -2585,7 +2662,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>11</v>
       </c>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ED6FB63-8E07-7847-832E-3A56A62888BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8A378-997F-B943-B203-8B9298A991C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5660" yWindow="1460" windowWidth="24800" windowHeight="14860" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -1473,12 +1473,12 @@
         <v>7</v>
       </c>
       <c r="J15" s="26">
-        <f t="shared" ref="J15:J21" si="9">IF(H15=0,0,IF(I15="WON",(G15-1)*0.95,-1))</f>
-        <v>0.46883116883116854</v>
+        <f>IF(H15=0,0,IF(I15="WON",(G15-1)*0.94,-1))</f>
+        <v>0.46389610389610358</v>
       </c>
       <c r="K15" s="27">
         <f t="shared" si="8"/>
-        <v>26.043571428571411</v>
+        <v>25.769428571428552</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -1504,18 +1504,18 @@
         <v>1.7024128686327078</v>
       </c>
       <c r="H16" s="54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="54" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J16" s="26">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>IF(H16=0,0,IF(I16="WON",(G16-1)*0.94,-1))</f>
+        <v>-1</v>
       </c>
       <c r="K16" s="27">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I17" s="51"/>
       <c r="J17" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J15:J21" si="9">IF(H17=0,0,IF(I17="WON",(G17-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K17" s="27">

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8A378-997F-B943-B203-8B9298A991C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97891604-C409-0C4F-8CF7-AF51834B5808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5660" yWindow="1460" windowWidth="24800" windowHeight="14860" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="1520" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -260,6 +260,18 @@
       </rPr>
       <t>: backing the favourite @ 20% above starting, first to 5 games in first set</t>
     </r>
+  </si>
+  <si>
+    <t>Nava</t>
+  </si>
+  <si>
+    <t>Expiry</t>
+  </si>
+  <si>
+    <t>Magpies</t>
+  </si>
+  <si>
+    <t>Kangaroos</t>
   </si>
 </sst>
 </file>
@@ -516,7 +528,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -668,8 +680,6 @@
     <xf numFmtId="2" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -678,6 +688,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1020,7 +1069,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K21"/>
+  <dimension ref="B2:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1120,7 +1169,7 @@
       <c r="C6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="52">
         <v>1.77</v>
       </c>
       <c r="E6" s="42">
@@ -1131,14 +1180,14 @@
         <f>E6-0.2</f>
         <v>0.36497175141242938</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="53">
         <f>1/F6</f>
         <v>2.7399380804953561</v>
       </c>
-      <c r="H6" s="54">
-        <v>0</v>
-      </c>
-      <c r="I6" s="54" t="s">
+      <c r="H6" s="52">
+        <v>0</v>
+      </c>
+      <c r="I6" s="52" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="26">
@@ -1157,7 +1206,7 @@
       <c r="C7" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="52">
         <v>1.91</v>
       </c>
       <c r="E7" s="42">
@@ -1168,13 +1217,13 @@
         <f t="shared" ref="F7:F12" si="3">E7-0.2</f>
         <v>0.32356020942408376</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="53">
         <v>3.1</v>
       </c>
-      <c r="H7" s="54">
-        <v>0</v>
-      </c>
-      <c r="I7" s="54" t="s">
+      <c r="H7" s="52">
+        <v>0</v>
+      </c>
+      <c r="I7" s="52" t="s">
         <v>7</v>
       </c>
       <c r="J7" s="26">
@@ -1193,7 +1242,7 @@
       <c r="C8" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="52">
         <v>1.44</v>
       </c>
       <c r="E8" s="42">
@@ -1204,14 +1253,14 @@
         <f t="shared" si="3"/>
         <v>0.49444444444444441</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="53">
         <f t="shared" ref="G8:G11" si="4">1/F8</f>
         <v>2.0224719101123596</v>
       </c>
-      <c r="H8" s="54">
-        <v>0</v>
-      </c>
-      <c r="I8" s="54" t="s">
+      <c r="H8" s="52">
+        <v>0</v>
+      </c>
+      <c r="I8" s="52" t="s">
         <v>7</v>
       </c>
       <c r="J8" s="26">
@@ -1230,7 +1279,7 @@
       <c r="C9" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="52">
         <v>1.19</v>
       </c>
       <c r="E9" s="42">
@@ -1241,14 +1290,14 @@
         <f t="shared" si="3"/>
         <v>0.64033613445378146</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="53">
         <f t="shared" si="4"/>
         <v>1.5616797900262469</v>
       </c>
-      <c r="H9" s="54">
-        <v>0</v>
-      </c>
-      <c r="I9" s="54" t="s">
+      <c r="H9" s="52">
+        <v>0</v>
+      </c>
+      <c r="I9" s="52" t="s">
         <v>7</v>
       </c>
       <c r="J9" s="26">
@@ -1267,7 +1316,7 @@
       <c r="C10" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="52">
         <v>1.38</v>
       </c>
       <c r="E10" s="42">
@@ -1278,14 +1327,14 @@
         <f t="shared" si="3"/>
         <v>0.52463768115942044</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="53">
         <f t="shared" si="4"/>
         <v>1.9060773480662978</v>
       </c>
-      <c r="H10" s="54">
+      <c r="H10" s="52">
         <v>1</v>
       </c>
-      <c r="I10" s="54" t="s">
+      <c r="I10" s="52" t="s">
         <v>11</v>
       </c>
       <c r="J10" s="26">
@@ -1304,7 +1353,7 @@
       <c r="C11" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="52">
         <v>1.02</v>
       </c>
       <c r="E11" s="42">
@@ -1315,14 +1364,14 @@
         <f t="shared" si="3"/>
         <v>0.78039215686274499</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="53">
         <f t="shared" si="4"/>
         <v>1.2814070351758795</v>
       </c>
-      <c r="H11" s="54">
-        <v>0</v>
-      </c>
-      <c r="I11" s="54" t="s">
+      <c r="H11" s="52">
+        <v>0</v>
+      </c>
+      <c r="I11" s="52" t="s">
         <v>7</v>
       </c>
       <c r="J11" s="26">
@@ -1371,39 +1420,39 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="44">
+      <c r="B13" s="57">
         <v>9</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="58">
         <v>1.2</v>
       </c>
-      <c r="E13" s="42">
-        <f t="shared" ref="E13:E21" si="5">1/D13</f>
+      <c r="E13" s="41">
+        <f t="shared" ref="E13:E30" si="5">1/D13</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F13" s="6">
-        <f t="shared" ref="F13:F21" si="6">E13-0.2</f>
+      <c r="F13" s="21">
+        <f t="shared" ref="F13:F30" si="6">E13-0.2</f>
         <v>0.6333333333333333</v>
       </c>
-      <c r="G13" s="49">
-        <f t="shared" ref="G13:G21" si="7">1/F13</f>
+      <c r="G13" s="59">
+        <f t="shared" ref="G13:G20" si="7">1/F13</f>
         <v>1.5789473684210527</v>
       </c>
-      <c r="H13" s="54">
-        <v>0</v>
-      </c>
-      <c r="I13" s="54" t="s">
+      <c r="H13" s="23">
+        <v>0</v>
+      </c>
+      <c r="I13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="24">
         <f>IF(H13=0,0,IF(I13="WON",(G13-1)*0.95,-1))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="27">
-        <f t="shared" ref="K13:K21" si="8">J13*J$3</f>
+      <c r="K13" s="25">
+        <f t="shared" ref="K13:K22" si="8">J13*J$3</f>
         <v>0</v>
       </c>
     </row>
@@ -1429,10 +1478,10 @@
         <f t="shared" si="7"/>
         <v>2.1839080459770113</v>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="52">
         <v>1</v>
       </c>
-      <c r="I14" s="54" t="s">
+      <c r="I14" s="52" t="s">
         <v>7</v>
       </c>
       <c r="J14" s="26">
@@ -1466,19 +1515,19 @@
         <f t="shared" si="7"/>
         <v>1.4935064935064932</v>
       </c>
-      <c r="H15" s="54">
+      <c r="H15" s="52">
         <v>1</v>
       </c>
-      <c r="I15" s="54" t="s">
+      <c r="I15" s="52" t="s">
         <v>7</v>
       </c>
       <c r="J15" s="26">
-        <f>IF(H15=0,0,IF(I15="WON",(G15-1)*0.94,-1))</f>
-        <v>0.46389610389610358</v>
+        <f t="shared" ref="J15:J21" si="9">IF(H15=0,0,IF(I15="WON",(G15-1)*0.95,-1))</f>
+        <v>0.46883116883116854</v>
       </c>
       <c r="K15" s="27">
         <f t="shared" si="8"/>
-        <v>25.769428571428552</v>
+        <v>26.043571428571411</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -1503,14 +1552,14 @@
         <f t="shared" si="7"/>
         <v>1.7024128686327078</v>
       </c>
-      <c r="H16" s="54">
+      <c r="H16" s="52">
         <v>1</v>
       </c>
-      <c r="I16" s="54" t="s">
+      <c r="I16" s="52" t="s">
         <v>11</v>
       </c>
       <c r="J16" s="26">
-        <f>IF(H16=0,0,IF(I16="WON",(G16-1)*0.94,-1))</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="K16" s="27">
@@ -1540,12 +1589,14 @@
         <f t="shared" si="7"/>
         <v>2.7399380804953561</v>
       </c>
-      <c r="H17" s="51">
-        <v>0</v>
-      </c>
-      <c r="I17" s="51"/>
+      <c r="H17" s="52">
+        <v>0</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>7</v>
+      </c>
       <c r="J17" s="26">
-        <f t="shared" ref="J15:J21" si="9">IF(H17=0,0,IF(I17="WON",(G17-1)*0.95,-1))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K17" s="27">
@@ -1575,10 +1626,12 @@
         <f t="shared" si="7"/>
         <v>2.6219512195121948</v>
       </c>
-      <c r="H18" s="51">
-        <v>0</v>
-      </c>
-      <c r="I18" s="51"/>
+      <c r="H18" s="52">
+        <v>0</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>7</v>
+      </c>
       <c r="J18" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1610,8 +1663,12 @@
         <f t="shared" si="7"/>
         <v>1.3938618925831205</v>
       </c>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
+      <c r="H19" s="52">
+        <v>0</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>7</v>
+      </c>
       <c r="J19" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1643,8 +1700,12 @@
         <f t="shared" si="7"/>
         <v>1.4432989690721649</v>
       </c>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
+      <c r="H20" s="52">
+        <v>0</v>
+      </c>
+      <c r="I20" s="52" t="s">
+        <v>7</v>
+      </c>
       <c r="J20" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -1662,28 +1723,331 @@
         <v>38</v>
       </c>
       <c r="D21" s="11">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="E21" s="43">
         <f t="shared" si="5"/>
-        <v>0.56818181818181823</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="F21" s="10">
         <f t="shared" si="6"/>
-        <v>0.36818181818181822</v>
+        <v>0.35555555555555557</v>
       </c>
       <c r="G21" s="50">
-        <f t="shared" si="7"/>
-        <v>2.716049382716049</v>
-      </c>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
+        <v>2.82</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J21" s="26">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K21" s="27">
         <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B22" s="46">
+        <v>18</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="58">
+        <v>1.64</v>
+      </c>
+      <c r="E22" s="41">
+        <f t="shared" si="5"/>
+        <v>0.6097560975609756</v>
+      </c>
+      <c r="F22" s="60">
+        <f t="shared" si="6"/>
+        <v>0.40975609756097559</v>
+      </c>
+      <c r="G22" s="59">
+        <f>1/F22</f>
+        <v>2.4404761904761907</v>
+      </c>
+      <c r="H22" s="23">
+        <v>1</v>
+      </c>
+      <c r="I22" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="24">
+        <f>IF(H22=0,0,IF(I22="WON",(G22-1)*0.94,-1))</f>
+        <v>1.3540476190476192</v>
+      </c>
+      <c r="K22" s="25">
+        <f t="shared" si="8"/>
+        <v>75.217345238095234</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" s="47">
+        <v>19</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1.56</v>
+      </c>
+      <c r="E23" s="42">
+        <f t="shared" si="5"/>
+        <v>0.64102564102564097</v>
+      </c>
+      <c r="F23" s="56">
+        <f t="shared" si="6"/>
+        <v>0.44102564102564096</v>
+      </c>
+      <c r="G23" s="49">
+        <f t="shared" ref="G23:G30" si="10">1/F23</f>
+        <v>2.2674418604651168</v>
+      </c>
+      <c r="H23" s="69">
+        <v>0</v>
+      </c>
+      <c r="I23" s="61"/>
+      <c r="J23" s="26">
+        <f t="shared" ref="J23:J30" si="11">IF(H23=0,0,IF(I23="WON",(G23-1)*0.95,-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="27">
+        <f t="shared" ref="K23:K30" si="12">J23*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B24" s="47">
+        <v>20</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="E24" s="42">
+        <f t="shared" si="5"/>
+        <v>0.75187969924812026</v>
+      </c>
+      <c r="F24" s="56">
+        <f t="shared" si="6"/>
+        <v>0.5518796992481203</v>
+      </c>
+      <c r="G24" s="49">
+        <f t="shared" si="10"/>
+        <v>1.8119891008174387</v>
+      </c>
+      <c r="H24" s="52">
+        <v>0</v>
+      </c>
+      <c r="I24" s="61"/>
+      <c r="J24" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B25" s="47">
+        <v>21</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E25" s="42">
+        <f t="shared" si="5"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="F25" s="56">
+        <f t="shared" si="6"/>
+        <v>0.70909090909090899</v>
+      </c>
+      <c r="G25" s="49">
+        <f t="shared" si="10"/>
+        <v>1.4102564102564104</v>
+      </c>
+      <c r="I25" s="61"/>
+      <c r="J25" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B26" s="47">
+        <v>22</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E26" s="42">
+        <f t="shared" si="5"/>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F26" s="56">
+        <f t="shared" si="6"/>
+        <v>0.70090090090090085</v>
+      </c>
+      <c r="G26" s="49">
+        <f t="shared" si="10"/>
+        <v>1.4267352185089976</v>
+      </c>
+      <c r="I26" s="61"/>
+      <c r="J26" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B27" s="47">
+        <v>23</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="E27" s="42">
+        <f t="shared" si="5"/>
+        <v>0.64935064935064934</v>
+      </c>
+      <c r="F27" s="56">
+        <f t="shared" si="6"/>
+        <v>0.44935064935064933</v>
+      </c>
+      <c r="G27" s="49">
+        <f t="shared" si="10"/>
+        <v>2.2254335260115607</v>
+      </c>
+      <c r="I27" s="61"/>
+      <c r="J27" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B28" s="47">
+        <v>24</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="E28" s="42">
+        <f t="shared" si="5"/>
+        <v>0.76923076923076916</v>
+      </c>
+      <c r="F28" s="56">
+        <f t="shared" si="6"/>
+        <v>0.56923076923076921</v>
+      </c>
+      <c r="G28" s="49">
+        <f t="shared" si="10"/>
+        <v>1.7567567567567568</v>
+      </c>
+      <c r="I28" s="61"/>
+      <c r="J28" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B29" s="47">
+        <v>25</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1.36</v>
+      </c>
+      <c r="E29" s="42">
+        <f t="shared" si="5"/>
+        <v>0.73529411764705876</v>
+      </c>
+      <c r="F29" s="56">
+        <f t="shared" si="6"/>
+        <v>0.5352941176470587</v>
+      </c>
+      <c r="G29" s="49">
+        <f t="shared" si="10"/>
+        <v>1.8681318681318686</v>
+      </c>
+      <c r="I29" s="61"/>
+      <c r="J29" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="48">
+        <v>26</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="11">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E30" s="43">
+        <f t="shared" si="5"/>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F30" s="62">
+        <f t="shared" si="6"/>
+        <v>0.70090090090090085</v>
+      </c>
+      <c r="G30" s="50">
+        <f t="shared" si="10"/>
+        <v>1.4267352185089976</v>
+      </c>
+      <c r="H30" s="63"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="28">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="29">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1695,7 +2059,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L10"/>
+  <dimension ref="B2:L12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -1789,7 +2153,7 @@
         <f>J5*J$3*0.94-0.21</f>
         <v>91.8994906832298</v>
       </c>
-      <c r="L5" s="53"/>
+      <c r="L5" s="51"/>
     </row>
     <row r="6" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
@@ -1826,13 +2190,13 @@
         <f>J6*J$3</f>
         <v>-55.55</v>
       </c>
-      <c r="L6" s="53"/>
+      <c r="L6" s="51"/>
     </row>
     <row r="7" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="54" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="31">
@@ -1869,7 +2233,7 @@
       <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="54" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="31">
@@ -1906,7 +2270,7 @@
       <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="54" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="31">
@@ -1939,11 +2303,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>6</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="54" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="31">
@@ -1974,6 +2338,79 @@
       <c r="K10" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
+        <v>7</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="31">
+        <v>1.75</v>
+      </c>
+      <c r="E11" s="20">
+        <f t="shared" ref="E11" si="7">1/D11</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" ref="F11" si="8">E11-0.2</f>
+        <v>0.37142857142857139</v>
+      </c>
+      <c r="G11" s="22">
+        <v>2.7</v>
+      </c>
+      <c r="H11" s="30">
+        <v>1</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" ref="J11" si="9">IF(H11=0,0,IF(I11="WON",(G11-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K11" s="25">
+        <f t="shared" ref="K11" si="10">J11*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <v>8</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="31">
+        <v>2.75</v>
+      </c>
+      <c r="E12" s="20">
+        <f t="shared" ref="E12" si="11">1/D12</f>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="F12" s="21">
+        <f t="shared" ref="F12" si="12">E12-0.2</f>
+        <v>0.16363636363636364</v>
+      </c>
+      <c r="G12" s="22">
+        <f>1/F12</f>
+        <v>6.1111111111111107</v>
+      </c>
+      <c r="H12" s="30">
+        <v>1</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" ref="J12" si="13">IF(H12=0,0,IF(I12="WON",(G12-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K12" s="25">
+        <f t="shared" ref="K12" si="14">J12*J$3</f>
+        <v>-55.55</v>
       </c>
     </row>
   </sheetData>
@@ -2268,441 +2705,145 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821F4CAB-11EC-4DB3-9BD6-AF06D08A4FD3}">
-  <dimension ref="B2:M15"/>
+  <dimension ref="B2:N6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="13" width="10.6640625" customWidth="1"/>
+    <col min="2" max="14" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="J3" s="32" t="s">
+      <c r="E3" s="1"/>
+      <c r="K3" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="39"/>
+      <c r="L3" s="7"/>
       <c r="M3" s="39"/>
-    </row>
-    <row r="4" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="39"/>
+    </row>
+    <row r="4" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="G4" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="I4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="J4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="K4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="L4" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="55">
+        <v>46150</v>
+      </c>
+      <c r="D5" s="35">
         <v>555</v>
       </c>
-      <c r="D5" s="35">
+      <c r="E5" s="35">
         <v>570</v>
       </c>
-      <c r="E5" s="35">
+      <c r="F5" s="35">
         <v>630</v>
       </c>
-      <c r="F5" s="35">
+      <c r="G5" s="35">
         <v>645</v>
       </c>
-      <c r="G5" s="36">
+      <c r="H5" s="36">
         <v>0.96</v>
       </c>
-      <c r="H5" s="37">
+      <c r="I5" s="37">
         <v>571</v>
       </c>
-      <c r="I5" s="36">
-        <f t="shared" ref="I5:I15" si="0">IF(AND(H5&lt;=E5,H5&gt;=D5),0,IF(H5&lt;D5,MAX(H5-D5,C5-D5),MAX(E5-H5,E5-F5)))</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="40">
+      <c r="J5" s="36">
+        <f t="shared" ref="J5:J6" si="0">IF(AND(I5&lt;=F5,I5&gt;=E5),0,IF(I5&lt;E5,MAX(I5-E5,D5-E5),MAX(F5-I5,F5-G5)))</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="40">
         <v>0.3</v>
       </c>
-      <c r="K5" s="38">
-        <f t="shared" ref="K5:K15" si="1">(G5+I5)*100-J5</f>
+      <c r="L5" s="38">
+        <f t="shared" ref="L5:L6" si="1">(H5+J5)*100-K5</f>
         <v>95.7</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="35">
-        <v>555</v>
+      <c r="C6" s="55">
+        <v>46157</v>
       </c>
       <c r="D6" s="35">
         <v>570</v>
       </c>
       <c r="E6" s="35">
-        <v>630</v>
+        <v>585</v>
       </c>
       <c r="F6" s="35">
         <v>645</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="35">
+        <v>660</v>
+      </c>
+      <c r="H6" s="36">
         <v>0.96</v>
       </c>
-      <c r="H6" s="37">
-        <v>572</v>
-      </c>
-      <c r="I6" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K6" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="35">
-        <v>555</v>
-      </c>
-      <c r="D7" s="35">
-        <v>570</v>
-      </c>
-      <c r="E7" s="35">
-        <v>630</v>
-      </c>
-      <c r="F7" s="35">
-        <v>645</v>
-      </c>
-      <c r="G7" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H7" s="37">
-        <v>573</v>
-      </c>
-      <c r="I7" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K7" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="35">
-        <v>555</v>
-      </c>
-      <c r="D8" s="35">
-        <v>570</v>
-      </c>
-      <c r="E8" s="35">
-        <v>630</v>
-      </c>
-      <c r="F8" s="35">
-        <v>645</v>
-      </c>
-      <c r="G8" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H8" s="37">
-        <v>574</v>
-      </c>
-      <c r="I8" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K8" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="35">
-        <v>555</v>
-      </c>
-      <c r="D9" s="35">
-        <v>570</v>
-      </c>
-      <c r="E9" s="35">
-        <v>630</v>
-      </c>
-      <c r="F9" s="35">
-        <v>645</v>
-      </c>
-      <c r="G9" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H9" s="37">
-        <v>545</v>
-      </c>
-      <c r="I9" s="36">
+      <c r="I6" s="37">
+        <v>540</v>
+      </c>
+      <c r="J6" s="36">
         <f t="shared" si="0"/>
         <v>-15</v>
       </c>
-      <c r="J9" s="40">
+      <c r="K6" s="40">
         <v>0.3</v>
       </c>
-      <c r="K9" s="38">
+      <c r="L6" s="38">
         <f t="shared" si="1"/>
         <v>-1404.3</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
-        <v>6</v>
-      </c>
-      <c r="C10" s="35">
-        <v>555</v>
-      </c>
-      <c r="D10" s="35">
-        <v>570</v>
-      </c>
-      <c r="E10" s="35">
-        <v>630</v>
-      </c>
-      <c r="F10" s="35">
-        <v>645</v>
-      </c>
-      <c r="G10" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H10" s="37">
-        <v>576</v>
-      </c>
-      <c r="I10" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K10" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="35">
-        <v>555</v>
-      </c>
-      <c r="D11" s="35">
-        <v>570</v>
-      </c>
-      <c r="E11" s="35">
-        <v>630</v>
-      </c>
-      <c r="F11" s="35">
-        <v>645</v>
-      </c>
-      <c r="G11" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H11" s="37">
-        <v>577</v>
-      </c>
-      <c r="I11" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K11" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="2">
-        <v>8</v>
-      </c>
-      <c r="C12" s="35">
-        <v>555</v>
-      </c>
-      <c r="D12" s="35">
-        <v>570</v>
-      </c>
-      <c r="E12" s="35">
-        <v>630</v>
-      </c>
-      <c r="F12" s="35">
-        <v>645</v>
-      </c>
-      <c r="G12" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H12" s="37">
-        <v>578</v>
-      </c>
-      <c r="I12" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K12" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
-        <v>9</v>
-      </c>
-      <c r="C13" s="35">
-        <v>555</v>
-      </c>
-      <c r="D13" s="35">
-        <v>570</v>
-      </c>
-      <c r="E13" s="35">
-        <v>630</v>
-      </c>
-      <c r="F13" s="35">
-        <v>645</v>
-      </c>
-      <c r="G13" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H13" s="37">
-        <v>579</v>
-      </c>
-      <c r="I13" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K13" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2">
-        <v>10</v>
-      </c>
-      <c r="C14" s="35">
-        <v>555</v>
-      </c>
-      <c r="D14" s="35">
-        <v>570</v>
-      </c>
-      <c r="E14" s="35">
-        <v>630</v>
-      </c>
-      <c r="F14" s="35">
-        <v>645</v>
-      </c>
-      <c r="G14" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H14" s="37">
-        <v>580</v>
-      </c>
-      <c r="I14" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K14" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
-        <v>11</v>
-      </c>
-      <c r="C15" s="35">
-        <v>555</v>
-      </c>
-      <c r="D15" s="35">
-        <v>570</v>
-      </c>
-      <c r="E15" s="35">
-        <v>630</v>
-      </c>
-      <c r="F15" s="35">
-        <v>645</v>
-      </c>
-      <c r="G15" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="H15" s="37">
-        <v>581</v>
-      </c>
-      <c r="I15" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="K15" s="38">
-        <f t="shared" si="1"/>
-        <v>95.7</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K5:K112">
+  <conditionalFormatting sqref="L5:L103">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K1048576">
+  <conditionalFormatting sqref="L5:L1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97891604-C409-0C4F-8CF7-AF51834B5808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF7C05D-1333-FC40-9FA5-BDC390A97E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="4000" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -528,7 +528,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -726,8 +726,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1796,30 +1799,31 @@
         <v>36</v>
       </c>
       <c r="D23" s="5">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="E23" s="42">
         <f t="shared" si="5"/>
-        <v>0.64102564102564097</v>
+        <v>0.62893081761006286</v>
       </c>
       <c r="F23" s="56">
         <f t="shared" si="6"/>
-        <v>0.44102564102564096</v>
+        <v>0.42893081761006285</v>
       </c>
       <c r="G23" s="49">
-        <f t="shared" ref="G23:G30" si="10">1/F23</f>
-        <v>2.2674418604651168</v>
-      </c>
-      <c r="H23" s="69">
-        <v>0</v>
-      </c>
-      <c r="I23" s="61"/>
+        <v>2.34</v>
+      </c>
+      <c r="H23" s="52">
+        <v>0</v>
+      </c>
+      <c r="I23" s="69" t="s">
+        <v>7</v>
+      </c>
       <c r="J23" s="26">
-        <f t="shared" ref="J23:J30" si="11">IF(H23=0,0,IF(I23="WON",(G23-1)*0.95,-1))</f>
+        <f t="shared" ref="J23:J30" si="10">IF(H23=0,0,IF(I23="WON",(G23-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K23" s="27">
-        <f t="shared" ref="K23:K30" si="12">J23*J$3</f>
+        <f t="shared" ref="K23:K30" si="11">J23*J$3</f>
         <v>0</v>
       </c>
     </row>
@@ -1831,30 +1835,32 @@
         <v>19</v>
       </c>
       <c r="D24" s="5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="E24" s="42">
         <f t="shared" si="5"/>
-        <v>0.75187969924812026</v>
+        <v>0.76923076923076916</v>
       </c>
       <c r="F24" s="56">
         <f t="shared" si="6"/>
-        <v>0.5518796992481203</v>
+        <v>0.56923076923076921</v>
       </c>
       <c r="G24" s="49">
+        <f t="shared" ref="G24:G30" si="12">1/F24</f>
+        <v>1.7567567567567568</v>
+      </c>
+      <c r="H24" s="52">
+        <v>0</v>
+      </c>
+      <c r="I24" s="69" t="s">
+        <v>7</v>
+      </c>
+      <c r="J24" s="26">
         <f t="shared" si="10"/>
-        <v>1.8119891008174387</v>
-      </c>
-      <c r="H24" s="52">
-        <v>0</v>
-      </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="26">
+        <v>0</v>
+      </c>
+      <c r="K24" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="27">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1866,28 +1872,33 @@
         <v>20</v>
       </c>
       <c r="D25" s="5">
-        <v>1.1000000000000001</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E25" s="42">
         <f t="shared" si="5"/>
-        <v>0.90909090909090906</v>
+        <v>0.89285714285714279</v>
       </c>
       <c r="F25" s="56">
         <f t="shared" si="6"/>
-        <v>0.70909090909090899</v>
+        <v>0.69285714285714284</v>
       </c>
       <c r="G25" s="49">
-        <f t="shared" si="10"/>
-        <v>1.4102564102564104</v>
-      </c>
-      <c r="I25" s="61"/>
+        <f t="shared" si="12"/>
+        <v>1.4432989690721649</v>
+      </c>
+      <c r="H25" s="52">
+        <v>1</v>
+      </c>
+      <c r="I25" s="69" t="s">
+        <v>7</v>
+      </c>
       <c r="J25" s="26">
+        <f>IF(H25=0,0,IF(I25="WON",(G25-1)*0.94,-1))</f>
+        <v>0.416701030927835</v>
+      </c>
+      <c r="K25" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>23.147742268041235</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
@@ -1898,27 +1909,31 @@
         <v>22</v>
       </c>
       <c r="D26" s="5">
-        <v>1.1100000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E26" s="42">
         <f t="shared" si="5"/>
-        <v>0.9009009009009008</v>
+        <v>0.86956521739130443</v>
       </c>
       <c r="F26" s="56">
         <f t="shared" si="6"/>
-        <v>0.70090090090090085</v>
+        <v>0.66956521739130448</v>
       </c>
       <c r="G26" s="49">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="52">
+        <v>0</v>
+      </c>
+      <c r="I26" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="J26" s="26">
         <f t="shared" si="10"/>
-        <v>1.4267352185089976</v>
-      </c>
-      <c r="I26" s="61"/>
-      <c r="J26" s="26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="27">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1930,28 +1945,33 @@
         <v>34</v>
       </c>
       <c r="D27" s="5">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="E27" s="42">
         <f t="shared" si="5"/>
-        <v>0.64935064935064934</v>
+        <v>0.58139534883720934</v>
       </c>
       <c r="F27" s="56">
         <f t="shared" si="6"/>
-        <v>0.44935064935064933</v>
+        <v>0.38139534883720932</v>
       </c>
       <c r="G27" s="49">
-        <f t="shared" si="10"/>
-        <v>2.2254335260115607</v>
-      </c>
-      <c r="I27" s="61"/>
+        <f t="shared" si="12"/>
+        <v>2.6219512195121948</v>
+      </c>
+      <c r="H27" s="52">
+        <v>1</v>
+      </c>
+      <c r="I27" s="70" t="s">
+        <v>7</v>
+      </c>
       <c r="J27" s="26">
+        <f>IF(H27=0,0,IF(I27="WON",(G27-1)*0.94,-1))</f>
+        <v>1.524634146341463</v>
+      </c>
+      <c r="K27" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>84.693426829268262</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
@@ -1973,16 +1993,16 @@
         <v>0.56923076923076921</v>
       </c>
       <c r="G28" s="49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1.7567567567567568</v>
       </c>
       <c r="I28" s="61"/>
       <c r="J28" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="27">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -2005,16 +2025,16 @@
         <v>0.5352941176470587</v>
       </c>
       <c r="G29" s="49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1.8681318681318686</v>
       </c>
       <c r="I29" s="61"/>
       <c r="J29" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="27">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -2037,17 +2057,17 @@
         <v>0.70090090090090085</v>
       </c>
       <c r="G30" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1.4267352185089976</v>
       </c>
       <c r="H30" s="63"/>
       <c r="I30" s="64"/>
       <c r="J30" s="28">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="29">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="29">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF7C05D-1333-FC40-9FA5-BDC390A97E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426F07CE-5B8D-5045-ABCA-50498993CD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4000" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-36480" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Kangaroos</t>
+  </si>
+  <si>
+    <t>GWS</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -708,12 +711,9 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -730,6 +730,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1072,7 +1105,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K30"/>
+  <dimension ref="B2:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1433,11 +1466,11 @@
         <v>1.2</v>
       </c>
       <c r="E13" s="41">
-        <f t="shared" ref="E13:E30" si="5">1/D13</f>
+        <f t="shared" ref="E13:E39" si="5">1/D13</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F13" s="21">
-        <f t="shared" ref="F13:F30" si="6">E13-0.2</f>
+        <f t="shared" ref="F13:F39" si="6">E13-0.2</f>
         <v>0.6333333333333333</v>
       </c>
       <c r="G13" s="59">
@@ -1758,7 +1791,7 @@
       <c r="B22" s="46">
         <v>18</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="63" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="58">
@@ -1779,7 +1812,7 @@
       <c r="H22" s="23">
         <v>1</v>
       </c>
-      <c r="I22" s="65" t="s">
+      <c r="I22" s="62" t="s">
         <v>7</v>
       </c>
       <c r="J22" s="24">
@@ -1795,7 +1828,7 @@
       <c r="B23" s="47">
         <v>19</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="64" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="5">
@@ -1815,7 +1848,7 @@
       <c r="H23" s="52">
         <v>0</v>
       </c>
-      <c r="I23" s="69" t="s">
+      <c r="I23" s="66" t="s">
         <v>7</v>
       </c>
       <c r="J23" s="26">
@@ -1831,7 +1864,7 @@
       <c r="B24" s="47">
         <v>20</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="5">
@@ -1846,13 +1879,13 @@
         <v>0.56923076923076921</v>
       </c>
       <c r="G24" s="49">
-        <f t="shared" ref="G24:G30" si="12">1/F24</f>
+        <f t="shared" ref="G24:G28" si="12">1/F24</f>
         <v>1.7567567567567568</v>
       </c>
       <c r="H24" s="52">
         <v>0</v>
       </c>
-      <c r="I24" s="69" t="s">
+      <c r="I24" s="66" t="s">
         <v>7</v>
       </c>
       <c r="J24" s="26">
@@ -1868,7 +1901,7 @@
       <c r="B25" s="47">
         <v>21</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="64" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="5">
@@ -1889,7 +1922,7 @@
       <c r="H25" s="52">
         <v>1</v>
       </c>
-      <c r="I25" s="69" t="s">
+      <c r="I25" s="66" t="s">
         <v>7</v>
       </c>
       <c r="J25" s="26">
@@ -1905,7 +1938,7 @@
       <c r="B26" s="47">
         <v>22</v>
       </c>
-      <c r="C26" s="67" t="s">
+      <c r="C26" s="64" t="s">
         <v>22</v>
       </c>
       <c r="D26" s="5">
@@ -1925,7 +1958,7 @@
       <c r="H26" s="52">
         <v>0</v>
       </c>
-      <c r="I26" s="70" t="s">
+      <c r="I26" s="67" t="s">
         <v>7</v>
       </c>
       <c r="J26" s="26">
@@ -1941,7 +1974,7 @@
       <c r="B27" s="47">
         <v>23</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="64" t="s">
         <v>34</v>
       </c>
       <c r="D27" s="5">
@@ -1962,7 +1995,7 @@
       <c r="H27" s="52">
         <v>1</v>
       </c>
-      <c r="I27" s="70" t="s">
+      <c r="I27" s="67" t="s">
         <v>7</v>
       </c>
       <c r="J27" s="26">
@@ -1978,7 +2011,7 @@
       <c r="B28" s="47">
         <v>24</v>
       </c>
-      <c r="C28" s="67" t="s">
+      <c r="C28" s="64" t="s">
         <v>50</v>
       </c>
       <c r="D28" s="5">
@@ -1996,7 +2029,12 @@
         <f t="shared" si="12"/>
         <v>1.7567567567567568</v>
       </c>
-      <c r="I28" s="61"/>
+      <c r="H28" s="52">
+        <v>0</v>
+      </c>
+      <c r="I28" s="66" t="s">
+        <v>7</v>
+      </c>
       <c r="J28" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
@@ -2010,7 +2048,7 @@
       <c r="B29" s="47">
         <v>25</v>
       </c>
-      <c r="C29" s="67" t="s">
+      <c r="C29" s="64" t="s">
         <v>18</v>
       </c>
       <c r="D29" s="5">
@@ -2025,24 +2063,28 @@
         <v>0.5352941176470587</v>
       </c>
       <c r="G29" s="49">
-        <f t="shared" si="12"/>
-        <v>1.8681318681318686</v>
-      </c>
-      <c r="I29" s="61"/>
+        <v>1.88</v>
+      </c>
+      <c r="H29" s="52">
+        <v>1</v>
+      </c>
+      <c r="I29" s="66" t="s">
+        <v>11</v>
+      </c>
       <c r="J29" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K29" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="30" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="48">
+      <c r="B30" s="47">
         <v>26</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="65" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="11">
@@ -2052,22 +2094,325 @@
         <f t="shared" si="5"/>
         <v>0.9009009009009008</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="61">
         <f t="shared" si="6"/>
         <v>0.70090090090090085</v>
       </c>
       <c r="G30" s="50">
-        <f t="shared" si="12"/>
-        <v>1.4267352185089976</v>
-      </c>
-      <c r="H30" s="63"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="28">
+        <v>1.44</v>
+      </c>
+      <c r="H30" s="68">
+        <v>0</v>
+      </c>
+      <c r="I30" s="69" t="s">
+        <v>7</v>
+      </c>
+      <c r="J30" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="27">
         <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B31" s="70">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1.35</v>
+      </c>
+      <c r="E31" s="42">
+        <f t="shared" si="5"/>
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="F31" s="56">
+        <f t="shared" si="6"/>
+        <v>0.54074074074074074</v>
+      </c>
+      <c r="G31" s="73">
+        <f>1/F31</f>
+        <v>1.8493150684931507</v>
+      </c>
+      <c r="H31" s="76">
+        <v>1</v>
+      </c>
+      <c r="I31" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="J31" s="24">
+        <f>IF(H31=0,0,IF(I31="WON",(G31-1)*0.94,-1))</f>
+        <v>0.79835616438356161</v>
+      </c>
+      <c r="K31" s="25">
+        <f t="shared" ref="K31:K39" si="13">J31*J$3</f>
+        <v>44.348684931506845</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="71">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E32" s="42">
+        <f t="shared" si="5"/>
+        <v>0.86956521739130443</v>
+      </c>
+      <c r="F32" s="56">
+        <f t="shared" si="6"/>
+        <v>0.66956521739130448</v>
+      </c>
+      <c r="G32" s="74">
+        <f t="shared" ref="G32:G39" si="14">1/F32</f>
+        <v>1.4935064935064932</v>
+      </c>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="26">
+        <f t="shared" ref="J31:J39" si="15">IF(H32=0,0,IF(I32="WON",(G32-1)*0.95,-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B33" s="71">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="E33" s="42">
+        <f t="shared" si="5"/>
+        <v>0.5988023952095809</v>
+      </c>
+      <c r="F33" s="56">
+        <f t="shared" si="6"/>
+        <v>0.39880239520958088</v>
+      </c>
+      <c r="G33" s="74">
+        <v>2.52</v>
+      </c>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="26">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="71">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1.42</v>
+      </c>
+      <c r="E34" s="42">
+        <f t="shared" si="5"/>
+        <v>0.70422535211267612</v>
+      </c>
+      <c r="F34" s="56">
+        <f t="shared" si="6"/>
+        <v>0.50422535211267605</v>
+      </c>
+      <c r="G34" s="74">
+        <f t="shared" si="14"/>
+        <v>1.9832402234636872</v>
+      </c>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="26">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="71">
+        <v>31</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="E35" s="42">
+        <f t="shared" si="5"/>
+        <v>0.78740157480314954</v>
+      </c>
+      <c r="F35" s="56">
+        <f t="shared" si="6"/>
+        <v>0.58740157480314958</v>
+      </c>
+      <c r="G35" s="74">
+        <f t="shared" si="14"/>
+        <v>1.7024128686327078</v>
+      </c>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="26">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B36" s="71">
+        <v>32</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E36" s="42">
+        <f t="shared" si="5"/>
+        <v>0.86956521739130443</v>
+      </c>
+      <c r="F36" s="56">
+        <f t="shared" si="6"/>
+        <v>0.66956521739130448</v>
+      </c>
+      <c r="G36" s="74">
+        <f t="shared" si="14"/>
+        <v>1.4935064935064932</v>
+      </c>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="26">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B37" s="71">
+        <v>33</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="E37" s="42">
+        <f t="shared" si="5"/>
+        <v>0.88495575221238942</v>
+      </c>
+      <c r="F37" s="56">
+        <f t="shared" si="6"/>
+        <v>0.68495575221238947</v>
+      </c>
+      <c r="G37" s="74">
+        <f t="shared" si="14"/>
+        <v>1.4599483204134365</v>
+      </c>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="26">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B38" s="71">
+        <v>34</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="5">
+        <v>1.37</v>
+      </c>
+      <c r="E38" s="42">
+        <f t="shared" si="5"/>
+        <v>0.72992700729927007</v>
+      </c>
+      <c r="F38" s="56">
+        <f t="shared" si="6"/>
+        <v>0.52992700729927011</v>
+      </c>
+      <c r="G38" s="74">
+        <f t="shared" si="14"/>
+        <v>1.887052341597796</v>
+      </c>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="26">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="72">
+        <v>35</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="E39" s="42">
+        <f t="shared" si="5"/>
+        <v>0.65789473684210531</v>
+      </c>
+      <c r="F39" s="56">
+        <f t="shared" si="6"/>
+        <v>0.4578947368421053</v>
+      </c>
+      <c r="G39" s="75">
+        <f t="shared" si="14"/>
+        <v>2.1839080459770113</v>
+      </c>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="28">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="29">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426F07CE-5B8D-5045-ABCA-50498993CD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B213F894-F96C-044E-8434-A45E405F3E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36480" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -531,7 +531,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -723,21 +723,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -759,11 +744,20 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1848,7 +1842,7 @@
       <c r="H23" s="52">
         <v>0</v>
       </c>
-      <c r="I23" s="66" t="s">
+      <c r="I23" s="74" t="s">
         <v>7</v>
       </c>
       <c r="J23" s="26">
@@ -1885,7 +1879,7 @@
       <c r="H24" s="52">
         <v>0</v>
       </c>
-      <c r="I24" s="66" t="s">
+      <c r="I24" s="74" t="s">
         <v>7</v>
       </c>
       <c r="J24" s="26">
@@ -1922,7 +1916,7 @@
       <c r="H25" s="52">
         <v>1</v>
       </c>
-      <c r="I25" s="66" t="s">
+      <c r="I25" s="74" t="s">
         <v>7</v>
       </c>
       <c r="J25" s="26">
@@ -1958,7 +1952,7 @@
       <c r="H26" s="52">
         <v>0</v>
       </c>
-      <c r="I26" s="67" t="s">
+      <c r="I26" s="75" t="s">
         <v>7</v>
       </c>
       <c r="J26" s="26">
@@ -1995,7 +1989,7 @@
       <c r="H27" s="52">
         <v>1</v>
       </c>
-      <c r="I27" s="67" t="s">
+      <c r="I27" s="75" t="s">
         <v>7</v>
       </c>
       <c r="J27" s="26">
@@ -2032,7 +2026,7 @@
       <c r="H28" s="52">
         <v>0</v>
       </c>
-      <c r="I28" s="66" t="s">
+      <c r="I28" s="74" t="s">
         <v>7</v>
       </c>
       <c r="J28" s="26">
@@ -2068,7 +2062,7 @@
       <c r="H29" s="52">
         <v>1</v>
       </c>
-      <c r="I29" s="66" t="s">
+      <c r="I29" s="74" t="s">
         <v>11</v>
       </c>
       <c r="J29" s="26">
@@ -2084,7 +2078,7 @@
       <c r="B30" s="47">
         <v>26</v>
       </c>
-      <c r="C30" s="65" t="s">
+      <c r="C30" s="64" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="11">
@@ -2101,10 +2095,10 @@
       <c r="G30" s="50">
         <v>1.44</v>
       </c>
-      <c r="H30" s="68">
-        <v>0</v>
-      </c>
-      <c r="I30" s="69" t="s">
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="76" t="s">
         <v>7</v>
       </c>
       <c r="J30" s="26">
@@ -2117,31 +2111,31 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B31" s="70">
+      <c r="B31" s="57">
         <v>27</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="23">
         <v>1.35</v>
       </c>
-      <c r="E31" s="42">
+      <c r="E31" s="41">
         <f t="shared" si="5"/>
         <v>0.7407407407407407</v>
       </c>
-      <c r="F31" s="56">
+      <c r="F31" s="60">
         <f t="shared" si="6"/>
         <v>0.54074074074074074</v>
       </c>
-      <c r="G31" s="73">
+      <c r="G31" s="68">
         <f>1/F31</f>
         <v>1.8493150684931507</v>
       </c>
-      <c r="H31" s="76">
+      <c r="H31" s="71">
         <v>1</v>
       </c>
-      <c r="I31" s="76" t="s">
+      <c r="I31" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J31" s="24">
@@ -2154,13 +2148,13 @@
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="71">
+      <c r="B32" s="44">
         <v>28</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="52">
         <v>1.1499999999999999</v>
       </c>
       <c r="E32" s="42">
@@ -2171,14 +2165,18 @@
         <f t="shared" si="6"/>
         <v>0.66956521739130448</v>
       </c>
-      <c r="G32" s="74">
+      <c r="G32" s="69">
         <f t="shared" ref="G32:G39" si="14">1/F32</f>
         <v>1.4935064935064932</v>
       </c>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
+      <c r="H32" s="73">
+        <v>0</v>
+      </c>
+      <c r="I32" s="73" t="s">
+        <v>7</v>
+      </c>
       <c r="J32" s="26">
-        <f t="shared" ref="J31:J39" si="15">IF(H32=0,0,IF(I32="WON",(G32-1)*0.95,-1))</f>
+        <f t="shared" ref="J32:J39" si="15">IF(H32=0,0,IF(I32="WON",(G32-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K32" s="27">
@@ -2187,13 +2185,13 @@
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="71">
+      <c r="B33" s="44">
         <v>29</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="52">
         <v>1.67</v>
       </c>
       <c r="E33" s="42">
@@ -2204,11 +2202,15 @@
         <f t="shared" si="6"/>
         <v>0.39880239520958088</v>
       </c>
-      <c r="G33" s="74">
+      <c r="G33" s="69">
         <v>2.52</v>
       </c>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
+      <c r="H33" s="73">
+        <v>0</v>
+      </c>
+      <c r="I33" s="73" t="s">
+        <v>7</v>
+      </c>
       <c r="J33" s="26">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -2219,13 +2221,13 @@
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B34" s="71">
+      <c r="B34" s="44">
         <v>30</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="52">
         <v>1.42</v>
       </c>
       <c r="E34" s="42">
@@ -2236,12 +2238,16 @@
         <f t="shared" si="6"/>
         <v>0.50422535211267605</v>
       </c>
-      <c r="G34" s="74">
+      <c r="G34" s="69">
         <f t="shared" si="14"/>
         <v>1.9832402234636872</v>
       </c>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
+      <c r="H34" s="73">
+        <v>0</v>
+      </c>
+      <c r="I34" s="73" t="s">
+        <v>7</v>
+      </c>
       <c r="J34" s="26">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -2252,13 +2258,13 @@
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B35" s="71">
+      <c r="B35" s="44">
         <v>31</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="52">
         <v>1.27</v>
       </c>
       <c r="E35" s="42">
@@ -2269,45 +2275,53 @@
         <f t="shared" si="6"/>
         <v>0.58740157480314958</v>
       </c>
-      <c r="G35" s="74">
+      <c r="G35" s="69">
         <f t="shared" si="14"/>
         <v>1.7024128686327078</v>
       </c>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
+      <c r="H35" s="73">
+        <v>1</v>
+      </c>
+      <c r="I35" s="73" t="s">
+        <v>11</v>
+      </c>
       <c r="J35" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K35" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="71">
+      <c r="B36" s="44">
         <v>32</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="5">
-        <v>1.1499999999999999</v>
+      <c r="D36" s="52">
+        <v>1.1299999999999999</v>
       </c>
       <c r="E36" s="42">
         <f t="shared" si="5"/>
-        <v>0.86956521739130443</v>
+        <v>0.88495575221238942</v>
       </c>
       <c r="F36" s="56">
         <f t="shared" si="6"/>
-        <v>0.66956521739130448</v>
-      </c>
-      <c r="G36" s="74">
+        <v>0.68495575221238947</v>
+      </c>
+      <c r="G36" s="69">
         <f t="shared" si="14"/>
-        <v>1.4935064935064932</v>
-      </c>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
+        <v>1.4599483204134365</v>
+      </c>
+      <c r="H36" s="73">
+        <v>0</v>
+      </c>
+      <c r="I36" s="73" t="s">
+        <v>7</v>
+      </c>
       <c r="J36" s="26">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -2318,13 +2332,13 @@
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B37" s="71">
+      <c r="B37" s="44">
         <v>33</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="52">
         <v>1.1299999999999999</v>
       </c>
       <c r="E37" s="42">
@@ -2335,12 +2349,16 @@
         <f t="shared" si="6"/>
         <v>0.68495575221238947</v>
       </c>
-      <c r="G37" s="74">
+      <c r="G37" s="69">
         <f t="shared" si="14"/>
         <v>1.4599483204134365</v>
       </c>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
+      <c r="H37" s="73">
+        <v>0</v>
+      </c>
+      <c r="I37" s="73" t="s">
+        <v>7</v>
+      </c>
       <c r="J37" s="26">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -2351,13 +2369,13 @@
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B38" s="71">
+      <c r="B38" s="44">
         <v>34</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="52">
         <v>1.37</v>
       </c>
       <c r="E38" s="42">
@@ -2368,12 +2386,16 @@
         <f t="shared" si="6"/>
         <v>0.52992700729927011</v>
       </c>
-      <c r="G38" s="74">
+      <c r="G38" s="69">
         <f t="shared" si="14"/>
         <v>1.887052341597796</v>
       </c>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
+      <c r="H38" s="73">
+        <v>0</v>
+      </c>
+      <c r="I38" s="73" t="s">
+        <v>7</v>
+      </c>
       <c r="J38" s="26">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -2384,36 +2406,40 @@
       </c>
     </row>
     <row r="39" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="72">
+      <c r="B39" s="45">
         <v>35</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="9">
         <v>1.52</v>
       </c>
-      <c r="E39" s="42">
+      <c r="E39" s="43">
         <f t="shared" si="5"/>
         <v>0.65789473684210531</v>
       </c>
-      <c r="F39" s="56">
+      <c r="F39" s="61">
         <f t="shared" si="6"/>
         <v>0.4578947368421053</v>
       </c>
-      <c r="G39" s="75">
+      <c r="G39" s="70">
         <f t="shared" si="14"/>
         <v>2.1839080459770113</v>
       </c>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
+      <c r="H39" s="72">
+        <v>1</v>
+      </c>
+      <c r="I39" s="72" t="s">
+        <v>7</v>
+      </c>
       <c r="J39" s="28">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>IF(H39=0,0,IF(I39="WON",(G39-1)*0.94,-1))</f>
+        <v>1.1128735632183906</v>
       </c>
       <c r="K39" s="29">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>61.820126436781592</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B213F894-F96C-044E-8434-A45E405F3E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8ED8E3-EEED-C245-86E3-D18F436AB236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36480" yWindow="500" windowWidth="34400" windowHeight="19000" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>GWS</t>
+  </si>
+  <si>
+    <t>DRAW</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1102,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K39"/>
+  <dimension ref="B2:K47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1460,11 +1463,11 @@
         <v>1.2</v>
       </c>
       <c r="E13" s="41">
-        <f t="shared" ref="E13:E39" si="5">1/D13</f>
+        <f t="shared" ref="E13:E47" si="5">1/D13</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F13" s="21">
-        <f t="shared" ref="F13:F39" si="6">E13-0.2</f>
+        <f t="shared" ref="F13:F47" si="6">E13-0.2</f>
         <v>0.6333333333333333</v>
       </c>
       <c r="G13" s="59">
@@ -2143,8 +2146,7 @@
         <v>0.79835616438356161</v>
       </c>
       <c r="K31" s="25">
-        <f t="shared" ref="K31:K39" si="13">J31*J$3</f>
-        <v>44.348684931506845</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
@@ -2166,7 +2168,7 @@
         <v>0.66956521739130448</v>
       </c>
       <c r="G32" s="69">
-        <f t="shared" ref="G32:G39" si="14">1/F32</f>
+        <f t="shared" ref="G32:G47" si="13">1/F32</f>
         <v>1.4935064935064932</v>
       </c>
       <c r="H32" s="73">
@@ -2176,11 +2178,11 @@
         <v>7</v>
       </c>
       <c r="J32" s="26">
-        <f t="shared" ref="J32:J39" si="15">IF(H32=0,0,IF(I32="WON",(G32-1)*0.95,-1))</f>
+        <f t="shared" ref="J32:J38" si="14">IF(H32=0,0,IF(I32="WON",(G32-1)*0.95,-1))</f>
         <v>0</v>
       </c>
       <c r="K32" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="K31:K45" si="15">J32*J$3</f>
         <v>0</v>
       </c>
     </row>
@@ -2212,11 +2214,11 @@
         <v>7</v>
       </c>
       <c r="J33" s="26">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="27">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2239,21 +2241,21 @@
         <v>0.50422535211267605</v>
       </c>
       <c r="G34" s="69">
+        <f t="shared" si="13"/>
+        <v>1.9832402234636872</v>
+      </c>
+      <c r="H34" s="73">
+        <v>0</v>
+      </c>
+      <c r="I34" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J34" s="26">
         <f t="shared" si="14"/>
-        <v>1.9832402234636872</v>
-      </c>
-      <c r="H34" s="73">
-        <v>0</v>
-      </c>
-      <c r="I34" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="J34" s="26">
+        <v>0</v>
+      </c>
+      <c r="K34" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="27">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2276,7 +2278,7 @@
         <v>0.58740157480314958</v>
       </c>
       <c r="G35" s="69">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.7024128686327078</v>
       </c>
       <c r="H35" s="73">
@@ -2286,11 +2288,11 @@
         <v>11</v>
       </c>
       <c r="J35" s="26">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="K35" s="27">
         <f t="shared" si="15"/>
-        <v>-1</v>
-      </c>
-      <c r="K35" s="27">
-        <f t="shared" si="13"/>
         <v>-55.55</v>
       </c>
     </row>
@@ -2313,21 +2315,21 @@
         <v>0.68495575221238947</v>
       </c>
       <c r="G36" s="69">
+        <f t="shared" si="13"/>
+        <v>1.4599483204134365</v>
+      </c>
+      <c r="H36" s="73">
+        <v>0</v>
+      </c>
+      <c r="I36" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J36" s="26">
         <f t="shared" si="14"/>
-        <v>1.4599483204134365</v>
-      </c>
-      <c r="H36" s="73">
-        <v>0</v>
-      </c>
-      <c r="I36" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="J36" s="26">
+        <v>0</v>
+      </c>
+      <c r="K36" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="27">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2350,21 +2352,21 @@
         <v>0.68495575221238947</v>
       </c>
       <c r="G37" s="69">
+        <f t="shared" si="13"/>
+        <v>1.4599483204134365</v>
+      </c>
+      <c r="H37" s="73">
+        <v>0</v>
+      </c>
+      <c r="I37" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J37" s="26">
         <f t="shared" si="14"/>
-        <v>1.4599483204134365</v>
-      </c>
-      <c r="H37" s="73">
-        <v>0</v>
-      </c>
-      <c r="I37" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="J37" s="26">
+        <v>0</v>
+      </c>
+      <c r="K37" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="27">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2387,26 +2389,26 @@
         <v>0.52992700729927011</v>
       </c>
       <c r="G38" s="69">
+        <f t="shared" si="13"/>
+        <v>1.887052341597796</v>
+      </c>
+      <c r="H38" s="73">
+        <v>0</v>
+      </c>
+      <c r="I38" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J38" s="26">
         <f t="shared" si="14"/>
-        <v>1.887052341597796</v>
-      </c>
-      <c r="H38" s="73">
-        <v>0</v>
-      </c>
-      <c r="I38" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="J38" s="26">
+        <v>0</v>
+      </c>
+      <c r="K38" s="27">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K38" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="39" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="45">
+      <c r="B39" s="44">
         <v>35</v>
       </c>
       <c r="C39" s="67" t="s">
@@ -2424,8 +2426,7 @@
         <v>0.4578947368421053</v>
       </c>
       <c r="G39" s="70">
-        <f t="shared" si="14"/>
-        <v>2.1839080459770113</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="H39" s="72">
         <v>1</v>
@@ -2435,11 +2436,304 @@
       </c>
       <c r="J39" s="28">
         <f>IF(H39=0,0,IF(I39="WON",(G39-1)*0.94,-1))</f>
-        <v>1.1128735632183906</v>
+        <v>1.1468</v>
       </c>
       <c r="K39" s="29">
+        <v>65.739999999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="46">
+        <v>36</v>
+      </c>
+      <c r="C40" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="52">
+        <v>1.28</v>
+      </c>
+      <c r="E40" s="42">
+        <f t="shared" si="5"/>
+        <v>0.78125</v>
+      </c>
+      <c r="F40" s="56">
+        <f t="shared" si="6"/>
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="G40" s="69">
         <f t="shared" si="13"/>
-        <v>61.820126436781592</v>
+        <v>1.7204301075268815</v>
+      </c>
+      <c r="H40" s="73">
+        <v>1</v>
+      </c>
+      <c r="I40" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="28">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="K40" s="27">
+        <f t="shared" si="15"/>
+        <v>-7.7770000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="47">
+        <v>37</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="52">
+        <v>1.54</v>
+      </c>
+      <c r="E41" s="42">
+        <f t="shared" si="5"/>
+        <v>0.64935064935064934</v>
+      </c>
+      <c r="F41" s="56">
+        <f t="shared" si="6"/>
+        <v>0.44935064935064933</v>
+      </c>
+      <c r="G41" s="69">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="H41" s="73">
+        <v>1</v>
+      </c>
+      <c r="I41" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="28">
+        <f t="shared" ref="J40:J47" si="16">IF(H41=0,0,IF(I41="WON",(G41-1)*0.94,-1))</f>
+        <v>1.1656000000000002</v>
+      </c>
+      <c r="K41" s="27">
+        <f t="shared" si="15"/>
+        <v>64.749080000000006</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="47">
+        <v>38</v>
+      </c>
+      <c r="C42" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="52">
+        <v>1.7</v>
+      </c>
+      <c r="E42" s="42">
+        <f t="shared" si="5"/>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="F42" s="56">
+        <f t="shared" si="6"/>
+        <v>0.38823529411764707</v>
+      </c>
+      <c r="G42" s="69">
+        <f t="shared" si="13"/>
+        <v>2.5757575757575757</v>
+      </c>
+      <c r="H42" s="73">
+        <v>1</v>
+      </c>
+      <c r="I42" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J42" s="28">
+        <f t="shared" si="16"/>
+        <v>1.481212121212121</v>
+      </c>
+      <c r="K42" s="27">
+        <f>J42*J$3+0.22</f>
+        <v>82.501333333333321</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B43" s="47">
+        <v>39</v>
+      </c>
+      <c r="C43" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="52">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E43" s="42">
+        <f t="shared" si="5"/>
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="F43" s="56">
+        <f t="shared" si="6"/>
+        <v>0.71743119266055033</v>
+      </c>
+      <c r="G43" s="69">
+        <f t="shared" si="13"/>
+        <v>1.3938618925831205</v>
+      </c>
+      <c r="H43" s="73">
+        <v>0</v>
+      </c>
+      <c r="I43" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J43" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B44" s="47">
+        <v>40</v>
+      </c>
+      <c r="C44" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44" s="52">
+        <v>1.28</v>
+      </c>
+      <c r="E44" s="42">
+        <f t="shared" si="5"/>
+        <v>0.78125</v>
+      </c>
+      <c r="F44" s="56">
+        <f t="shared" si="6"/>
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="G44" s="69">
+        <f t="shared" si="13"/>
+        <v>1.7204301075268815</v>
+      </c>
+      <c r="H44" s="73">
+        <v>1</v>
+      </c>
+      <c r="I44" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J44" s="26">
+        <f t="shared" si="16"/>
+        <v>0.67720430107526863</v>
+      </c>
+      <c r="K44" s="27">
+        <f>J44*J$3-0.02</f>
+        <v>37.598698924731167</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B45" s="47">
+        <v>41</v>
+      </c>
+      <c r="C45" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="52">
+        <v>1.64</v>
+      </c>
+      <c r="E45" s="42">
+        <f t="shared" si="5"/>
+        <v>0.6097560975609756</v>
+      </c>
+      <c r="F45" s="56">
+        <f t="shared" si="6"/>
+        <v>0.40975609756097559</v>
+      </c>
+      <c r="G45" s="69">
+        <f t="shared" si="13"/>
+        <v>2.4404761904761907</v>
+      </c>
+      <c r="H45" s="73">
+        <v>1</v>
+      </c>
+      <c r="I45" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J45" s="26">
+        <f t="shared" si="16"/>
+        <v>1.3540476190476192</v>
+      </c>
+      <c r="K45" s="27">
+        <f>J45*J$3-0.03</f>
+        <v>75.187345238095233</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B46" s="47">
+        <v>42</v>
+      </c>
+      <c r="C46" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="52">
+        <v>1.2</v>
+      </c>
+      <c r="E46" s="42">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F46" s="56">
+        <f t="shared" si="6"/>
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="G46" s="69">
+        <f t="shared" si="13"/>
+        <v>1.5789473684210527</v>
+      </c>
+      <c r="H46" s="73">
+        <v>0</v>
+      </c>
+      <c r="I46" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J46" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="27">
+        <f>J46*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="48">
+        <v>43</v>
+      </c>
+      <c r="C47" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="52">
+        <v>1.61</v>
+      </c>
+      <c r="E47" s="42">
+        <f t="shared" si="5"/>
+        <v>0.6211180124223602</v>
+      </c>
+      <c r="F47" s="56">
+        <f t="shared" si="6"/>
+        <v>0.42111801242236019</v>
+      </c>
+      <c r="G47" s="69">
+        <f t="shared" si="13"/>
+        <v>2.3746312684365787</v>
+      </c>
+      <c r="H47" s="73">
+        <v>0</v>
+      </c>
+      <c r="I47" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J47" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="27">
+        <f>J47*J$3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8ED8E3-EEED-C245-86E3-D18F436AB236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8306D4-608B-0649-A6CB-F04E56C7DF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>DRAW</t>
+  </si>
+  <si>
+    <t>Tigers</t>
   </si>
 </sst>
 </file>
@@ -534,7 +537,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -760,6 +763,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1102,7 +1123,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K47"/>
+  <dimension ref="B2:K56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -2182,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="27">
-        <f t="shared" ref="K31:K45" si="15">J32*J$3</f>
+        <f t="shared" ref="K32:K43" si="15">J32*J$3</f>
         <v>0</v>
       </c>
     </row>
@@ -2506,7 +2527,7 @@
         <v>7</v>
       </c>
       <c r="J41" s="28">
-        <f t="shared" ref="J40:J47" si="16">IF(H41=0,0,IF(I41="WON",(G41-1)*0.94,-1))</f>
+        <f t="shared" ref="J41:J49" si="16">IF(H41=0,0,IF(I41="WON",(G41-1)*0.94,-1))</f>
         <v>1.1656000000000002</v>
       </c>
       <c r="K41" s="27">
@@ -2700,7 +2721,7 @@
       </c>
     </row>
     <row r="47" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="48">
+      <c r="B47" s="47">
         <v>43</v>
       </c>
       <c r="C47" s="64" t="s">
@@ -2733,6 +2754,328 @@
       </c>
       <c r="K47" s="27">
         <f>J47*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B48" s="65">
+        <v>44</v>
+      </c>
+      <c r="C48" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="23">
+        <v>1.76</v>
+      </c>
+      <c r="E48" s="41">
+        <f t="shared" ref="E48:E56" si="17">1/D48</f>
+        <v>0.56818181818181823</v>
+      </c>
+      <c r="F48" s="60">
+        <f t="shared" ref="F48:F56" si="18">E48-0.2</f>
+        <v>0.36818181818181822</v>
+      </c>
+      <c r="G48" s="68">
+        <f t="shared" ref="G48:G56" si="19">1/F48</f>
+        <v>2.716049382716049</v>
+      </c>
+      <c r="H48" s="80">
+        <v>1</v>
+      </c>
+      <c r="I48" s="80" t="s">
+        <v>7</v>
+      </c>
+      <c r="J48" s="24">
+        <f t="shared" ref="J48:J56" si="20">IF(H48=0,0,IF(I48="WON",(G48-1)*0.94,-1))</f>
+        <v>1.6130864197530861</v>
+      </c>
+      <c r="K48" s="25">
+        <f t="shared" ref="K48:K56" si="21">J48*J$3</f>
+        <v>89.606950617283928</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B49" s="66">
+        <v>45</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E49" s="42">
+        <f t="shared" si="17"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="F49" s="79">
+        <f t="shared" si="18"/>
+        <v>0.70909090909090899</v>
+      </c>
+      <c r="G49" s="69">
+        <f t="shared" si="19"/>
+        <v>1.4102564102564104</v>
+      </c>
+      <c r="H49" s="77">
+        <v>0</v>
+      </c>
+      <c r="I49" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J49" s="26">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="27">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B50" s="66">
+        <v>46</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="78">
+        <v>1.93</v>
+      </c>
+      <c r="E50" s="42">
+        <f t="shared" si="17"/>
+        <v>0.5181347150259068</v>
+      </c>
+      <c r="F50" s="79">
+        <f t="shared" si="18"/>
+        <v>0.31813471502590679</v>
+      </c>
+      <c r="G50" s="69">
+        <v>3.15</v>
+      </c>
+      <c r="H50" s="77">
+        <v>1</v>
+      </c>
+      <c r="I50" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="J50" s="26">
+        <f t="shared" si="20"/>
+        <v>-1</v>
+      </c>
+      <c r="K50" s="27">
+        <f t="shared" si="21"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B51" s="66">
+        <v>47</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="78">
+        <v>1.41</v>
+      </c>
+      <c r="E51" s="42">
+        <f t="shared" si="17"/>
+        <v>0.70921985815602839</v>
+      </c>
+      <c r="F51" s="79">
+        <f t="shared" si="18"/>
+        <v>0.50921985815602833</v>
+      </c>
+      <c r="G51" s="69">
+        <f t="shared" si="19"/>
+        <v>1.9637883008356547</v>
+      </c>
+      <c r="H51" s="77">
+        <v>1</v>
+      </c>
+      <c r="I51" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J51" s="26">
+        <f t="shared" si="20"/>
+        <v>0.90596100278551539</v>
+      </c>
+      <c r="K51" s="27">
+        <f t="shared" si="21"/>
+        <v>50.326133704735376</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B52" s="66">
+        <v>48</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" s="78">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E52" s="42">
+        <f t="shared" si="17"/>
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="F52" s="79">
+        <f t="shared" si="18"/>
+        <v>0.69285714285714284</v>
+      </c>
+      <c r="G52" s="69">
+        <v>1.45</v>
+      </c>
+      <c r="H52" s="77">
+        <v>1</v>
+      </c>
+      <c r="I52" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J52" s="26">
+        <f t="shared" si="20"/>
+        <v>0.42299999999999993</v>
+      </c>
+      <c r="K52" s="27">
+        <f t="shared" si="21"/>
+        <v>23.497649999999997</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B53" s="66">
+        <v>49</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="78">
+        <v>1.45</v>
+      </c>
+      <c r="E53" s="42">
+        <f t="shared" si="17"/>
+        <v>0.68965517241379315</v>
+      </c>
+      <c r="F53" s="79">
+        <f t="shared" si="18"/>
+        <v>0.48965517241379314</v>
+      </c>
+      <c r="G53" s="69">
+        <f t="shared" si="19"/>
+        <v>2.0422535211267605</v>
+      </c>
+      <c r="H53" s="77">
+        <v>1</v>
+      </c>
+      <c r="I53" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J53" s="26">
+        <f t="shared" si="20"/>
+        <v>0.97971830985915487</v>
+      </c>
+      <c r="K53" s="27">
+        <f t="shared" si="21"/>
+        <v>54.423352112676049</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B54" s="66">
+        <v>50</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" s="78">
+        <v>1.51</v>
+      </c>
+      <c r="E54" s="42">
+        <f t="shared" si="17"/>
+        <v>0.66225165562913912</v>
+      </c>
+      <c r="F54" s="79">
+        <f t="shared" si="18"/>
+        <v>0.46225165562913911</v>
+      </c>
+      <c r="G54" s="69">
+        <v>2.17</v>
+      </c>
+      <c r="H54" s="77">
+        <v>0</v>
+      </c>
+      <c r="I54" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J54" s="26">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="27">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B55" s="66">
+        <v>51</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="78">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E55" s="42">
+        <f t="shared" si="17"/>
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="F55" s="79">
+        <f t="shared" si="18"/>
+        <v>0.69285714285714284</v>
+      </c>
+      <c r="G55" s="69">
+        <f t="shared" si="19"/>
+        <v>1.4432989690721649</v>
+      </c>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="26">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="27">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="67">
+        <v>52</v>
+      </c>
+      <c r="C56" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="9">
+        <v>1.17</v>
+      </c>
+      <c r="E56" s="43">
+        <f t="shared" si="17"/>
+        <v>0.85470085470085477</v>
+      </c>
+      <c r="F56" s="61">
+        <f t="shared" si="18"/>
+        <v>0.65470085470085482</v>
+      </c>
+      <c r="G56" s="70">
+        <f t="shared" si="19"/>
+        <v>1.5274151436031329</v>
+      </c>
+      <c r="H56" s="82"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="28">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="29">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8306D4-608B-0649-A6CB-F04E56C7DF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE515ED-F2F1-AC4B-8E7D-3F5695290F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -537,7 +537,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -765,19 +765,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2527,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="J41" s="28">
-        <f t="shared" ref="J41:J49" si="16">IF(H41=0,0,IF(I41="WON",(G41-1)*0.94,-1))</f>
+        <f t="shared" ref="J41:J47" si="16">IF(H41=0,0,IF(I41="WON",(G41-1)*0.94,-1))</f>
         <v>1.1656000000000002</v>
       </c>
       <c r="K41" s="27">
@@ -2779,10 +2767,10 @@
         <f t="shared" ref="G48:G56" si="19">1/F48</f>
         <v>2.716049382716049</v>
       </c>
-      <c r="H48" s="80">
-        <v>1</v>
-      </c>
-      <c r="I48" s="80" t="s">
+      <c r="H48" s="77">
+        <v>1</v>
+      </c>
+      <c r="I48" s="77" t="s">
         <v>7</v>
       </c>
       <c r="J48" s="24">
@@ -2801,14 +2789,14 @@
       <c r="C49" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="78">
+      <c r="D49" s="52">
         <v>1.1000000000000001</v>
       </c>
       <c r="E49" s="42">
         <f t="shared" si="17"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="F49" s="79">
+      <c r="F49" s="56">
         <f t="shared" si="18"/>
         <v>0.70909090909090899</v>
       </c>
@@ -2816,10 +2804,10 @@
         <f t="shared" si="19"/>
         <v>1.4102564102564104</v>
       </c>
-      <c r="H49" s="77">
-        <v>0</v>
-      </c>
-      <c r="I49" s="77" t="s">
+      <c r="H49" s="73">
+        <v>0</v>
+      </c>
+      <c r="I49" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J49" s="26">
@@ -2838,24 +2826,24 @@
       <c r="C50" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="78">
+      <c r="D50" s="52">
         <v>1.93</v>
       </c>
       <c r="E50" s="42">
         <f t="shared" si="17"/>
         <v>0.5181347150259068</v>
       </c>
-      <c r="F50" s="79">
+      <c r="F50" s="56">
         <f t="shared" si="18"/>
         <v>0.31813471502590679</v>
       </c>
       <c r="G50" s="69">
         <v>3.15</v>
       </c>
-      <c r="H50" s="77">
-        <v>1</v>
-      </c>
-      <c r="I50" s="77" t="s">
+      <c r="H50" s="73">
+        <v>1</v>
+      </c>
+      <c r="I50" s="73" t="s">
         <v>11</v>
       </c>
       <c r="J50" s="26">
@@ -2874,14 +2862,14 @@
       <c r="C51" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="78">
+      <c r="D51" s="52">
         <v>1.41</v>
       </c>
       <c r="E51" s="42">
         <f t="shared" si="17"/>
         <v>0.70921985815602839</v>
       </c>
-      <c r="F51" s="79">
+      <c r="F51" s="56">
         <f t="shared" si="18"/>
         <v>0.50921985815602833</v>
       </c>
@@ -2889,10 +2877,10 @@
         <f t="shared" si="19"/>
         <v>1.9637883008356547</v>
       </c>
-      <c r="H51" s="77">
-        <v>1</v>
-      </c>
-      <c r="I51" s="77" t="s">
+      <c r="H51" s="73">
+        <v>1</v>
+      </c>
+      <c r="I51" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J51" s="26">
@@ -2911,24 +2899,24 @@
       <c r="C52" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D52" s="78">
+      <c r="D52" s="52">
         <v>1.1200000000000001</v>
       </c>
       <c r="E52" s="42">
         <f t="shared" si="17"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F52" s="79">
+      <c r="F52" s="56">
         <f t="shared" si="18"/>
         <v>0.69285714285714284</v>
       </c>
       <c r="G52" s="69">
         <v>1.45</v>
       </c>
-      <c r="H52" s="77">
-        <v>1</v>
-      </c>
-      <c r="I52" s="77" t="s">
+      <c r="H52" s="73">
+        <v>1</v>
+      </c>
+      <c r="I52" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J52" s="26">
@@ -2947,14 +2935,14 @@
       <c r="C53" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="78">
+      <c r="D53" s="52">
         <v>1.45</v>
       </c>
       <c r="E53" s="42">
         <f t="shared" si="17"/>
         <v>0.68965517241379315</v>
       </c>
-      <c r="F53" s="79">
+      <c r="F53" s="56">
         <f t="shared" si="18"/>
         <v>0.48965517241379314</v>
       </c>
@@ -2962,10 +2950,10 @@
         <f t="shared" si="19"/>
         <v>2.0422535211267605</v>
       </c>
-      <c r="H53" s="77">
-        <v>1</v>
-      </c>
-      <c r="I53" s="77" t="s">
+      <c r="H53" s="73">
+        <v>1</v>
+      </c>
+      <c r="I53" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J53" s="26">
@@ -2984,24 +2972,24 @@
       <c r="C54" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="78">
+      <c r="D54" s="52">
         <v>1.51</v>
       </c>
       <c r="E54" s="42">
         <f t="shared" si="17"/>
         <v>0.66225165562913912</v>
       </c>
-      <c r="F54" s="79">
+      <c r="F54" s="56">
         <f t="shared" si="18"/>
         <v>0.46225165562913911</v>
       </c>
       <c r="G54" s="69">
         <v>2.17</v>
       </c>
-      <c r="H54" s="77">
-        <v>0</v>
-      </c>
-      <c r="I54" s="77" t="s">
+      <c r="H54" s="73">
+        <v>0</v>
+      </c>
+      <c r="I54" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J54" s="26">
@@ -3020,14 +3008,14 @@
       <c r="C55" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="D55" s="78">
+      <c r="D55" s="52">
         <v>1.1200000000000001</v>
       </c>
       <c r="E55" s="42">
         <f t="shared" si="17"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F55" s="79">
+      <c r="F55" s="56">
         <f t="shared" si="18"/>
         <v>0.69285714285714284</v>
       </c>
@@ -3035,8 +3023,12 @@
         <f t="shared" si="19"/>
         <v>1.4432989690721649</v>
       </c>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J55" s="26">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -3068,15 +3060,19 @@
         <f t="shared" si="19"/>
         <v>1.5274151436031329</v>
       </c>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
+      <c r="H56" s="78">
+        <v>1</v>
+      </c>
+      <c r="I56" s="78" t="s">
+        <v>7</v>
+      </c>
       <c r="J56" s="28">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.49577023498694489</v>
       </c>
       <c r="K56" s="29">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>27.540036553524786</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE515ED-F2F1-AC4B-8E7D-3F5695290F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987A327-CFD8-3C4C-937B-933CA93DE74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
     <sheet name="Tennis" sheetId="2" r:id="rId2"/>
-    <sheet name="Cricket" sheetId="9" r:id="rId3"/>
-    <sheet name="Basketball" sheetId="10" r:id="rId4"/>
-    <sheet name="NFL" sheetId="11" r:id="rId5"/>
-    <sheet name="Options" sheetId="13" r:id="rId6"/>
+    <sheet name="Options" sheetId="13" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -69,29 +66,6 @@
   </si>
   <si>
     <t>Unit (u)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Strategy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: backing the favourite @ 20% above starting</t>
-    </r>
   </si>
   <si>
     <t>LOST</t>
@@ -150,9 +124,6 @@
     <t>Hawks</t>
   </si>
   <si>
-    <t>No Matches Yet</t>
-  </si>
-  <si>
     <t>Fees</t>
   </si>
   <si>
@@ -260,9 +231,6 @@
       </rPr>
       <t>: backing the favourite @ 20% above starting, first to 5 games in first set</t>
     </r>
-  </si>
-  <si>
-    <t>Nava</t>
   </si>
   <si>
     <t>Expiry</t>
@@ -1122,7 +1090,7 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2"/>
     </row>
@@ -1140,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>2</v>
@@ -1164,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
@@ -1172,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="23">
         <v>1.34</v>
@@ -1209,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="52">
         <v>1.77</v>
@@ -1230,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" s="26">
         <f t="shared" ref="J6:J11" si="0">IF(H6=0,0,IF(I6="WON",(G6-1)*0.95,-1))</f>
@@ -1246,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="52">
         <v>1.91</v>
@@ -1282,7 +1250,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="52">
         <v>1.44</v>
@@ -1319,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="52">
         <v>1.19</v>
@@ -1356,7 +1324,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="52">
         <v>1.38</v>
@@ -1377,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" s="26">
         <f t="shared" si="0"/>
@@ -1393,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="52">
         <v>1.02</v>
@@ -1430,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="9">
         <v>1.74</v>
@@ -1466,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="58">
         <v>1.2</v>
@@ -1503,7 +1471,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="5">
         <v>1.52</v>
@@ -1540,7 +1508,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="5">
         <v>1.1499999999999999</v>
@@ -1577,7 +1545,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="5">
         <v>1.27</v>
@@ -1598,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" s="26">
         <f t="shared" si="9"/>
@@ -1614,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5">
         <v>1.77</v>
@@ -1651,7 +1619,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="5">
         <v>1.72</v>
@@ -1688,7 +1656,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5">
         <v>1.0900000000000001</v>
@@ -1725,7 +1693,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="5">
         <v>1.1200000000000001</v>
@@ -1762,7 +1730,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" s="11">
         <v>1.8</v>
@@ -1798,7 +1766,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D22" s="58">
         <v>1.64</v>
@@ -1835,7 +1803,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D23" s="5">
         <v>1.59</v>
@@ -1871,7 +1839,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5">
         <v>1.3</v>
@@ -1908,7 +1876,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="5">
         <v>1.1200000000000001</v>
@@ -1945,7 +1913,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5">
         <v>1.1499999999999999</v>
@@ -1981,7 +1949,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D27" s="5">
         <v>1.72</v>
@@ -2018,7 +1986,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D28" s="5">
         <v>1.3</v>
@@ -2055,7 +2023,7 @@
         <v>25</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" s="5">
         <v>1.36</v>
@@ -2075,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" s="26">
         <f t="shared" si="10"/>
@@ -2091,7 +2059,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30" s="11">
         <v>1.1100000000000001</v>
@@ -2127,7 +2095,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="23">
         <v>1.35</v>
@@ -2163,7 +2131,7 @@
         <v>28</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D32" s="52">
         <v>1.1499999999999999</v>
@@ -2200,7 +2168,7 @@
         <v>29</v>
       </c>
       <c r="C33" s="66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33" s="52">
         <v>1.67</v>
@@ -2236,7 +2204,7 @@
         <v>30</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D34" s="52">
         <v>1.42</v>
@@ -2273,7 +2241,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D35" s="52">
         <v>1.27</v>
@@ -2294,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J35" s="26">
         <f t="shared" si="14"/>
@@ -2310,7 +2278,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" s="52">
         <v>1.1299999999999999</v>
@@ -2347,7 +2315,7 @@
         <v>33</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37" s="52">
         <v>1.1299999999999999</v>
@@ -2384,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38" s="52">
         <v>1.37</v>
@@ -2421,7 +2389,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D39" s="9">
         <v>1.52</v>
@@ -2456,7 +2424,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D40" s="52">
         <v>1.28</v>
@@ -2477,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="73" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J40" s="28">
         <v>-0.14000000000000001</v>
@@ -2492,7 +2460,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="52">
         <v>1.54</v>
@@ -2528,7 +2496,7 @@
         <v>38</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D42" s="52">
         <v>1.7</v>
@@ -2565,7 +2533,7 @@
         <v>39</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43" s="52">
         <v>1.0900000000000001</v>
@@ -2602,7 +2570,7 @@
         <v>40</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D44" s="52">
         <v>1.28</v>
@@ -2639,7 +2607,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D45" s="52">
         <v>1.64</v>
@@ -2676,7 +2644,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D46" s="52">
         <v>1.2</v>
@@ -2713,7 +2681,7 @@
         <v>43</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47" s="52">
         <v>1.61</v>
@@ -2750,7 +2718,7 @@
         <v>44</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48" s="23">
         <v>1.76</v>
@@ -2787,7 +2755,7 @@
         <v>45</v>
       </c>
       <c r="C49" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D49" s="52">
         <v>1.1000000000000001</v>
@@ -2824,7 +2792,7 @@
         <v>46</v>
       </c>
       <c r="C50" s="44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D50" s="52">
         <v>1.93</v>
@@ -2844,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J50" s="26">
         <f t="shared" si="20"/>
@@ -2860,7 +2828,7 @@
         <v>47</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D51" s="52">
         <v>1.41</v>
@@ -2897,7 +2865,7 @@
         <v>48</v>
       </c>
       <c r="C52" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D52" s="52">
         <v>1.1200000000000001</v>
@@ -2933,7 +2901,7 @@
         <v>49</v>
       </c>
       <c r="C53" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D53" s="52">
         <v>1.45</v>
@@ -2970,7 +2938,7 @@
         <v>50</v>
       </c>
       <c r="C54" s="44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D54" s="52">
         <v>1.51</v>
@@ -3006,7 +2974,7 @@
         <v>51</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D55" s="52">
         <v>1.1200000000000001</v>
@@ -3043,7 +3011,7 @@
         <v>52</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D56" s="9">
         <v>1.17</v>
@@ -3083,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L12"/>
+  <dimension ref="B2:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -3092,14 +3060,14 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>9</v>
@@ -3114,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>2</v>
@@ -3138,7 +3106,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -3146,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="31">
         <v>1.78</v>
@@ -3184,7 +3152,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="31">
         <v>1.56</v>
@@ -3204,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" s="15">
         <f>IF(H6=0,0,IF(I6="WON",(G6-1),-1))</f>
@@ -3221,7 +3189,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" s="31">
         <v>1.1100000000000001</v>
@@ -3258,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8" s="31">
         <v>1.42</v>
@@ -3295,7 +3263,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" s="31">
         <v>1.33</v>
@@ -3316,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J10" si="6">IF(H9=0,0,IF(I9="WON",(G9-1),-1))</f>
@@ -3327,12 +3295,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>6</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D10" s="31">
         <v>1.33</v>
@@ -3362,79 +3330,6 @@
       <c r="K10" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="31">
-        <v>1.75</v>
-      </c>
-      <c r="E11" s="20">
-        <f t="shared" ref="E11" si="7">1/D11</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F11" s="21">
-        <f t="shared" ref="F11" si="8">E11-0.2</f>
-        <v>0.37142857142857139</v>
-      </c>
-      <c r="G11" s="22">
-        <v>2.7</v>
-      </c>
-      <c r="H11" s="30">
-        <v>1</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" ref="J11" si="9">IF(H11=0,0,IF(I11="WON",(G11-1),-1))</f>
-        <v>-1</v>
-      </c>
-      <c r="K11" s="25">
-        <f t="shared" ref="K11" si="10">J11*J$3</f>
-        <v>-55.55</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="2">
-        <v>8</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="31">
-        <v>2.75</v>
-      </c>
-      <c r="E12" s="20">
-        <f t="shared" ref="E12" si="11">1/D12</f>
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="F12" s="21">
-        <f t="shared" ref="F12" si="12">E12-0.2</f>
-        <v>0.16363636363636364</v>
-      </c>
-      <c r="G12" s="22">
-        <f>1/F12</f>
-        <v>6.1111111111111107</v>
-      </c>
-      <c r="H12" s="30">
-        <v>1</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" ref="J12" si="13">IF(H12=0,0,IF(I12="WON",(G12-1),-1))</f>
-        <v>-1</v>
-      </c>
-      <c r="K12" s="25">
-        <f t="shared" ref="K12" si="14">J12*J$3</f>
-        <v>-55.55</v>
       </c>
     </row>
   </sheetData>
@@ -3444,290 +3339,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E6120F-3D79-45D2-9E7F-690D79FF71F4}">
-  <dimension ref="B2:K5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="I3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="8">
-        <v>55.55</v>
-      </c>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="20" t="e">
-        <f>1/D5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="21" t="e">
-        <f>E5-0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="22" t="e">
-        <f>1/F5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H5" s="30">
-        <v>1</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="15" t="e">
-        <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="25" t="e">
-        <f>J5*J$3</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90ADAF7-1BB4-48D6-89E7-0AED41AA649D}">
-  <dimension ref="B2:K5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="I3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="8">
-        <v>55.55</v>
-      </c>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="20" t="e">
-        <f>1/D5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="21" t="e">
-        <f>E5-0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="22" t="e">
-        <f>1/F5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H5" s="30">
-        <v>1</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="15" t="e">
-        <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="25" t="e">
-        <f>J5*J$3</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BA0578-228A-4ECA-BD97-9526260EC85E}">
-  <dimension ref="B2:K5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="I3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="8">
-        <v>55.55</v>
-      </c>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="20" t="e">
-        <f>1/D5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="21" t="e">
-        <f>E5-0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="22" t="e">
-        <f>1/F5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H5" s="30">
-        <v>1</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="15" t="e">
-        <f>IF(H5=0,0,IF(I5="WON",(G5-1)*0.95,-1))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="25" t="e">
-        <f>J5*J$3</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821F4CAB-11EC-4DB3-9BD6-AF06D08A4FD3}">
   <dimension ref="B2:N6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3737,7 +3348,7 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -3746,7 +3357,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="K3" s="32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="39"/>
@@ -3757,34 +3368,34 @@
         <v>0</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="G4" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="H4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="J4" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987A327-CFD8-3C4C-937B-933CA93DE74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18B7B1-6B6E-4849-B56C-7634ED29BF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" activeTab="2" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -3402,74 +3402,42 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="55">
-        <v>46150</v>
-      </c>
-      <c r="D5" s="35">
-        <v>555</v>
-      </c>
-      <c r="E5" s="35">
-        <v>570</v>
-      </c>
-      <c r="F5" s="35">
-        <v>630</v>
-      </c>
-      <c r="G5" s="35">
-        <v>645</v>
-      </c>
-      <c r="H5" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="I5" s="37">
-        <v>571</v>
-      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="36">
         <f t="shared" ref="J5:J6" si="0">IF(AND(I5&lt;=F5,I5&gt;=E5),0,IF(I5&lt;E5,MAX(I5-E5,D5-E5),MAX(F5-I5,F5-G5)))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="40">
-        <v>0.3</v>
-      </c>
+      <c r="K5" s="40"/>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L6" si="1">(H5+J5)*100-K5</f>
-        <v>95.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="55">
-        <v>46157</v>
-      </c>
-      <c r="D6" s="35">
-        <v>570</v>
-      </c>
-      <c r="E6" s="35">
-        <v>585</v>
-      </c>
-      <c r="F6" s="35">
-        <v>645</v>
-      </c>
-      <c r="G6" s="35">
-        <v>660</v>
-      </c>
-      <c r="H6" s="36">
-        <v>0.96</v>
-      </c>
-      <c r="I6" s="37">
-        <v>540</v>
-      </c>
+      <c r="C6" s="55"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
       <c r="J6" s="36">
         <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-      <c r="K6" s="40">
-        <v>0.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" s="40"/>
       <c r="L6" s="38">
         <f t="shared" si="1"/>
-        <v>-1404.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18B7B1-6B6E-4849-B56C-7634ED29BF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259EFB70-1C3B-4D28-9F2F-6507D48B9CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" activeTab="2" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -204,12 +204,6 @@
     <t>Andreeva</t>
   </si>
   <si>
-    <t>Jovic</t>
-  </si>
-  <si>
-    <t>Kostyuk</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -250,15 +244,24 @@
   <si>
     <t>Tigers</t>
   </si>
+  <si>
+    <t>Gauff</t>
+  </si>
+  <si>
+    <t>Sinner</t>
+  </si>
+  <si>
+    <t>Ruud</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -503,9 +506,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -528,7 +531,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -609,22 +612,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -657,7 +660,7 @@
     <xf numFmtId="2" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -737,6 +740,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1079,22 +1115,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:K65"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="11" width="10.1640625" customWidth="1"/>
+    <col min="4" max="11" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2"/>
     </row>
-    <row r="3" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
@@ -1103,7 +1139,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +1171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1172,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>2</v>
       </c>
@@ -1209,7 +1245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>3</v>
       </c>
@@ -1245,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>4</v>
       </c>
@@ -1282,7 +1318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>5</v>
       </c>
@@ -1319,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>6</v>
       </c>
@@ -1356,7 +1392,7 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>7</v>
       </c>
@@ -1393,7 +1429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1429,7 +1465,7 @@
         <v>87.724560000000011</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="57">
         <v>9</v>
       </c>
@@ -1466,7 +1502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="44">
         <v>10</v>
       </c>
@@ -1503,7 +1539,7 @@
         <v>61.820126436781592</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="44">
         <v>11</v>
       </c>
@@ -1540,7 +1576,7 @@
         <v>26.043571428571411</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="44">
         <v>12</v>
       </c>
@@ -1577,7 +1613,7 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="44">
         <v>13</v>
       </c>
@@ -1614,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="44">
         <v>14</v>
       </c>
@@ -1651,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="44">
         <v>15</v>
       </c>
@@ -1688,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="44">
         <v>16</v>
       </c>
@@ -1725,7 +1761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="45">
         <v>17</v>
       </c>
@@ -1761,12 +1797,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="46">
         <v>18</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D22" s="58">
         <v>1.64</v>
@@ -1798,7 +1834,7 @@
         <v>75.217345238095234</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="47">
         <v>19</v>
       </c>
@@ -1834,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="47">
         <v>20</v>
       </c>
@@ -1871,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="47">
         <v>21</v>
       </c>
@@ -1908,7 +1944,7 @@
         <v>23.147742268041235</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="47">
         <v>22</v>
       </c>
@@ -1944,7 +1980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="47">
         <v>23</v>
       </c>
@@ -1981,12 +2017,12 @@
         <v>84.693426829268262</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="47">
         <v>24</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D28" s="5">
         <v>1.3</v>
@@ -2018,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="47">
         <v>25</v>
       </c>
@@ -2054,7 +2090,7 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="47">
         <v>26</v>
       </c>
@@ -2090,7 +2126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="57">
         <v>27</v>
       </c>
@@ -2126,7 +2162,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="44">
         <v>28</v>
       </c>
@@ -2163,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="44">
         <v>29</v>
       </c>
@@ -2199,12 +2235,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="44">
         <v>30</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D34" s="52">
         <v>1.42</v>
@@ -2236,7 +2272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="44">
         <v>31</v>
       </c>
@@ -2273,7 +2309,7 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="44">
         <v>32</v>
       </c>
@@ -2310,7 +2346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="44">
         <v>33</v>
       </c>
@@ -2347,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="44">
         <v>34</v>
       </c>
@@ -2384,12 +2420,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="44">
         <v>35</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D39" s="9">
         <v>1.52</v>
@@ -2419,7 +2455,7 @@
         <v>65.739999999999995</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="46">
         <v>36</v>
       </c>
@@ -2445,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="73" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J40" s="28">
         <v>-0.14000000000000001</v>
@@ -2455,7 +2491,7 @@
         <v>-7.7770000000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="47">
         <v>37</v>
       </c>
@@ -2491,7 +2527,7 @@
         <v>64.749080000000006</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="47">
         <v>38</v>
       </c>
@@ -2528,7 +2564,7 @@
         <v>82.501333333333321</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="47">
         <v>39</v>
       </c>
@@ -2565,7 +2601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="47">
         <v>40</v>
       </c>
@@ -2602,7 +2638,7 @@
         <v>37.598698924731167</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="47">
         <v>41</v>
       </c>
@@ -2639,7 +2675,7 @@
         <v>75.187345238095233</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="47">
         <v>42</v>
       </c>
@@ -2676,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="47">
         <v>43</v>
       </c>
@@ -2713,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="65">
         <v>44</v>
       </c>
@@ -2742,15 +2778,15 @@
         <v>7</v>
       </c>
       <c r="J48" s="24">
-        <f t="shared" ref="J48:J56" si="20">IF(H48=0,0,IF(I48="WON",(G48-1)*0.94,-1))</f>
+        <f t="shared" ref="J48:J57" si="20">IF(H48=0,0,IF(I48="WON",(G48-1)*0.94,-1))</f>
         <v>1.6130864197530861</v>
       </c>
       <c r="K48" s="25">
-        <f t="shared" ref="K48:K56" si="21">J48*J$3</f>
+        <f t="shared" ref="K48:K57" si="21">J48*J$3</f>
         <v>89.606950617283928</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="66">
         <v>45</v>
       </c>
@@ -2787,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="66">
         <v>46</v>
       </c>
@@ -2823,7 +2859,7 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="66">
         <v>47</v>
       </c>
@@ -2860,7 +2896,7 @@
         <v>50.326133704735376</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="66">
         <v>48</v>
       </c>
@@ -2896,7 +2932,7 @@
         <v>23.497649999999997</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="66">
         <v>49</v>
       </c>
@@ -2933,7 +2969,7 @@
         <v>54.423352112676049</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="66">
         <v>50</v>
       </c>
@@ -2969,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="66">
         <v>51</v>
       </c>
@@ -3006,12 +3042,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="67">
         <v>52</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D56" s="9">
         <v>1.17</v>
@@ -3024,23 +3060,332 @@
         <f t="shared" si="18"/>
         <v>0.65470085470085482</v>
       </c>
-      <c r="G56" s="70">
+      <c r="G56" s="69">
         <f t="shared" si="19"/>
         <v>1.5274151436031329</v>
       </c>
-      <c r="H56" s="78">
+      <c r="H56" s="79">
         <v>1</v>
       </c>
-      <c r="I56" s="78" t="s">
-        <v>7</v>
-      </c>
-      <c r="J56" s="28">
+      <c r="I56" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="J56" s="26">
         <f t="shared" si="20"/>
         <v>0.49577023498694489</v>
       </c>
-      <c r="K56" s="29">
+      <c r="K56" s="27">
         <f t="shared" si="21"/>
         <v>27.540036553524786</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="46">
+        <v>53</v>
+      </c>
+      <c r="C57" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="77">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E57" s="43">
+        <f t="shared" ref="E57:E65" si="22">1/D57</f>
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="F57" s="61">
+        <f t="shared" ref="F57:F65" si="23">E57-0.2</f>
+        <v>0.69285714285714284</v>
+      </c>
+      <c r="G57" s="68">
+        <f t="shared" ref="G57:G65" si="24">1/F57</f>
+        <v>1.4432989690721649</v>
+      </c>
+      <c r="H57" s="23">
+        <v>1</v>
+      </c>
+      <c r="I57" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" ref="J57:J65" si="25">IF(H57=0,0,IF(I57="WON",(G57-1)*0.94,-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K57" s="25">
+        <f t="shared" ref="K57:K65" si="26">J57*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="47">
+        <v>54</v>
+      </c>
+      <c r="C58" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="E58" s="43">
+        <f t="shared" si="22"/>
+        <v>0.84745762711864414</v>
+      </c>
+      <c r="F58" s="61">
+        <f t="shared" si="23"/>
+        <v>0.64745762711864407</v>
+      </c>
+      <c r="G58" s="69">
+        <f t="shared" si="24"/>
+        <v>1.544502617801047</v>
+      </c>
+      <c r="H58" s="82">
+        <v>1</v>
+      </c>
+      <c r="I58" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="25"/>
+        <v>0.51183246073298416</v>
+      </c>
+      <c r="K58" s="27">
+        <f t="shared" si="26"/>
+        <v>28.432293193717268</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="47">
+        <v>55</v>
+      </c>
+      <c r="C59" s="83" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="79">
+        <v>1.25</v>
+      </c>
+      <c r="E59" s="43">
+        <f t="shared" si="22"/>
+        <v>0.8</v>
+      </c>
+      <c r="F59" s="61">
+        <f t="shared" si="23"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G59" s="69">
+        <f t="shared" si="24"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="H59" s="82">
+        <v>0</v>
+      </c>
+      <c r="I59" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="47">
+        <v>56</v>
+      </c>
+      <c r="C60" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="79">
+        <v>1.53</v>
+      </c>
+      <c r="E60" s="43">
+        <f t="shared" si="22"/>
+        <v>0.65359477124183007</v>
+      </c>
+      <c r="F60" s="61">
+        <f t="shared" si="23"/>
+        <v>0.45359477124183006</v>
+      </c>
+      <c r="G60" s="69">
+        <f t="shared" si="24"/>
+        <v>2.2046109510086453</v>
+      </c>
+      <c r="H60" s="82"/>
+      <c r="I60" s="74"/>
+      <c r="J60" s="80">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="47">
+        <v>57</v>
+      </c>
+      <c r="C61" s="83" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="79">
+        <v>1.49</v>
+      </c>
+      <c r="E61" s="43">
+        <f t="shared" si="22"/>
+        <v>0.67114093959731547</v>
+      </c>
+      <c r="F61" s="61">
+        <f t="shared" si="23"/>
+        <v>0.47114093959731546</v>
+      </c>
+      <c r="G61" s="69">
+        <f t="shared" si="24"/>
+        <v>2.1225071225071224</v>
+      </c>
+      <c r="H61" s="82"/>
+      <c r="I61" s="74"/>
+      <c r="J61" s="80">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="47">
+        <v>58</v>
+      </c>
+      <c r="C62" s="83" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="79">
+        <v>1.69</v>
+      </c>
+      <c r="E62" s="43">
+        <f t="shared" si="22"/>
+        <v>0.59171597633136097</v>
+      </c>
+      <c r="F62" s="61">
+        <f t="shared" si="23"/>
+        <v>0.39171597633136096</v>
+      </c>
+      <c r="G62" s="69">
+        <f t="shared" si="24"/>
+        <v>2.5528700906344408</v>
+      </c>
+      <c r="H62" s="82"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="80">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="47">
+        <v>59</v>
+      </c>
+      <c r="C63" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="79">
+        <v>1.21</v>
+      </c>
+      <c r="E63" s="43">
+        <f t="shared" si="22"/>
+        <v>0.82644628099173556</v>
+      </c>
+      <c r="F63" s="61">
+        <f t="shared" si="23"/>
+        <v>0.62644628099173549</v>
+      </c>
+      <c r="G63" s="69">
+        <f t="shared" si="24"/>
+        <v>1.5963060686015833</v>
+      </c>
+      <c r="H63" s="82"/>
+      <c r="I63" s="74"/>
+      <c r="J63" s="80">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="47">
+        <v>60</v>
+      </c>
+      <c r="C64" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="79">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E64" s="43">
+        <f t="shared" si="22"/>
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="F64" s="61">
+        <f t="shared" si="23"/>
+        <v>0.69285714285714284</v>
+      </c>
+      <c r="G64" s="69">
+        <f t="shared" si="24"/>
+        <v>1.4432989690721649</v>
+      </c>
+      <c r="H64" s="82"/>
+      <c r="I64" s="74"/>
+      <c r="J64" s="80">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="48">
+        <v>61</v>
+      </c>
+      <c r="C65" s="84" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" s="78">
+        <v>1.28</v>
+      </c>
+      <c r="E65" s="43">
+        <f t="shared" si="22"/>
+        <v>0.78125</v>
+      </c>
+      <c r="F65" s="61">
+        <f t="shared" si="23"/>
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="G65" s="70">
+        <f t="shared" si="24"/>
+        <v>1.7204301075268815</v>
+      </c>
+      <c r="H65" s="9"/>
+      <c r="I65" s="76"/>
+      <c r="J65" s="81">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="29">
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3051,19 +3396,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:L14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
@@ -3077,7 +3422,7 @@
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
@@ -3109,7 +3454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -3147,7 +3492,7 @@
       </c>
       <c r="L5" s="51"/>
     </row>
-    <row r="6" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -3184,7 +3529,7 @@
       </c>
       <c r="L6" s="51"/>
     </row>
-    <row r="7" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -3195,11 +3540,11 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="E7" s="20">
-        <f t="shared" ref="E7:E10" si="0">1/D7</f>
+        <f t="shared" ref="E7:E11" si="0">1/D7</f>
         <v>0.9009009009009008</v>
       </c>
       <c r="F7" s="21">
-        <f t="shared" ref="F7:F10" si="1">E7-0.2</f>
+        <f t="shared" ref="F7:F11" si="1">E7-0.2</f>
         <v>0.70090090090090085</v>
       </c>
       <c r="G7" s="22">
@@ -3221,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -3258,33 +3603,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D9" s="31">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="E9" s="20">
         <f t="shared" si="0"/>
-        <v>0.75187969924812026</v>
+        <v>0.68493150684931503</v>
       </c>
       <c r="F9" s="21">
         <f t="shared" si="1"/>
-        <v>0.5518796992481203</v>
+        <v>0.48493150684931502</v>
       </c>
       <c r="G9" s="22">
-        <f t="shared" ref="G9:G10" si="5">1/F9</f>
-        <v>1.8119891008174387</v>
+        <f t="shared" ref="G9:G11" si="5">1/F9</f>
+        <v>2.0621468926553677</v>
       </c>
       <c r="H9" s="30">
         <v>0</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J10" si="6">IF(H9=0,0,IF(I9="WON",(G9-1),-1))</f>
@@ -3295,27 +3640,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>6</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D10" s="31">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="E10" s="20">
         <f t="shared" si="0"/>
-        <v>0.75187969924812026</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F10" s="21">
         <f t="shared" si="1"/>
-        <v>0.5518796992481203</v>
+        <v>0.74339622641509417</v>
       </c>
       <c r="G10" s="22">
         <f t="shared" si="5"/>
-        <v>1.8119891008174387</v>
+        <v>1.3451776649746197</v>
       </c>
       <c r="H10" s="30">
         <v>0</v>
@@ -3330,6 +3675,45 @@
       <c r="K10" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>7</v>
+      </c>
+      <c r="C11" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="86">
+        <v>1.45</v>
+      </c>
+      <c r="E11" s="87">
+        <f t="shared" si="0"/>
+        <v>0.68965517241379315</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="1"/>
+        <v>0.48965517241379314</v>
+      </c>
+      <c r="G11" s="88">
+        <f t="shared" si="5"/>
+        <v>2.0422535211267605</v>
+      </c>
+      <c r="H11" s="89"/>
+    </row>
+    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3341,17 +3725,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821F4CAB-11EC-4DB3-9BD6-AF06D08A4FD3}">
   <dimension ref="B2:N6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="14" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3363,12 +3747,12 @@
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
     </row>
-    <row r="4" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>23</v>
@@ -3398,7 +3782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -3419,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>2</v>
       </c>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259EFB70-1C3B-4D28-9F2F-6507D48B9CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB13E9B7-57CD-4398-ADB3-D720564867F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -252,6 +252,24 @@
   </si>
   <si>
     <t>Ruud</t>
+  </si>
+  <si>
+    <t>Putinseva</t>
+  </si>
+  <si>
+    <t>Keys</t>
+  </si>
+  <si>
+    <t>Yastremska</t>
+  </si>
+  <si>
+    <t>Molcan</t>
+  </si>
+  <si>
+    <t>Ivan Justo</t>
+  </si>
+  <si>
+    <t>Vallejo</t>
   </si>
 </sst>
 </file>
@@ -508,7 +526,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -773,6 +791,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3396,7 +3417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L14"/>
+  <dimension ref="B2:L18"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -3540,11 +3561,11 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="E7" s="20">
-        <f t="shared" ref="E7:E11" si="0">1/D7</f>
+        <f t="shared" ref="E7:E18" si="0">1/D7</f>
         <v>0.9009009009009008</v>
       </c>
       <c r="F7" s="21">
-        <f t="shared" ref="F7:F11" si="1">E7-0.2</f>
+        <f t="shared" ref="F7:F18" si="1">E7-0.2</f>
         <v>0.70090090090090085</v>
       </c>
       <c r="G7" s="22">
@@ -3622,7 +3643,7 @@
         <v>0.48493150684931502</v>
       </c>
       <c r="G9" s="22">
-        <f t="shared" ref="G9:G11" si="5">1/F9</f>
+        <f t="shared" ref="G9:G18" si="5">1/F9</f>
         <v>2.0621468926553677</v>
       </c>
       <c r="H9" s="30">
@@ -3700,20 +3721,226 @@
         <v>2.0422535211267605</v>
       </c>
       <c r="H11" s="89"/>
+      <c r="J11" s="15">
+        <f t="shared" ref="J11:J15" si="7">IF(H11=0,0,IF(I11="WON",(G11-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="25">
+        <f t="shared" ref="K11:K15" si="8">J11*J$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>8</v>
       </c>
+      <c r="C12" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="86">
+        <v>1.36</v>
+      </c>
+      <c r="E12" s="87">
+        <f t="shared" si="0"/>
+        <v>0.73529411764705876</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="1"/>
+        <v>0.5352941176470587</v>
+      </c>
+      <c r="G12" s="88">
+        <f t="shared" si="5"/>
+        <v>1.8681318681318686</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="86">
+        <v>1.22</v>
+      </c>
+      <c r="E13" s="87">
+        <f t="shared" si="0"/>
+        <v>0.81967213114754101</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="1"/>
+        <v>0.61967213114754105</v>
+      </c>
+      <c r="G13" s="88">
+        <f t="shared" si="5"/>
+        <v>1.6137566137566135</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>10</v>
+      </c>
+      <c r="C14" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="86">
+        <v>1.89</v>
+      </c>
+      <c r="E14" s="87">
+        <f t="shared" si="0"/>
+        <v>0.52910052910052918</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="1"/>
+        <v>0.32910052910052917</v>
+      </c>
+      <c r="G14" s="88">
+        <v>3.05</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="86">
+        <v>1.84</v>
+      </c>
+      <c r="E15" s="87">
+        <f t="shared" si="0"/>
+        <v>0.54347826086956519</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="1"/>
+        <v>0.34347826086956518</v>
+      </c>
+      <c r="G15" s="88">
+        <v>2.92</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="3">
+        <v>12</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="86">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E16" s="87">
+        <f t="shared" si="0"/>
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="1"/>
+        <v>0.71743119266055033</v>
+      </c>
+      <c r="G16" s="88">
+        <f t="shared" si="5"/>
+        <v>1.3938618925831205</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" ref="J16" si="9">IF(H16=0,0,IF(I16="WON",(G16-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="25">
+        <f t="shared" ref="K16" si="10">J16*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="3">
+        <v>13</v>
+      </c>
+      <c r="C17" s="85" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="86">
+        <v>1.84</v>
+      </c>
+      <c r="E17" s="90">
+        <f t="shared" si="0"/>
+        <v>0.54347826086956519</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="1"/>
+        <v>0.34347826086956518</v>
+      </c>
+      <c r="G17" s="88">
+        <v>2.92</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" ref="J17:J18" si="11">IF(H17=0,0,IF(I17="WON",(G17-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="25">
+        <f t="shared" ref="K17:K18" si="12">J17*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <v>14</v>
+      </c>
+      <c r="C18" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="86">
+        <v>1.79</v>
+      </c>
+      <c r="E18" s="90">
+        <f t="shared" si="0"/>
+        <v>0.55865921787709494</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="1"/>
+        <v>0.35865921787709493</v>
+      </c>
+      <c r="G18" s="88">
+        <v>2.8</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="25">
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB13E9B7-57CD-4398-ADB3-D720564867F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380CA458-4864-4DD9-8C2D-7488E91583F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="75">
   <si>
     <t>ID</t>
   </si>
@@ -270,6 +270,57 @@
   </si>
   <si>
     <t>Vallejo</t>
+  </si>
+  <si>
+    <t>Collignon</t>
+  </si>
+  <si>
+    <t>Bosio</t>
+  </si>
+  <si>
+    <t>Zakharova</t>
+  </si>
+  <si>
+    <t>Ofner</t>
+  </si>
+  <si>
+    <t>Garin</t>
+  </si>
+  <si>
+    <t>Van Assche</t>
+  </si>
+  <si>
+    <t>Putintseva</t>
+  </si>
+  <si>
+    <t>Hijijata</t>
+  </si>
+  <si>
+    <t>Zhang</t>
+  </si>
+  <si>
+    <t>Basavareddy</t>
+  </si>
+  <si>
+    <t>Gaston</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+  </si>
+  <si>
+    <t>Kessler</t>
+  </si>
+  <si>
+    <t>Hijikata</t>
+  </si>
+  <si>
+    <t>Bondar</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>Sakkari</t>
   </si>
 </sst>
 </file>
@@ -526,7 +577,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -618,9 +669,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -685,9 +733,6 @@
     <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -760,40 +805,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1136,7 +1175,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K65"/>
+  <dimension ref="B2:K67"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -1196,13 +1235,13 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="45" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="23">
         <v>1.34</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="40">
         <f>1/D5</f>
         <v>0.74626865671641784</v>
       </c>
@@ -1233,13 +1272,13 @@
       <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="51">
         <v>1.77</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="41">
         <f>1/D6</f>
         <v>0.56497175141242939</v>
       </c>
@@ -1247,14 +1286,14 @@
         <f>E6-0.2</f>
         <v>0.36497175141242938</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="52">
         <f>1/F6</f>
         <v>2.7399380804953561</v>
       </c>
-      <c r="H6" s="52">
-        <v>0</v>
-      </c>
-      <c r="I6" s="52" t="s">
+      <c r="H6" s="51">
+        <v>0</v>
+      </c>
+      <c r="I6" s="51" t="s">
         <v>10</v>
       </c>
       <c r="J6" s="26">
@@ -1270,13 +1309,13 @@
       <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="51">
         <v>1.91</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="41">
         <f t="shared" ref="E7:E12" si="2">1/D7</f>
         <v>0.52356020942408377</v>
       </c>
@@ -1284,13 +1323,13 @@
         <f t="shared" ref="F7:F12" si="3">E7-0.2</f>
         <v>0.32356020942408376</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="52">
         <v>3.1</v>
       </c>
-      <c r="H7" s="52">
-        <v>0</v>
-      </c>
-      <c r="I7" s="52" t="s">
+      <c r="H7" s="51">
+        <v>0</v>
+      </c>
+      <c r="I7" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J7" s="26">
@@ -1306,13 +1345,13 @@
       <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="51">
         <v>1.44</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="41">
         <f t="shared" si="2"/>
         <v>0.69444444444444442</v>
       </c>
@@ -1320,14 +1359,14 @@
         <f t="shared" si="3"/>
         <v>0.49444444444444441</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="52">
         <f t="shared" ref="G8:G11" si="4">1/F8</f>
         <v>2.0224719101123596</v>
       </c>
-      <c r="H8" s="52">
-        <v>0</v>
-      </c>
-      <c r="I8" s="52" t="s">
+      <c r="H8" s="51">
+        <v>0</v>
+      </c>
+      <c r="I8" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J8" s="26">
@@ -1343,13 +1382,13 @@
       <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="51">
         <v>1.19</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="41">
         <f t="shared" si="2"/>
         <v>0.84033613445378152</v>
       </c>
@@ -1357,14 +1396,14 @@
         <f t="shared" si="3"/>
         <v>0.64033613445378146</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="52">
         <f t="shared" si="4"/>
         <v>1.5616797900262469</v>
       </c>
-      <c r="H9" s="52">
-        <v>0</v>
-      </c>
-      <c r="I9" s="52" t="s">
+      <c r="H9" s="51">
+        <v>0</v>
+      </c>
+      <c r="I9" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J9" s="26">
@@ -1380,13 +1419,13 @@
       <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="51">
         <v>1.38</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="41">
         <f t="shared" si="2"/>
         <v>0.7246376811594204</v>
       </c>
@@ -1394,14 +1433,14 @@
         <f t="shared" si="3"/>
         <v>0.52463768115942044</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="52">
         <f t="shared" si="4"/>
         <v>1.9060773480662978</v>
       </c>
-      <c r="H10" s="52">
-        <v>1</v>
-      </c>
-      <c r="I10" s="52" t="s">
+      <c r="H10" s="51">
+        <v>1</v>
+      </c>
+      <c r="I10" s="51" t="s">
         <v>10</v>
       </c>
       <c r="J10" s="26">
@@ -1417,13 +1456,13 @@
       <c r="B11" s="3">
         <v>7</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="51">
         <v>1.02</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="41">
         <f t="shared" si="2"/>
         <v>0.98039215686274506</v>
       </c>
@@ -1431,14 +1470,14 @@
         <f t="shared" si="3"/>
         <v>0.78039215686274499</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="52">
         <f t="shared" si="4"/>
         <v>1.2814070351758795</v>
       </c>
-      <c r="H11" s="52">
-        <v>0</v>
-      </c>
-      <c r="I11" s="52" t="s">
+      <c r="H11" s="51">
+        <v>0</v>
+      </c>
+      <c r="I11" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J11" s="26">
@@ -1454,13 +1493,13 @@
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="47" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="9">
         <v>1.74</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="42">
         <f t="shared" si="2"/>
         <v>0.57471264367816088</v>
       </c>
@@ -1487,16 +1526,16 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="57">
+      <c r="B13" s="55">
         <v>9</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="56">
         <v>1.2</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="40">
         <f t="shared" ref="E13:E47" si="5">1/D13</f>
         <v>0.83333333333333337</v>
       </c>
@@ -1504,7 +1543,7 @@
         <f t="shared" ref="F13:F47" si="6">E13-0.2</f>
         <v>0.6333333333333333</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="57">
         <f t="shared" ref="G13:G20" si="7">1/F13</f>
         <v>1.5789473684210527</v>
       </c>
@@ -1524,16 +1563,16 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="44">
+      <c r="B14" s="43">
         <v>10</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="43" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="5">
         <v>1.52</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="41">
         <f t="shared" si="5"/>
         <v>0.65789473684210531</v>
       </c>
@@ -1541,14 +1580,14 @@
         <f t="shared" si="6"/>
         <v>0.4578947368421053</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="48">
         <f t="shared" si="7"/>
         <v>2.1839080459770113</v>
       </c>
-      <c r="H14" s="52">
-        <v>1</v>
-      </c>
-      <c r="I14" s="52" t="s">
+      <c r="H14" s="51">
+        <v>1</v>
+      </c>
+      <c r="I14" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J14" s="26">
@@ -1561,16 +1600,16 @@
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="44">
+      <c r="B15" s="43">
         <v>11</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="43" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="5">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="41">
         <f t="shared" si="5"/>
         <v>0.86956521739130443</v>
       </c>
@@ -1578,14 +1617,14 @@
         <f t="shared" si="6"/>
         <v>0.66956521739130448</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="48">
         <f t="shared" si="7"/>
         <v>1.4935064935064932</v>
       </c>
-      <c r="H15" s="52">
-        <v>1</v>
-      </c>
-      <c r="I15" s="52" t="s">
+      <c r="H15" s="51">
+        <v>1</v>
+      </c>
+      <c r="I15" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J15" s="26">
@@ -1598,16 +1637,16 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="44">
+      <c r="B16" s="43">
         <v>12</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="43" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="5">
         <v>1.27</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <f t="shared" si="5"/>
         <v>0.78740157480314954</v>
       </c>
@@ -1615,14 +1654,14 @@
         <f t="shared" si="6"/>
         <v>0.58740157480314958</v>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="48">
         <f t="shared" si="7"/>
         <v>1.7024128686327078</v>
       </c>
-      <c r="H16" s="52">
-        <v>1</v>
-      </c>
-      <c r="I16" s="52" t="s">
+      <c r="H16" s="51">
+        <v>1</v>
+      </c>
+      <c r="I16" s="51" t="s">
         <v>10</v>
       </c>
       <c r="J16" s="26">
@@ -1635,16 +1674,16 @@
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="44">
+      <c r="B17" s="43">
         <v>13</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="43" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="5">
         <v>1.77</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="41">
         <f t="shared" si="5"/>
         <v>0.56497175141242939</v>
       </c>
@@ -1652,14 +1691,14 @@
         <f t="shared" si="6"/>
         <v>0.36497175141242938</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="48">
         <f t="shared" si="7"/>
         <v>2.7399380804953561</v>
       </c>
-      <c r="H17" s="52">
-        <v>0</v>
-      </c>
-      <c r="I17" s="52" t="s">
+      <c r="H17" s="51">
+        <v>0</v>
+      </c>
+      <c r="I17" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J17" s="26">
@@ -1672,16 +1711,16 @@
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="44">
+      <c r="B18" s="43">
         <v>14</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="43" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="5">
         <v>1.72</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="41">
         <f t="shared" si="5"/>
         <v>0.58139534883720934</v>
       </c>
@@ -1689,14 +1728,14 @@
         <f t="shared" si="6"/>
         <v>0.38139534883720932</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="48">
         <f t="shared" si="7"/>
         <v>2.6219512195121948</v>
       </c>
-      <c r="H18" s="52">
-        <v>0</v>
-      </c>
-      <c r="I18" s="52" t="s">
+      <c r="H18" s="51">
+        <v>0</v>
+      </c>
+      <c r="I18" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J18" s="26">
@@ -1709,16 +1748,16 @@
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="44">
+      <c r="B19" s="43">
         <v>15</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="43" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="5">
         <v>1.0900000000000001</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="41">
         <f t="shared" si="5"/>
         <v>0.9174311926605504</v>
       </c>
@@ -1726,14 +1765,14 @@
         <f t="shared" si="6"/>
         <v>0.71743119266055033</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="48">
         <f t="shared" si="7"/>
         <v>1.3938618925831205</v>
       </c>
-      <c r="H19" s="52">
-        <v>0</v>
-      </c>
-      <c r="I19" s="52" t="s">
+      <c r="H19" s="51">
+        <v>0</v>
+      </c>
+      <c r="I19" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J19" s="26">
@@ -1746,16 +1785,16 @@
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="44">
+      <c r="B20" s="43">
         <v>16</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="43" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="5">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="41">
         <f t="shared" si="5"/>
         <v>0.89285714285714279</v>
       </c>
@@ -1763,14 +1802,14 @@
         <f t="shared" si="6"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="48">
         <f t="shared" si="7"/>
         <v>1.4432989690721649</v>
       </c>
-      <c r="H20" s="52">
-        <v>0</v>
-      </c>
-      <c r="I20" s="52" t="s">
+      <c r="H20" s="51">
+        <v>0</v>
+      </c>
+      <c r="I20" s="51" t="s">
         <v>7</v>
       </c>
       <c r="J20" s="26">
@@ -1783,16 +1822,16 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="45">
+      <c r="B21" s="44">
         <v>17</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="44" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="11">
         <v>1.8</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="42">
         <f t="shared" si="5"/>
         <v>0.55555555555555558</v>
       </c>
@@ -1800,7 +1839,7 @@
         <f t="shared" si="6"/>
         <v>0.35555555555555557</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="49">
         <v>2.82</v>
       </c>
       <c r="H21" s="9">
@@ -1819,31 +1858,31 @@
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="46">
+      <c r="B22" s="45">
         <v>18</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="56">
         <v>1.64</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="40">
         <f t="shared" si="5"/>
         <v>0.6097560975609756</v>
       </c>
-      <c r="F22" s="60">
+      <c r="F22" s="58">
         <f t="shared" si="6"/>
         <v>0.40975609756097559</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G22" s="57">
         <f>1/F22</f>
         <v>2.4404761904761907</v>
       </c>
       <c r="H22" s="23">
         <v>1</v>
       </c>
-      <c r="I22" s="62" t="s">
+      <c r="I22" s="60" t="s">
         <v>7</v>
       </c>
       <c r="J22" s="24">
@@ -1856,30 +1895,30 @@
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="47">
+      <c r="B23" s="46">
         <v>19</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C23" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="5">
         <v>1.59</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="41">
         <f t="shared" si="5"/>
         <v>0.62893081761006286</v>
       </c>
-      <c r="F23" s="56">
+      <c r="F23" s="54">
         <f t="shared" si="6"/>
         <v>0.42893081761006285</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="48">
         <v>2.34</v>
       </c>
-      <c r="H23" s="52">
-        <v>0</v>
-      </c>
-      <c r="I23" s="74" t="s">
+      <c r="H23" s="51">
+        <v>0</v>
+      </c>
+      <c r="I23" s="72" t="s">
         <v>7</v>
       </c>
       <c r="J23" s="26">
@@ -1892,31 +1931,31 @@
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="47">
+      <c r="B24" s="46">
         <v>20</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="62" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="5">
         <v>1.3</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="41">
         <f t="shared" si="5"/>
         <v>0.76923076923076916</v>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="54">
         <f t="shared" si="6"/>
         <v>0.56923076923076921</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="48">
         <f t="shared" ref="G24:G28" si="12">1/F24</f>
         <v>1.7567567567567568</v>
       </c>
-      <c r="H24" s="52">
-        <v>0</v>
-      </c>
-      <c r="I24" s="74" t="s">
+      <c r="H24" s="51">
+        <v>0</v>
+      </c>
+      <c r="I24" s="72" t="s">
         <v>7</v>
       </c>
       <c r="J24" s="26">
@@ -1929,31 +1968,31 @@
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="47">
+      <c r="B25" s="46">
         <v>21</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="C25" s="62" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="5">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="41">
         <f t="shared" si="5"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F25" s="56">
+      <c r="F25" s="54">
         <f t="shared" si="6"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G25" s="49">
+      <c r="G25" s="48">
         <f t="shared" si="12"/>
         <v>1.4432989690721649</v>
       </c>
-      <c r="H25" s="52">
-        <v>1</v>
-      </c>
-      <c r="I25" s="74" t="s">
+      <c r="H25" s="51">
+        <v>1</v>
+      </c>
+      <c r="I25" s="72" t="s">
         <v>7</v>
       </c>
       <c r="J25" s="26">
@@ -1966,30 +2005,30 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="47">
+      <c r="B26" s="46">
         <v>22</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="62" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="5">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="41">
         <f t="shared" si="5"/>
         <v>0.86956521739130443</v>
       </c>
-      <c r="F26" s="56">
+      <c r="F26" s="54">
         <f t="shared" si="6"/>
         <v>0.66956521739130448</v>
       </c>
-      <c r="G26" s="49">
+      <c r="G26" s="48">
         <v>1.5</v>
       </c>
-      <c r="H26" s="52">
-        <v>0</v>
-      </c>
-      <c r="I26" s="75" t="s">
+      <c r="H26" s="51">
+        <v>0</v>
+      </c>
+      <c r="I26" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J26" s="26">
@@ -2002,31 +2041,31 @@
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B27" s="47">
+      <c r="B27" s="46">
         <v>23</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="62" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="5">
         <v>1.72</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="41">
         <f t="shared" si="5"/>
         <v>0.58139534883720934</v>
       </c>
-      <c r="F27" s="56">
+      <c r="F27" s="54">
         <f t="shared" si="6"/>
         <v>0.38139534883720932</v>
       </c>
-      <c r="G27" s="49">
+      <c r="G27" s="48">
         <f t="shared" si="12"/>
         <v>2.6219512195121948</v>
       </c>
-      <c r="H27" s="52">
-        <v>1</v>
-      </c>
-      <c r="I27" s="75" t="s">
+      <c r="H27" s="51">
+        <v>1</v>
+      </c>
+      <c r="I27" s="73" t="s">
         <v>7</v>
       </c>
       <c r="J27" s="26">
@@ -2039,31 +2078,31 @@
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="47">
+      <c r="B28" s="46">
         <v>24</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="D28" s="5">
         <v>1.3</v>
       </c>
-      <c r="E28" s="42">
+      <c r="E28" s="41">
         <f t="shared" si="5"/>
         <v>0.76923076923076916</v>
       </c>
-      <c r="F28" s="56">
+      <c r="F28" s="54">
         <f t="shared" si="6"/>
         <v>0.56923076923076921</v>
       </c>
-      <c r="G28" s="49">
+      <c r="G28" s="48">
         <f t="shared" si="12"/>
         <v>1.7567567567567568</v>
       </c>
-      <c r="H28" s="52">
-        <v>0</v>
-      </c>
-      <c r="I28" s="74" t="s">
+      <c r="H28" s="51">
+        <v>0</v>
+      </c>
+      <c r="I28" s="72" t="s">
         <v>7</v>
       </c>
       <c r="J28" s="26">
@@ -2076,30 +2115,30 @@
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="47">
+      <c r="B29" s="46">
         <v>25</v>
       </c>
-      <c r="C29" s="64" t="s">
+      <c r="C29" s="62" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="5">
         <v>1.36</v>
       </c>
-      <c r="E29" s="42">
+      <c r="E29" s="41">
         <f t="shared" si="5"/>
         <v>0.73529411764705876</v>
       </c>
-      <c r="F29" s="56">
+      <c r="F29" s="54">
         <f t="shared" si="6"/>
         <v>0.5352941176470587</v>
       </c>
-      <c r="G29" s="49">
+      <c r="G29" s="48">
         <v>1.88</v>
       </c>
-      <c r="H29" s="52">
-        <v>1</v>
-      </c>
-      <c r="I29" s="74" t="s">
+      <c r="H29" s="51">
+        <v>1</v>
+      </c>
+      <c r="I29" s="72" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="26">
@@ -2112,30 +2151,30 @@
       </c>
     </row>
     <row r="30" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <v>26</v>
       </c>
-      <c r="C30" s="64" t="s">
+      <c r="C30" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="11">
         <v>1.1100000000000001</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="42">
         <f t="shared" si="5"/>
         <v>0.9009009009009008</v>
       </c>
-      <c r="F30" s="61">
+      <c r="F30" s="59">
         <f t="shared" si="6"/>
         <v>0.70090090090090085</v>
       </c>
-      <c r="G30" s="50">
+      <c r="G30" s="49">
         <v>1.44</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
       </c>
-      <c r="I30" s="76" t="s">
+      <c r="I30" s="74" t="s">
         <v>7</v>
       </c>
       <c r="J30" s="26">
@@ -2148,31 +2187,31 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="57">
+      <c r="B31" s="55">
         <v>27</v>
       </c>
-      <c r="C31" s="65" t="s">
+      <c r="C31" s="63" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="23">
         <v>1.35</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="40">
         <f t="shared" si="5"/>
         <v>0.7407407407407407</v>
       </c>
-      <c r="F31" s="60">
+      <c r="F31" s="58">
         <f t="shared" si="6"/>
         <v>0.54074074074074074</v>
       </c>
-      <c r="G31" s="68">
+      <c r="G31" s="66">
         <f>1/F31</f>
         <v>1.8493150684931507</v>
       </c>
-      <c r="H31" s="71">
-        <v>1</v>
-      </c>
-      <c r="I31" s="71" t="s">
+      <c r="H31" s="69">
+        <v>1</v>
+      </c>
+      <c r="I31" s="69" t="s">
         <v>7</v>
       </c>
       <c r="J31" s="24">
@@ -2184,31 +2223,31 @@
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="44">
+      <c r="B32" s="43">
         <v>28</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="51">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E32" s="42">
+      <c r="E32" s="41">
         <f t="shared" si="5"/>
         <v>0.86956521739130443</v>
       </c>
-      <c r="F32" s="56">
+      <c r="F32" s="54">
         <f t="shared" si="6"/>
         <v>0.66956521739130448</v>
       </c>
-      <c r="G32" s="69">
+      <c r="G32" s="67">
         <f t="shared" ref="G32:G47" si="13">1/F32</f>
         <v>1.4935064935064932</v>
       </c>
-      <c r="H32" s="73">
-        <v>0</v>
-      </c>
-      <c r="I32" s="73" t="s">
+      <c r="H32" s="71">
+        <v>0</v>
+      </c>
+      <c r="I32" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J32" s="26">
@@ -2221,30 +2260,30 @@
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="44">
+      <c r="B33" s="43">
         <v>29</v>
       </c>
-      <c r="C33" s="66" t="s">
+      <c r="C33" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="51">
         <v>1.67</v>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="41">
         <f t="shared" si="5"/>
         <v>0.5988023952095809</v>
       </c>
-      <c r="F33" s="56">
+      <c r="F33" s="54">
         <f t="shared" si="6"/>
         <v>0.39880239520958088</v>
       </c>
-      <c r="G33" s="69">
+      <c r="G33" s="67">
         <v>2.52</v>
       </c>
-      <c r="H33" s="73">
-        <v>0</v>
-      </c>
-      <c r="I33" s="73" t="s">
+      <c r="H33" s="71">
+        <v>0</v>
+      </c>
+      <c r="I33" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J33" s="26">
@@ -2257,31 +2296,31 @@
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="44">
+      <c r="B34" s="43">
         <v>30</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="51">
         <v>1.42</v>
       </c>
-      <c r="E34" s="42">
+      <c r="E34" s="41">
         <f t="shared" si="5"/>
         <v>0.70422535211267612</v>
       </c>
-      <c r="F34" s="56">
+      <c r="F34" s="54">
         <f t="shared" si="6"/>
         <v>0.50422535211267605</v>
       </c>
-      <c r="G34" s="69">
+      <c r="G34" s="67">
         <f t="shared" si="13"/>
         <v>1.9832402234636872</v>
       </c>
-      <c r="H34" s="73">
-        <v>0</v>
-      </c>
-      <c r="I34" s="73" t="s">
+      <c r="H34" s="71">
+        <v>0</v>
+      </c>
+      <c r="I34" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J34" s="26">
@@ -2294,31 +2333,31 @@
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="44">
+      <c r="B35" s="43">
         <v>31</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="52">
+      <c r="D35" s="51">
         <v>1.27</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="41">
         <f t="shared" si="5"/>
         <v>0.78740157480314954</v>
       </c>
-      <c r="F35" s="56">
+      <c r="F35" s="54">
         <f t="shared" si="6"/>
         <v>0.58740157480314958</v>
       </c>
-      <c r="G35" s="69">
+      <c r="G35" s="67">
         <f t="shared" si="13"/>
         <v>1.7024128686327078</v>
       </c>
-      <c r="H35" s="73">
-        <v>1</v>
-      </c>
-      <c r="I35" s="73" t="s">
+      <c r="H35" s="71">
+        <v>1</v>
+      </c>
+      <c r="I35" s="71" t="s">
         <v>10</v>
       </c>
       <c r="J35" s="26">
@@ -2331,31 +2370,31 @@
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="44">
+      <c r="B36" s="43">
         <v>32</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="51">
         <v>1.1299999999999999</v>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="41">
         <f t="shared" si="5"/>
         <v>0.88495575221238942</v>
       </c>
-      <c r="F36" s="56">
+      <c r="F36" s="54">
         <f t="shared" si="6"/>
         <v>0.68495575221238947</v>
       </c>
-      <c r="G36" s="69">
+      <c r="G36" s="67">
         <f t="shared" si="13"/>
         <v>1.4599483204134365</v>
       </c>
-      <c r="H36" s="73">
-        <v>0</v>
-      </c>
-      <c r="I36" s="73" t="s">
+      <c r="H36" s="71">
+        <v>0</v>
+      </c>
+      <c r="I36" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J36" s="26">
@@ -2368,31 +2407,31 @@
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B37" s="44">
+      <c r="B37" s="43">
         <v>33</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C37" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="51">
         <v>1.1299999999999999</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="41">
         <f t="shared" si="5"/>
         <v>0.88495575221238942</v>
       </c>
-      <c r="F37" s="56">
+      <c r="F37" s="54">
         <f t="shared" si="6"/>
         <v>0.68495575221238947</v>
       </c>
-      <c r="G37" s="69">
+      <c r="G37" s="67">
         <f t="shared" si="13"/>
         <v>1.4599483204134365</v>
       </c>
-      <c r="H37" s="73">
-        <v>0</v>
-      </c>
-      <c r="I37" s="73" t="s">
+      <c r="H37" s="71">
+        <v>0</v>
+      </c>
+      <c r="I37" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J37" s="26">
@@ -2405,31 +2444,31 @@
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B38" s="44">
+      <c r="B38" s="43">
         <v>34</v>
       </c>
-      <c r="C38" s="66" t="s">
+      <c r="C38" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="51">
         <v>1.37</v>
       </c>
-      <c r="E38" s="42">
+      <c r="E38" s="41">
         <f t="shared" si="5"/>
         <v>0.72992700729927007</v>
       </c>
-      <c r="F38" s="56">
+      <c r="F38" s="54">
         <f t="shared" si="6"/>
         <v>0.52992700729927011</v>
       </c>
-      <c r="G38" s="69">
+      <c r="G38" s="67">
         <f t="shared" si="13"/>
         <v>1.887052341597796</v>
       </c>
-      <c r="H38" s="73">
-        <v>0</v>
-      </c>
-      <c r="I38" s="73" t="s">
+      <c r="H38" s="71">
+        <v>0</v>
+      </c>
+      <c r="I38" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J38" s="26">
@@ -2442,30 +2481,30 @@
       </c>
     </row>
     <row r="39" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="44">
+      <c r="B39" s="43">
         <v>35</v>
       </c>
-      <c r="C39" s="67" t="s">
+      <c r="C39" s="65" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="9">
         <v>1.52</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="42">
         <f t="shared" si="5"/>
         <v>0.65789473684210531</v>
       </c>
-      <c r="F39" s="61">
+      <c r="F39" s="59">
         <f t="shared" si="6"/>
         <v>0.4578947368421053</v>
       </c>
-      <c r="G39" s="70">
+      <c r="G39" s="68">
         <v>2.2200000000000002</v>
       </c>
-      <c r="H39" s="72">
-        <v>1</v>
-      </c>
-      <c r="I39" s="72" t="s">
+      <c r="H39" s="70">
+        <v>1</v>
+      </c>
+      <c r="I39" s="70" t="s">
         <v>7</v>
       </c>
       <c r="J39" s="28">
@@ -2477,31 +2516,31 @@
       </c>
     </row>
     <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="46">
+      <c r="B40" s="45">
         <v>36</v>
       </c>
-      <c r="C40" s="64" t="s">
+      <c r="C40" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="52">
+      <c r="D40" s="51">
         <v>1.28</v>
       </c>
-      <c r="E40" s="42">
+      <c r="E40" s="41">
         <f t="shared" si="5"/>
         <v>0.78125</v>
       </c>
-      <c r="F40" s="56">
+      <c r="F40" s="54">
         <f t="shared" si="6"/>
         <v>0.58125000000000004</v>
       </c>
-      <c r="G40" s="69">
+      <c r="G40" s="67">
         <f t="shared" si="13"/>
         <v>1.7204301075268815</v>
       </c>
-      <c r="H40" s="73">
-        <v>1</v>
-      </c>
-      <c r="I40" s="73" t="s">
+      <c r="H40" s="71">
+        <v>1</v>
+      </c>
+      <c r="I40" s="71" t="s">
         <v>47</v>
       </c>
       <c r="J40" s="28">
@@ -2513,30 +2552,30 @@
       </c>
     </row>
     <row r="41" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="47">
+      <c r="B41" s="46">
         <v>37</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="52">
+      <c r="D41" s="51">
         <v>1.54</v>
       </c>
-      <c r="E41" s="42">
+      <c r="E41" s="41">
         <f t="shared" si="5"/>
         <v>0.64935064935064934</v>
       </c>
-      <c r="F41" s="56">
+      <c r="F41" s="54">
         <f t="shared" si="6"/>
         <v>0.44935064935064933</v>
       </c>
-      <c r="G41" s="69">
+      <c r="G41" s="67">
         <v>2.2400000000000002</v>
       </c>
-      <c r="H41" s="73">
-        <v>1</v>
-      </c>
-      <c r="I41" s="73" t="s">
+      <c r="H41" s="71">
+        <v>1</v>
+      </c>
+      <c r="I41" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J41" s="28">
@@ -2549,31 +2588,31 @@
       </c>
     </row>
     <row r="42" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="47">
+      <c r="B42" s="46">
         <v>38</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="51">
         <v>1.7</v>
       </c>
-      <c r="E42" s="42">
+      <c r="E42" s="41">
         <f t="shared" si="5"/>
         <v>0.58823529411764708</v>
       </c>
-      <c r="F42" s="56">
+      <c r="F42" s="54">
         <f t="shared" si="6"/>
         <v>0.38823529411764707</v>
       </c>
-      <c r="G42" s="69">
+      <c r="G42" s="67">
         <f t="shared" si="13"/>
         <v>2.5757575757575757</v>
       </c>
-      <c r="H42" s="73">
-        <v>1</v>
-      </c>
-      <c r="I42" s="73" t="s">
+      <c r="H42" s="71">
+        <v>1</v>
+      </c>
+      <c r="I42" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J42" s="28">
@@ -2586,31 +2625,31 @@
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="47">
+      <c r="B43" s="46">
         <v>39</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="52">
+      <c r="D43" s="51">
         <v>1.0900000000000001</v>
       </c>
-      <c r="E43" s="42">
+      <c r="E43" s="41">
         <f t="shared" si="5"/>
         <v>0.9174311926605504</v>
       </c>
-      <c r="F43" s="56">
+      <c r="F43" s="54">
         <f t="shared" si="6"/>
         <v>0.71743119266055033</v>
       </c>
-      <c r="G43" s="69">
+      <c r="G43" s="67">
         <f t="shared" si="13"/>
         <v>1.3938618925831205</v>
       </c>
-      <c r="H43" s="73">
-        <v>0</v>
-      </c>
-      <c r="I43" s="73" t="s">
+      <c r="H43" s="71">
+        <v>0</v>
+      </c>
+      <c r="I43" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J43" s="26">
@@ -2623,31 +2662,31 @@
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="47">
+      <c r="B44" s="46">
         <v>40</v>
       </c>
-      <c r="C44" s="64" t="s">
+      <c r="C44" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="51">
         <v>1.28</v>
       </c>
-      <c r="E44" s="42">
+      <c r="E44" s="41">
         <f t="shared" si="5"/>
         <v>0.78125</v>
       </c>
-      <c r="F44" s="56">
+      <c r="F44" s="54">
         <f t="shared" si="6"/>
         <v>0.58125000000000004</v>
       </c>
-      <c r="G44" s="69">
+      <c r="G44" s="67">
         <f t="shared" si="13"/>
         <v>1.7204301075268815</v>
       </c>
-      <c r="H44" s="73">
-        <v>1</v>
-      </c>
-      <c r="I44" s="73" t="s">
+      <c r="H44" s="71">
+        <v>1</v>
+      </c>
+      <c r="I44" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J44" s="26">
@@ -2660,31 +2699,31 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="47">
+      <c r="B45" s="46">
         <v>41</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="51">
         <v>1.64</v>
       </c>
-      <c r="E45" s="42">
+      <c r="E45" s="41">
         <f t="shared" si="5"/>
         <v>0.6097560975609756</v>
       </c>
-      <c r="F45" s="56">
+      <c r="F45" s="54">
         <f t="shared" si="6"/>
         <v>0.40975609756097559</v>
       </c>
-      <c r="G45" s="69">
+      <c r="G45" s="67">
         <f t="shared" si="13"/>
         <v>2.4404761904761907</v>
       </c>
-      <c r="H45" s="73">
-        <v>1</v>
-      </c>
-      <c r="I45" s="73" t="s">
+      <c r="H45" s="71">
+        <v>1</v>
+      </c>
+      <c r="I45" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J45" s="26">
@@ -2697,31 +2736,31 @@
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="47">
+      <c r="B46" s="46">
         <v>42</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="51">
         <v>1.2</v>
       </c>
-      <c r="E46" s="42">
+      <c r="E46" s="41">
         <f t="shared" si="5"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F46" s="56">
+      <c r="F46" s="54">
         <f t="shared" si="6"/>
         <v>0.6333333333333333</v>
       </c>
-      <c r="G46" s="69">
+      <c r="G46" s="67">
         <f t="shared" si="13"/>
         <v>1.5789473684210527</v>
       </c>
-      <c r="H46" s="73">
-        <v>0</v>
-      </c>
-      <c r="I46" s="73" t="s">
+      <c r="H46" s="71">
+        <v>0</v>
+      </c>
+      <c r="I46" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J46" s="26">
@@ -2734,31 +2773,31 @@
       </c>
     </row>
     <row r="47" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="47">
+      <c r="B47" s="46">
         <v>43</v>
       </c>
-      <c r="C47" s="64" t="s">
+      <c r="C47" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="51">
         <v>1.61</v>
       </c>
-      <c r="E47" s="42">
+      <c r="E47" s="41">
         <f t="shared" si="5"/>
         <v>0.6211180124223602</v>
       </c>
-      <c r="F47" s="56">
+      <c r="F47" s="54">
         <f t="shared" si="6"/>
         <v>0.42111801242236019</v>
       </c>
-      <c r="G47" s="69">
+      <c r="G47" s="67">
         <f t="shared" si="13"/>
         <v>2.3746312684365787</v>
       </c>
-      <c r="H47" s="73">
-        <v>0</v>
-      </c>
-      <c r="I47" s="73" t="s">
+      <c r="H47" s="71">
+        <v>0</v>
+      </c>
+      <c r="I47" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J47" s="26">
@@ -2771,68 +2810,68 @@
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="65">
+      <c r="B48" s="63">
         <v>44</v>
       </c>
-      <c r="C48" s="57" t="s">
+      <c r="C48" s="55" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="23">
         <v>1.76</v>
       </c>
-      <c r="E48" s="41">
+      <c r="E48" s="40">
         <f t="shared" ref="E48:E56" si="17">1/D48</f>
         <v>0.56818181818181823</v>
       </c>
-      <c r="F48" s="60">
+      <c r="F48" s="58">
         <f t="shared" ref="F48:F56" si="18">E48-0.2</f>
         <v>0.36818181818181822</v>
       </c>
-      <c r="G48" s="68">
+      <c r="G48" s="66">
         <f t="shared" ref="G48:G56" si="19">1/F48</f>
         <v>2.716049382716049</v>
       </c>
-      <c r="H48" s="77">
-        <v>1</v>
-      </c>
-      <c r="I48" s="77" t="s">
+      <c r="H48" s="75">
+        <v>1</v>
+      </c>
+      <c r="I48" s="75" t="s">
         <v>7</v>
       </c>
       <c r="J48" s="24">
-        <f t="shared" ref="J48:J57" si="20">IF(H48=0,0,IF(I48="WON",(G48-1)*0.94,-1))</f>
+        <f t="shared" ref="J48:J56" si="20">IF(H48=0,0,IF(I48="WON",(G48-1)*0.94,-1))</f>
         <v>1.6130864197530861</v>
       </c>
       <c r="K48" s="25">
-        <f t="shared" ref="K48:K57" si="21">J48*J$3</f>
+        <f t="shared" ref="K48:K56" si="21">J48*J$3</f>
         <v>89.606950617283928</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="66">
+      <c r="B49" s="64">
         <v>45</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="52">
+      <c r="D49" s="51">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E49" s="42">
+      <c r="E49" s="41">
         <f t="shared" si="17"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="F49" s="56">
+      <c r="F49" s="54">
         <f t="shared" si="18"/>
         <v>0.70909090909090899</v>
       </c>
-      <c r="G49" s="69">
+      <c r="G49" s="67">
         <f t="shared" si="19"/>
         <v>1.4102564102564104</v>
       </c>
-      <c r="H49" s="73">
-        <v>0</v>
-      </c>
-      <c r="I49" s="73" t="s">
+      <c r="H49" s="71">
+        <v>0</v>
+      </c>
+      <c r="I49" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J49" s="26">
@@ -2845,30 +2884,30 @@
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="66">
+      <c r="B50" s="64">
         <v>46</v>
       </c>
-      <c r="C50" s="44" t="s">
+      <c r="C50" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="51">
         <v>1.93</v>
       </c>
-      <c r="E50" s="42">
+      <c r="E50" s="41">
         <f t="shared" si="17"/>
         <v>0.5181347150259068</v>
       </c>
-      <c r="F50" s="56">
+      <c r="F50" s="54">
         <f t="shared" si="18"/>
         <v>0.31813471502590679</v>
       </c>
-      <c r="G50" s="69">
+      <c r="G50" s="67">
         <v>3.15</v>
       </c>
-      <c r="H50" s="73">
-        <v>1</v>
-      </c>
-      <c r="I50" s="73" t="s">
+      <c r="H50" s="71">
+        <v>1</v>
+      </c>
+      <c r="I50" s="71" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="26">
@@ -2881,31 +2920,31 @@
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="66">
+      <c r="B51" s="64">
         <v>47</v>
       </c>
-      <c r="C51" s="44" t="s">
+      <c r="C51" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="52">
+      <c r="D51" s="51">
         <v>1.41</v>
       </c>
-      <c r="E51" s="42">
+      <c r="E51" s="41">
         <f t="shared" si="17"/>
         <v>0.70921985815602839</v>
       </c>
-      <c r="F51" s="56">
+      <c r="F51" s="54">
         <f t="shared" si="18"/>
         <v>0.50921985815602833</v>
       </c>
-      <c r="G51" s="69">
+      <c r="G51" s="67">
         <f t="shared" si="19"/>
         <v>1.9637883008356547</v>
       </c>
-      <c r="H51" s="73">
-        <v>1</v>
-      </c>
-      <c r="I51" s="73" t="s">
+      <c r="H51" s="71">
+        <v>1</v>
+      </c>
+      <c r="I51" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J51" s="26">
@@ -2918,30 +2957,30 @@
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B52" s="66">
+      <c r="B52" s="64">
         <v>48</v>
       </c>
-      <c r="C52" s="44" t="s">
+      <c r="C52" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="D52" s="52">
+      <c r="D52" s="51">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E52" s="42">
+      <c r="E52" s="41">
         <f t="shared" si="17"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F52" s="56">
+      <c r="F52" s="54">
         <f t="shared" si="18"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G52" s="69">
+      <c r="G52" s="67">
         <v>1.45</v>
       </c>
-      <c r="H52" s="73">
-        <v>1</v>
-      </c>
-      <c r="I52" s="73" t="s">
+      <c r="H52" s="71">
+        <v>1</v>
+      </c>
+      <c r="I52" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J52" s="26">
@@ -2954,31 +2993,31 @@
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="66">
+      <c r="B53" s="64">
         <v>49</v>
       </c>
-      <c r="C53" s="44" t="s">
+      <c r="C53" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="51">
         <v>1.45</v>
       </c>
-      <c r="E53" s="42">
+      <c r="E53" s="41">
         <f t="shared" si="17"/>
         <v>0.68965517241379315</v>
       </c>
-      <c r="F53" s="56">
+      <c r="F53" s="54">
         <f t="shared" si="18"/>
         <v>0.48965517241379314</v>
       </c>
-      <c r="G53" s="69">
+      <c r="G53" s="67">
         <f t="shared" si="19"/>
         <v>2.0422535211267605</v>
       </c>
-      <c r="H53" s="73">
-        <v>1</v>
-      </c>
-      <c r="I53" s="73" t="s">
+      <c r="H53" s="71">
+        <v>1</v>
+      </c>
+      <c r="I53" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J53" s="26">
@@ -2991,30 +3030,30 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B54" s="66">
+      <c r="B54" s="64">
         <v>50</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="C54" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D54" s="52">
+      <c r="D54" s="51">
         <v>1.51</v>
       </c>
-      <c r="E54" s="42">
+      <c r="E54" s="41">
         <f t="shared" si="17"/>
         <v>0.66225165562913912</v>
       </c>
-      <c r="F54" s="56">
+      <c r="F54" s="54">
         <f t="shared" si="18"/>
         <v>0.46225165562913911</v>
       </c>
-      <c r="G54" s="69">
+      <c r="G54" s="67">
         <v>2.17</v>
       </c>
-      <c r="H54" s="73">
-        <v>0</v>
-      </c>
-      <c r="I54" s="73" t="s">
+      <c r="H54" s="71">
+        <v>0</v>
+      </c>
+      <c r="I54" s="71" t="s">
         <v>7</v>
       </c>
       <c r="J54" s="26">
@@ -3027,24 +3066,24 @@
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B55" s="66">
+      <c r="B55" s="64">
         <v>51</v>
       </c>
-      <c r="C55" s="44" t="s">
+      <c r="C55" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="51">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E55" s="42">
+      <c r="E55" s="41">
         <f t="shared" si="17"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F55" s="56">
+      <c r="F55" s="54">
         <f t="shared" si="18"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G55" s="69">
+      <c r="G55" s="67">
         <f t="shared" si="19"/>
         <v>1.4432989690721649</v>
       </c>
@@ -3064,31 +3103,31 @@
       </c>
     </row>
     <row r="56" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="67">
+      <c r="B56" s="65">
         <v>52</v>
       </c>
-      <c r="C56" s="45" t="s">
+      <c r="C56" s="44" t="s">
         <v>48</v>
       </c>
       <c r="D56" s="9">
         <v>1.17</v>
       </c>
-      <c r="E56" s="43">
+      <c r="E56" s="42">
         <f t="shared" si="17"/>
         <v>0.85470085470085477</v>
       </c>
-      <c r="F56" s="61">
+      <c r="F56" s="59">
         <f t="shared" si="18"/>
         <v>0.65470085470085482</v>
       </c>
-      <c r="G56" s="69">
+      <c r="G56" s="67">
         <f t="shared" si="19"/>
         <v>1.5274151436031329</v>
       </c>
-      <c r="H56" s="79">
-        <v>1</v>
-      </c>
-      <c r="I56" s="79" t="s">
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J56" s="26">
@@ -3101,31 +3140,31 @@
       </c>
     </row>
     <row r="57" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="46">
+      <c r="B57" s="45">
         <v>53</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="77">
+      <c r="D57" s="75">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E57" s="43">
+      <c r="E57" s="42">
         <f t="shared" ref="E57:E65" si="22">1/D57</f>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F57" s="61">
+      <c r="F57" s="59">
         <f t="shared" ref="F57:F65" si="23">E57-0.2</f>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G57" s="68">
+      <c r="G57" s="66">
         <f t="shared" ref="G57:G65" si="24">1/F57</f>
         <v>1.4432989690721649</v>
       </c>
       <c r="H57" s="23">
         <v>1</v>
       </c>
-      <c r="I57" s="62" t="s">
+      <c r="I57" s="60" t="s">
         <v>10</v>
       </c>
       <c r="J57" s="15">
@@ -3138,34 +3177,34 @@
       </c>
     </row>
     <row r="58" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="47">
+      <c r="B58" s="46">
         <v>54</v>
       </c>
-      <c r="C58" s="83" t="s">
+      <c r="C58" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="79">
+      <c r="D58" s="1">
         <v>1.18</v>
       </c>
-      <c r="E58" s="43">
+      <c r="E58" s="42">
         <f t="shared" si="22"/>
         <v>0.84745762711864414</v>
       </c>
-      <c r="F58" s="61">
+      <c r="F58" s="59">
         <f t="shared" si="23"/>
         <v>0.64745762711864407</v>
       </c>
-      <c r="G58" s="69">
+      <c r="G58" s="67">
         <f t="shared" si="24"/>
         <v>1.544502617801047</v>
       </c>
-      <c r="H58" s="82">
-        <v>1</v>
-      </c>
-      <c r="I58" s="74" t="s">
-        <v>7</v>
-      </c>
-      <c r="J58" s="80">
+      <c r="H58" s="51">
+        <v>1</v>
+      </c>
+      <c r="I58" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J58" s="77">
         <f t="shared" si="25"/>
         <v>0.51183246073298416</v>
       </c>
@@ -3175,34 +3214,34 @@
       </c>
     </row>
     <row r="59" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="47">
+      <c r="B59" s="46">
         <v>55</v>
       </c>
-      <c r="C59" s="83" t="s">
+      <c r="C59" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="79">
+      <c r="D59" s="1">
         <v>1.25</v>
       </c>
-      <c r="E59" s="43">
+      <c r="E59" s="42">
         <f t="shared" si="22"/>
         <v>0.8</v>
       </c>
-      <c r="F59" s="61">
+      <c r="F59" s="59">
         <f t="shared" si="23"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G59" s="69">
+      <c r="G59" s="67">
         <f t="shared" si="24"/>
         <v>1.6666666666666665</v>
       </c>
-      <c r="H59" s="82">
-        <v>0</v>
-      </c>
-      <c r="I59" s="74" t="s">
-        <v>7</v>
-      </c>
-      <c r="J59" s="80">
+      <c r="H59" s="51">
+        <v>0</v>
+      </c>
+      <c r="I59" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J59" s="77">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -3212,129 +3251,144 @@
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="47">
+      <c r="B60" s="46">
         <v>56</v>
       </c>
-      <c r="C60" s="83" t="s">
+      <c r="C60" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="79">
+      <c r="D60" s="1">
         <v>1.53</v>
       </c>
-      <c r="E60" s="43">
+      <c r="E60" s="42">
         <f t="shared" si="22"/>
         <v>0.65359477124183007</v>
       </c>
-      <c r="F60" s="61">
+      <c r="F60" s="59">
         <f t="shared" si="23"/>
         <v>0.45359477124183006</v>
       </c>
-      <c r="G60" s="69">
+      <c r="G60" s="67">
         <f t="shared" si="24"/>
         <v>2.2046109510086453</v>
       </c>
-      <c r="H60" s="82"/>
-      <c r="I60" s="74"/>
-      <c r="J60" s="80">
+      <c r="H60" s="51">
+        <v>1</v>
+      </c>
+      <c r="I60" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J60" s="77">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1.1323342939481265</v>
       </c>
       <c r="K60" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>62.90117002881842</v>
       </c>
     </row>
     <row r="61" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="47">
+      <c r="B61" s="46">
         <v>57</v>
       </c>
-      <c r="C61" s="83" t="s">
+      <c r="C61" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="79">
+      <c r="D61" s="1">
         <v>1.49</v>
       </c>
-      <c r="E61" s="43">
+      <c r="E61" s="42">
         <f t="shared" si="22"/>
         <v>0.67114093959731547</v>
       </c>
-      <c r="F61" s="61">
+      <c r="F61" s="59">
         <f t="shared" si="23"/>
         <v>0.47114093959731546</v>
       </c>
-      <c r="G61" s="69">
+      <c r="G61" s="67">
         <f t="shared" si="24"/>
         <v>2.1225071225071224</v>
       </c>
-      <c r="H61" s="82"/>
-      <c r="I61" s="74"/>
-      <c r="J61" s="80">
+      <c r="H61" s="51">
+        <v>1</v>
+      </c>
+      <c r="I61" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="J61" s="77">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K61" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="62" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="47">
+      <c r="B62" s="46">
         <v>58</v>
       </c>
-      <c r="C62" s="83" t="s">
+      <c r="C62" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="79">
-        <v>1.69</v>
-      </c>
-      <c r="E62" s="43">
+      <c r="D62" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="E62" s="42">
         <f t="shared" si="22"/>
-        <v>0.59171597633136097</v>
-      </c>
-      <c r="F62" s="61">
+        <v>0.57471264367816088</v>
+      </c>
+      <c r="F62" s="59">
         <f t="shared" si="23"/>
-        <v>0.39171597633136096</v>
-      </c>
-      <c r="G62" s="69">
-        <f t="shared" si="24"/>
-        <v>2.5528700906344408</v>
-      </c>
-      <c r="H62" s="82"/>
-      <c r="I62" s="74"/>
-      <c r="J62" s="80">
+        <v>0.37471264367816087</v>
+      </c>
+      <c r="G62" s="67">
+        <v>2.68</v>
+      </c>
+      <c r="H62" s="51">
+        <v>1</v>
+      </c>
+      <c r="I62" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="77">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K62" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="63" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="47">
+      <c r="B63" s="46">
         <v>59</v>
       </c>
-      <c r="C63" s="83" t="s">
+      <c r="C63" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="79">
+      <c r="D63" s="1">
         <v>1.21</v>
       </c>
-      <c r="E63" s="43">
+      <c r="E63" s="42">
         <f t="shared" si="22"/>
         <v>0.82644628099173556</v>
       </c>
-      <c r="F63" s="61">
+      <c r="F63" s="59">
         <f t="shared" si="23"/>
         <v>0.62644628099173549</v>
       </c>
-      <c r="G63" s="69">
+      <c r="G63" s="67">
         <f t="shared" si="24"/>
         <v>1.5963060686015833</v>
       </c>
-      <c r="H63" s="82"/>
-      <c r="I63" s="74"/>
-      <c r="J63" s="80">
+      <c r="H63" s="51">
+        <v>0</v>
+      </c>
+      <c r="I63" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J63" s="77">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -3344,30 +3398,34 @@
       </c>
     </row>
     <row r="64" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="47">
+      <c r="B64" s="46">
         <v>60</v>
       </c>
-      <c r="C64" s="83" t="s">
+      <c r="C64" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="79">
+      <c r="D64" s="1">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E64" s="43">
+      <c r="E64" s="42">
         <f t="shared" si="22"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F64" s="61">
+      <c r="F64" s="59">
         <f t="shared" si="23"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G64" s="69">
+      <c r="G64" s="67">
         <f t="shared" si="24"/>
         <v>1.4432989690721649</v>
       </c>
-      <c r="H64" s="82"/>
-      <c r="I64" s="74"/>
-      <c r="J64" s="80">
+      <c r="H64" s="51">
+        <v>0</v>
+      </c>
+      <c r="I64" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J64" s="77">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -3377,37 +3435,49 @@
       </c>
     </row>
     <row r="65" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="48">
+      <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="84" t="s">
+      <c r="C65" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="D65" s="78">
+      <c r="D65" s="76">
         <v>1.28</v>
       </c>
-      <c r="E65" s="43">
+      <c r="E65" s="42">
         <f t="shared" si="22"/>
         <v>0.78125</v>
       </c>
-      <c r="F65" s="61">
+      <c r="F65" s="59">
         <f t="shared" si="23"/>
         <v>0.58125000000000004</v>
       </c>
-      <c r="G65" s="70">
+      <c r="G65" s="68">
         <f t="shared" si="24"/>
         <v>1.7204301075268815</v>
       </c>
-      <c r="H65" s="9"/>
-      <c r="I65" s="76"/>
-      <c r="J65" s="81">
+      <c r="H65" s="9">
+        <v>1</v>
+      </c>
+      <c r="I65" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="J65" s="78">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K65" s="29">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B66"/>
+      <c r="C66"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B67"/>
+      <c r="C67"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3417,7 +3487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L18"/>
+  <dimension ref="B2:L37"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -3475,14 +3545,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="83">
         <v>1.78</v>
       </c>
       <c r="E5" s="20">
@@ -3497,13 +3567,13 @@
         <f>1/F5</f>
         <v>2.7639751552795029</v>
       </c>
-      <c r="H5" s="30">
-        <v>1</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="15">
+      <c r="H5" s="83">
+        <v>1</v>
+      </c>
+      <c r="I5" s="83" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="24">
         <f>IF(H5=0,0,IF(I5="WON",(G5-1),-1))</f>
         <v>1.7639751552795029</v>
       </c>
@@ -3511,204 +3581,204 @@
         <f>J5*J$3*0.94-0.21</f>
         <v>91.8994906832298</v>
       </c>
-      <c r="L5" s="51"/>
-    </row>
-    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="2">
+      <c r="L5" s="50"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="7">
         <v>1.56</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="81">
         <f>1/D6</f>
         <v>0.64102564102564097</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="6">
         <f>E6-0.2</f>
         <v>0.44102564102564096</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="52">
         <v>2.2799999999999998</v>
       </c>
-      <c r="H6" s="30">
-        <v>1</v>
-      </c>
-      <c r="I6" s="31" t="s">
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="26">
         <f>IF(H6=0,0,IF(I6="WON",(G6-1),-1))</f>
         <v>-1</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="27">
         <f>J6*J$3</f>
         <v>-55.55</v>
       </c>
-      <c r="L6" s="51"/>
-    </row>
-    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="2">
+      <c r="L6" s="50"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="E7" s="20">
-        <f t="shared" ref="E7:E18" si="0">1/D7</f>
+      <c r="E7" s="81">
+        <f t="shared" ref="E7:E19" si="0">1/D7</f>
         <v>0.9009009009009008</v>
       </c>
-      <c r="F7" s="21">
-        <f t="shared" ref="F7:F18" si="1">E7-0.2</f>
+      <c r="F7" s="6">
+        <f t="shared" ref="F7:F19" si="1">E7-0.2</f>
         <v>0.70090090090090085</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="52">
         <f t="shared" ref="G7:G8" si="2">1/F7</f>
         <v>1.4267352185089976</v>
       </c>
-      <c r="H7" s="30">
-        <v>0</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="15">
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="26">
         <f t="shared" ref="J7:J8" si="3">IF(H7=0,0,IF(I7="WON",(G7-1),-1))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="27">
         <f t="shared" ref="K7:K10" si="4">J7*J$3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="7">
         <v>1.42</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="81">
         <f t="shared" si="0"/>
         <v>0.70422535211267612</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="6">
         <f t="shared" si="1"/>
         <v>0.50422535211267605</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="52">
         <f t="shared" si="2"/>
         <v>1.9832402234636872</v>
       </c>
-      <c r="H8" s="30">
-        <v>0</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="15">
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="7">
         <v>1.46</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="81">
         <f t="shared" si="0"/>
         <v>0.68493150684931503</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="6">
         <f t="shared" si="1"/>
         <v>0.48493150684931502</v>
       </c>
-      <c r="G9" s="22">
-        <f t="shared" ref="G9:G18" si="5">1/F9</f>
+      <c r="G9" s="52">
+        <f t="shared" ref="G9:G19" si="5">1/F9</f>
         <v>2.0621468926553677</v>
       </c>
-      <c r="H9" s="30">
-        <v>0</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="15">
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="26">
         <f t="shared" ref="J9:J10" si="6">IF(H9=0,0,IF(I9="WON",(G9-1),-1))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="7">
         <v>1.06</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="81">
         <f t="shared" si="0"/>
         <v>0.94339622641509424</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="6">
         <f t="shared" si="1"/>
         <v>0.74339622641509417</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="52">
         <f t="shared" si="5"/>
         <v>1.3451776649746197</v>
       </c>
-      <c r="H10" s="30">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="J10" s="15">
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="85" t="s">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>7</v>
+      </c>
+      <c r="C11" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="7">
         <v>1.45</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="81">
         <f t="shared" si="0"/>
         <v>0.68965517241379315</v>
       </c>
@@ -3716,31 +3786,36 @@
         <f t="shared" si="1"/>
         <v>0.48965517241379314</v>
       </c>
-      <c r="G11" s="88">
+      <c r="G11" s="52">
         <f t="shared" si="5"/>
         <v>2.0422535211267605</v>
       </c>
-      <c r="H11" s="89"/>
-      <c r="J11" s="15">
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="26">
         <f t="shared" ref="J11:J15" si="7">IF(H11=0,0,IF(I11="WON",(G11-1),-1))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="27">
         <f t="shared" ref="K11:K15" si="8">J11*J$3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
         <v>8</v>
       </c>
-      <c r="C12" s="85" t="s">
+      <c r="C12" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="7">
         <v>1.36</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="81">
         <f t="shared" si="0"/>
         <v>0.73529411764705876</v>
       </c>
@@ -3748,30 +3823,36 @@
         <f t="shared" si="1"/>
         <v>0.5352941176470587</v>
       </c>
-      <c r="G12" s="88">
+      <c r="G12" s="52">
         <f t="shared" si="5"/>
         <v>1.8681318681318686</v>
       </c>
-      <c r="J12" s="15">
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" s="26">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="27">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
         <v>9</v>
       </c>
-      <c r="C13" s="85" t="s">
+      <c r="C13" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="7">
         <v>1.22</v>
       </c>
-      <c r="E13" s="87">
+      <c r="E13" s="81">
         <f t="shared" si="0"/>
         <v>0.81967213114754101</v>
       </c>
@@ -3779,30 +3860,36 @@
         <f t="shared" si="1"/>
         <v>0.61967213114754105</v>
       </c>
-      <c r="G13" s="88">
+      <c r="G13" s="52">
         <f t="shared" si="5"/>
         <v>1.6137566137566135</v>
       </c>
-      <c r="J13" s="15">
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" s="26">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="27">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="7">
         <v>1.89</v>
       </c>
-      <c r="E14" s="87">
+      <c r="E14" s="81">
         <f t="shared" si="0"/>
         <v>0.52910052910052918</v>
       </c>
@@ -3810,29 +3897,35 @@
         <f t="shared" si="1"/>
         <v>0.32910052910052917</v>
       </c>
-      <c r="G14" s="88">
+      <c r="G14" s="52">
         <v>3.05</v>
       </c>
-      <c r="J14" s="15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="25">
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="26">
+        <f>IF(H14=0,0,IF(I14="WON",(G14*0.94-1),-1))</f>
+        <v>1.8669999999999995</v>
+      </c>
+      <c r="K14" s="27">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>103.71184999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="85" t="s">
+      <c r="C15" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="7">
         <v>1.84</v>
       </c>
-      <c r="E15" s="87">
+      <c r="E15" s="81">
         <f t="shared" si="0"/>
         <v>0.54347826086956519</v>
       </c>
@@ -3840,29 +3933,35 @@
         <f t="shared" si="1"/>
         <v>0.34347826086956518</v>
       </c>
-      <c r="G15" s="88">
+      <c r="G15" s="52">
         <v>2.92</v>
       </c>
-      <c r="J15" s="15">
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="25">
+        <v>-1</v>
+      </c>
+      <c r="K15" s="27">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>12</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c r="E16" s="87">
+      <c r="E16" s="81">
         <f t="shared" si="0"/>
         <v>0.9174311926605504</v>
       </c>
@@ -3870,30 +3969,36 @@
         <f t="shared" si="1"/>
         <v>0.71743119266055033</v>
       </c>
-      <c r="G16" s="88">
+      <c r="G16" s="52">
         <f t="shared" si="5"/>
         <v>1.3938618925831205</v>
       </c>
-      <c r="J16" s="15">
-        <f t="shared" ref="J16" si="9">IF(H16=0,0,IF(I16="WON",(G16-1),-1))</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="25">
-        <f t="shared" ref="K16" si="10">J16*J$3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="26">
+        <f>IF(H16=0,0,IF(I16="WON",(G16*0.94-1),-1))</f>
+        <v>0.31023017902813321</v>
+      </c>
+      <c r="K16" s="27">
+        <f t="shared" ref="K16" si="9">J16*J$3</f>
+        <v>17.233286445012798</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>13</v>
       </c>
-      <c r="C17" s="85" t="s">
+      <c r="C17" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="7">
         <v>1.84</v>
       </c>
-      <c r="E17" s="90">
+      <c r="E17" s="81">
         <f t="shared" si="0"/>
         <v>0.54347826086956519</v>
       </c>
@@ -3901,29 +4006,35 @@
         <f t="shared" si="1"/>
         <v>0.34347826086956518</v>
       </c>
-      <c r="G17" s="88">
+      <c r="G17" s="52">
         <v>2.92</v>
       </c>
-      <c r="J17" s="15">
-        <f t="shared" ref="J17:J18" si="11">IF(H17=0,0,IF(I17="WON",(G17-1),-1))</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="25">
-        <f t="shared" ref="K17:K18" si="12">J17*J$3</f>
-        <v>0</v>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="26">
+        <f t="shared" ref="J17" si="10">IF(H17=0,0,IF(I17="WON",(G17-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K17" s="27">
+        <f t="shared" ref="K17:K19" si="11">J17*J$3</f>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>14</v>
       </c>
-      <c r="C18" s="85" t="s">
+      <c r="C18" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="7">
         <v>1.79</v>
       </c>
-      <c r="E18" s="90">
+      <c r="E18" s="81">
         <f t="shared" si="0"/>
         <v>0.55865921787709494</v>
       </c>
@@ -3931,16 +4042,708 @@
         <f t="shared" si="1"/>
         <v>0.35865921787709493</v>
       </c>
-      <c r="G18" s="88">
+      <c r="G18" s="52">
         <v>2.8</v>
       </c>
-      <c r="J18" s="15">
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="26">
+        <f>IF(H18=0,0,IF(I18="WON",(G18*0.94-1),-1))</f>
+        <v>1.6319999999999997</v>
+      </c>
+      <c r="K18" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="25">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>90.657599999999974</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>15</v>
+      </c>
+      <c r="C19" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="E19" s="81">
+        <f t="shared" si="0"/>
+        <v>0.58139534883720934</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="1"/>
+        <v>0.38139534883720932</v>
+      </c>
+      <c r="G19" s="52">
+        <f t="shared" si="5"/>
+        <v>2.6219512195121948</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" s="26">
+        <f>IF(H19=0,0,IF(I19="WON",(G19*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K19" s="27">
+        <f t="shared" si="11"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>16</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.54</v>
+      </c>
+      <c r="E20" s="81">
+        <f t="shared" ref="E20" si="12">1/D20</f>
+        <v>0.64935064935064934</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" ref="F20" si="13">E20-0.2</f>
+        <v>0.44935064935064933</v>
+      </c>
+      <c r="G20" s="52">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J20" s="26">
+        <f>IF(H20=0,0,IF(I20="WON",(G20*0.94-1),-1))</f>
+        <v>1.1055999999999999</v>
+      </c>
+      <c r="K20" s="27">
+        <f t="shared" ref="K20" si="14">J20*J$3</f>
+        <v>61.416079999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>17</v>
+      </c>
+      <c r="C21" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="E21" s="81">
+        <f t="shared" ref="E21:E37" si="15">1/D21</f>
+        <v>0.65789473684210531</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" ref="F21:F37" si="16">E21-0.2</f>
+        <v>0.4578947368421053</v>
+      </c>
+      <c r="G21" s="52">
+        <f t="shared" ref="G21:G29" si="17">1/F21</f>
+        <v>2.1839080459770113</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="26">
+        <f t="shared" ref="J21:J30" si="18">IF(H21=0,0,IF(I21="WON",(G21*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K21" s="27">
+        <f t="shared" ref="K21:K30" si="19">J21*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <v>18</v>
+      </c>
+      <c r="C22" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="E22" s="81">
+        <f t="shared" si="15"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="16"/>
+        <v>0.37142857142857139</v>
+      </c>
+      <c r="G22" s="52">
+        <v>2.7</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="26">
+        <f t="shared" si="18"/>
+        <v>1.5379999999999998</v>
+      </c>
+      <c r="K22" s="27">
+        <f t="shared" si="19"/>
+        <v>85.43589999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <v>19</v>
+      </c>
+      <c r="C23" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="E23" s="81">
+        <f t="shared" si="15"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="16"/>
+        <v>0.51428571428571423</v>
+      </c>
+      <c r="G23" s="52">
+        <f t="shared" si="17"/>
+        <v>1.9444444444444446</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="26">
+        <f t="shared" si="18"/>
+        <v>-1</v>
+      </c>
+      <c r="K23" s="27">
+        <f t="shared" si="19"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>20</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="E24" s="81">
+        <f t="shared" si="15"/>
+        <v>0.76923076923076916</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="16"/>
+        <v>0.56923076923076921</v>
+      </c>
+      <c r="G24" s="52">
+        <f t="shared" si="17"/>
+        <v>1.7567567567567568</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="26">
+        <f t="shared" si="18"/>
+        <v>-1</v>
+      </c>
+      <c r="K24" s="27">
+        <f t="shared" si="19"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>21</v>
+      </c>
+      <c r="C25" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="E25" s="81">
+        <f t="shared" si="15"/>
+        <v>0.70422535211267612</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="16"/>
+        <v>0.50422535211267605</v>
+      </c>
+      <c r="G25" s="52">
+        <f t="shared" si="17"/>
+        <v>1.9832402234636872</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
+        <v>22</v>
+      </c>
+      <c r="C26" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="E26" s="81">
+        <f t="shared" si="15"/>
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="16"/>
+        <v>0.54074074074074074</v>
+      </c>
+      <c r="G26" s="52">
+        <f t="shared" si="17"/>
+        <v>1.8493150684931507</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J26" s="26">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>23</v>
+      </c>
+      <c r="C27" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="E27" s="81">
+        <f t="shared" si="15"/>
+        <v>0.61349693251533743</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="16"/>
+        <v>0.41349693251533742</v>
+      </c>
+      <c r="G27" s="52">
+        <f t="shared" si="17"/>
+        <v>2.4183976261127595</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J27" s="26">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="4">
+        <v>24</v>
+      </c>
+      <c r="C28" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="85">
+        <v>1.71</v>
+      </c>
+      <c r="E28" s="86">
+        <f t="shared" si="15"/>
+        <v>0.58479532163742687</v>
+      </c>
+      <c r="F28" s="10">
+        <f t="shared" si="16"/>
+        <v>0.38479532163742686</v>
+      </c>
+      <c r="G28" s="12">
+        <f t="shared" si="17"/>
+        <v>2.5987841945288759</v>
+      </c>
+      <c r="H28" s="76">
+        <v>1</v>
+      </c>
+      <c r="I28" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" s="28">
+        <f t="shared" si="18"/>
+        <v>-1</v>
+      </c>
+      <c r="K28" s="29">
+        <f t="shared" si="19"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>25</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.95</v>
+      </c>
+      <c r="E29" s="81">
+        <f t="shared" si="15"/>
+        <v>0.51282051282051289</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="16"/>
+        <v>0.31282051282051287</v>
+      </c>
+      <c r="G29" s="52">
+        <f t="shared" si="17"/>
+        <v>3.1967213114754092</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J29" s="26">
+        <f t="shared" si="18"/>
+        <v>2.0049180327868843</v>
+      </c>
+      <c r="K29" s="27">
+        <f t="shared" si="19"/>
+        <v>111.37319672131142</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
+        <v>26</v>
+      </c>
+      <c r="C30" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="E30" s="81">
+        <f t="shared" si="15"/>
+        <v>0.64102564102564097</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="16"/>
+        <v>0.44102564102564096</v>
+      </c>
+      <c r="G30" s="52">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J30" s="26">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="27">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="3">
+        <v>27</v>
+      </c>
+      <c r="C31" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2</v>
+      </c>
+      <c r="E31" s="81">
+        <f t="shared" si="15"/>
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="16"/>
+        <v>0.3</v>
+      </c>
+      <c r="G31" s="52">
+        <v>3.35</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J31" s="26">
+        <f t="shared" ref="J31" si="20">IF(H31=0,0,IF(I31="WON",(G31*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="27">
+        <f t="shared" ref="K31" si="21">J31*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
+        <v>28</v>
+      </c>
+      <c r="C32" s="80" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="E32" s="81">
+        <f t="shared" si="15"/>
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="16"/>
+        <v>0.55757575757575761</v>
+      </c>
+      <c r="G32" s="52">
+        <f t="shared" ref="G32:G36" si="22">1/F32</f>
+        <v>1.7934782608695652</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="26">
+        <f t="shared" ref="J32" si="23">IF(H32=0,0,IF(I32="WON",(G32*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="27">
+        <f t="shared" ref="K32" si="24">J32*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
+        <v>29</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="E33" s="81">
+        <f t="shared" si="15"/>
+        <v>0.55865921787709494</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="16"/>
+        <v>0.35865921787709493</v>
+      </c>
+      <c r="G33" s="52">
+        <v>2.8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J33" s="26">
+        <f t="shared" ref="J33" si="25">IF(H33=0,0,IF(I33="WON",(G33*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="27">
+        <f t="shared" ref="K33" si="26">J33*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="3">
+        <v>30</v>
+      </c>
+      <c r="C34" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2</v>
+      </c>
+      <c r="E34" s="81">
+        <f t="shared" si="15"/>
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="16"/>
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="52">
+        <v>3.35</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="26">
+        <f t="shared" ref="J34" si="27">IF(H34=0,0,IF(I34="WON",(G34*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K34" s="27">
+        <f t="shared" ref="K34" si="28">J34*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="3">
+        <v>31</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="E35" s="81">
+        <f t="shared" si="15"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="16"/>
+        <v>0.51428571428571423</v>
+      </c>
+      <c r="G35" s="52">
+        <f t="shared" si="22"/>
+        <v>1.9444444444444446</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="26">
+        <f t="shared" ref="J35" si="29">IF(H35=0,0,IF(I35="WON",(G35*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="27">
+        <f t="shared" ref="K35" si="30">J35*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="3">
+        <v>32</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="E36" s="81">
+        <f t="shared" si="15"/>
+        <v>0.65789473684210531</v>
+      </c>
+      <c r="F36" s="6">
+        <f t="shared" si="16"/>
+        <v>0.4578947368421053</v>
+      </c>
+      <c r="G36" s="52">
+        <f t="shared" si="22"/>
+        <v>2.1839080459770113</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J36" s="26">
+        <f t="shared" ref="J36" si="31">IF(H36=0,0,IF(I36="WON",(G36*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="27">
+        <f t="shared" ref="K36" si="32">J36*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="3">
+        <v>33</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="7">
+        <v>2</v>
+      </c>
+      <c r="E37" s="81">
+        <f t="shared" si="15"/>
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" si="16"/>
+        <v>0.3</v>
+      </c>
+      <c r="G37" s="52">
+        <v>3.35</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J37" s="26">
+        <f t="shared" ref="J37" si="33">IF(H37=0,0,IF(I37="WON",(G37*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K37" s="27">
+        <f t="shared" ref="K37" si="34">J37*J$3</f>
+        <v>-55.55</v>
       </c>
     </row>
   </sheetData>
@@ -3967,12 +4770,12 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="31" t="s">
         <v>28</v>
       </c>
       <c r="L3" s="7"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
     </row>
     <row r="4" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="13" t="s">
@@ -3984,13 +4787,13 @@
       <c r="D4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="32" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="33" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="17" t="s">
@@ -4013,19 +4816,19 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="36">
+      <c r="C5" s="53"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="35">
         <f t="shared" ref="J5:J6" si="0">IF(AND(I5&lt;=F5,I5&gt;=E5),0,IF(I5&lt;E5,MAX(I5-E5,D5-E5),MAX(F5-I5,F5-G5)))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="40"/>
-      <c r="L5" s="38">
+      <c r="K5" s="39"/>
+      <c r="L5" s="37">
         <f t="shared" ref="L5:L6" si="1">(H5+J5)*100-K5</f>
         <v>0</v>
       </c>
@@ -4034,19 +4837,19 @@
       <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="36">
+      <c r="C6" s="53"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="40"/>
-      <c r="L6" s="38">
+      <c r="K6" s="39"/>
+      <c r="L6" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380CA458-4864-4DD9-8C2D-7488E91583F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C7F6C9-2CD8-42A3-A2E7-C9906BA04DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="75">
   <si>
     <t>ID</t>
   </si>
@@ -4630,14 +4630,16 @@
       <c r="H34" s="1">
         <v>1</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J34" s="26">
         <f t="shared" ref="J34" si="27">IF(H34=0,0,IF(I34="WON",(G34*0.94-1),-1))</f>
-        <v>-1</v>
+        <v>2.149</v>
       </c>
       <c r="K34" s="27">
         <f t="shared" ref="K34" si="28">J34*J$3</f>
-        <v>-55.55</v>
+        <v>119.37694999999999</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C7F6C9-2CD8-42A3-A2E7-C9906BA04DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F837BF-F31C-40D5-898D-F7905AFBA1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
     <sheet name="Tennis" sheetId="2" r:id="rId2"/>
-    <sheet name="Options" sheetId="13" r:id="rId3"/>
+    <sheet name="Shares" sheetId="13" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>Sakkari</t>
+  </si>
+  <si>
+    <t>Bombers</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -811,9 +814,6 @@
     <xf numFmtId="2" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -834,6 +834,36 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1175,7 +1205,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K67"/>
+  <dimension ref="B2:K74"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -3106,17 +3136,17 @@
       <c r="B56" s="65">
         <v>52</v>
       </c>
-      <c r="C56" s="44" t="s">
+      <c r="C56" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="88">
         <v>1.17</v>
       </c>
-      <c r="E56" s="42">
+      <c r="E56" s="41">
         <f t="shared" si="17"/>
         <v>0.85470085470085477</v>
       </c>
-      <c r="F56" s="59">
+      <c r="F56" s="87">
         <f t="shared" si="18"/>
         <v>0.65470085470085482</v>
       </c>
@@ -3139,25 +3169,25 @@
         <v>27.540036553524786</v>
       </c>
     </row>
-    <row r="57" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="45">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="2">
         <v>53</v>
       </c>
-      <c r="C57" s="61" t="s">
+      <c r="C57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D57" s="75">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E57" s="42">
+      <c r="E57" s="40">
         <f t="shared" ref="E57:E65" si="22">1/D57</f>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F57" s="59">
+      <c r="F57" s="21">
         <f t="shared" ref="F57:F65" si="23">E57-0.2</f>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G57" s="66">
+      <c r="G57" s="91">
         <f t="shared" ref="G57:G65" si="24">1/F57</f>
         <v>1.4432989690721649</v>
       </c>
@@ -3176,25 +3206,25 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="58" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="46">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="3">
         <v>54</v>
       </c>
-      <c r="C58" s="62" t="s">
+      <c r="C58" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="86">
         <v>1.18</v>
       </c>
-      <c r="E58" s="42">
+      <c r="E58" s="41">
         <f t="shared" si="22"/>
         <v>0.84745762711864414</v>
       </c>
-      <c r="F58" s="59">
+      <c r="F58" s="6">
         <f t="shared" si="23"/>
         <v>0.64745762711864407</v>
       </c>
-      <c r="G58" s="67">
+      <c r="G58" s="90">
         <f t="shared" si="24"/>
         <v>1.544502617801047</v>
       </c>
@@ -3213,25 +3243,25 @@
         <v>28.432293193717268</v>
       </c>
     </row>
-    <row r="59" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="46">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B59" s="3">
         <v>55</v>
       </c>
-      <c r="C59" s="62" t="s">
+      <c r="C59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="86">
         <v>1.25</v>
       </c>
-      <c r="E59" s="42">
+      <c r="E59" s="41">
         <f t="shared" si="22"/>
         <v>0.8</v>
       </c>
-      <c r="F59" s="59">
+      <c r="F59" s="6">
         <f t="shared" si="23"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G59" s="67">
+      <c r="G59" s="90">
         <f t="shared" si="24"/>
         <v>1.6666666666666665</v>
       </c>
@@ -3250,25 +3280,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="46">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B60" s="3">
         <v>56</v>
       </c>
-      <c r="C60" s="62" t="s">
+      <c r="C60" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="86">
         <v>1.53</v>
       </c>
-      <c r="E60" s="42">
+      <c r="E60" s="41">
         <f t="shared" si="22"/>
         <v>0.65359477124183007</v>
       </c>
-      <c r="F60" s="59">
+      <c r="F60" s="6">
         <f t="shared" si="23"/>
         <v>0.45359477124183006</v>
       </c>
-      <c r="G60" s="67">
+      <c r="G60" s="90">
         <f t="shared" si="24"/>
         <v>2.2046109510086453</v>
       </c>
@@ -3287,25 +3317,25 @@
         <v>62.90117002881842</v>
       </c>
     </row>
-    <row r="61" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="46">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61" s="3">
         <v>57</v>
       </c>
-      <c r="C61" s="62" t="s">
+      <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="86">
         <v>1.49</v>
       </c>
-      <c r="E61" s="42">
+      <c r="E61" s="41">
         <f t="shared" si="22"/>
         <v>0.67114093959731547</v>
       </c>
-      <c r="F61" s="59">
+      <c r="F61" s="6">
         <f t="shared" si="23"/>
         <v>0.47114093959731546</v>
       </c>
-      <c r="G61" s="67">
+      <c r="G61" s="90">
         <f t="shared" si="24"/>
         <v>2.1225071225071224</v>
       </c>
@@ -3324,25 +3354,25 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="62" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="46">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B62" s="3">
         <v>58</v>
       </c>
-      <c r="C62" s="62" t="s">
+      <c r="C62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" s="86">
         <v>1.74</v>
       </c>
-      <c r="E62" s="42">
+      <c r="E62" s="41">
         <f t="shared" si="22"/>
         <v>0.57471264367816088</v>
       </c>
-      <c r="F62" s="59">
+      <c r="F62" s="6">
         <f t="shared" si="23"/>
         <v>0.37471264367816087</v>
       </c>
-      <c r="G62" s="67">
+      <c r="G62" s="90">
         <v>2.68</v>
       </c>
       <c r="H62" s="51">
@@ -3360,25 +3390,25 @@
         <v>-55.55</v>
       </c>
     </row>
-    <row r="63" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="46">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B63" s="3">
         <v>59</v>
       </c>
-      <c r="C63" s="62" t="s">
+      <c r="C63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="86">
         <v>1.21</v>
       </c>
-      <c r="E63" s="42">
+      <c r="E63" s="41">
         <f t="shared" si="22"/>
         <v>0.82644628099173556</v>
       </c>
-      <c r="F63" s="59">
+      <c r="F63" s="6">
         <f t="shared" si="23"/>
         <v>0.62644628099173549</v>
       </c>
-      <c r="G63" s="67">
+      <c r="G63" s="90">
         <f t="shared" si="24"/>
         <v>1.5963060686015833</v>
       </c>
@@ -3397,25 +3427,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="46">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="3">
         <v>60</v>
       </c>
-      <c r="C64" s="62" t="s">
+      <c r="C64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="86">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E64" s="42">
+      <c r="E64" s="41">
         <f t="shared" si="22"/>
         <v>0.89285714285714279</v>
       </c>
-      <c r="F64" s="59">
+      <c r="F64" s="6">
         <f t="shared" si="23"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G64" s="67">
+      <c r="G64" s="90">
         <f t="shared" si="24"/>
         <v>1.4432989690721649</v>
       </c>
@@ -3435,49 +3465,358 @@
       </c>
     </row>
     <row r="65" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="47">
+      <c r="B65" s="3">
         <v>61</v>
       </c>
-      <c r="C65" s="79" t="s">
+      <c r="C65" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D65" s="76">
+      <c r="D65" s="86">
         <v>1.28</v>
       </c>
-      <c r="E65" s="42">
+      <c r="E65" s="41">
         <f t="shared" si="22"/>
         <v>0.78125</v>
       </c>
-      <c r="F65" s="59">
+      <c r="F65" s="6">
         <f t="shared" si="23"/>
         <v>0.58125000000000004</v>
       </c>
-      <c r="G65" s="68">
+      <c r="G65" s="90">
         <f t="shared" si="24"/>
         <v>1.7204301075268815</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="88">
         <v>1</v>
       </c>
-      <c r="I65" s="74" t="s">
+      <c r="I65" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="J65" s="78">
+      <c r="J65" s="89">
         <f t="shared" si="25"/>
         <v>-1</v>
       </c>
-      <c r="K65" s="29">
+      <c r="K65" s="27">
         <f t="shared" si="26"/>
         <v>-55.55</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B66"/>
-      <c r="C66"/>
+      <c r="B66" s="63">
+        <v>62</v>
+      </c>
+      <c r="C66" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="75">
+        <v>1.62</v>
+      </c>
+      <c r="E66" s="40">
+        <f t="shared" ref="E66:E74" si="27">1/D66</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F66" s="58">
+        <f t="shared" ref="F66:F74" si="28">E66-0.2</f>
+        <v>0.41728395061728391</v>
+      </c>
+      <c r="G66" s="91">
+        <f t="shared" ref="G66:G74" si="29">1/F66</f>
+        <v>2.3964497041420123</v>
+      </c>
+      <c r="H66" s="23">
+        <v>1</v>
+      </c>
+      <c r="I66" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="J66" s="15">
+        <f t="shared" ref="J66:J74" si="30">IF(H66=0,0,IF(I66="WON",(G66-1)*0.94,-1))</f>
+        <v>1.3126627218934914</v>
+      </c>
+      <c r="K66" s="25">
+        <f t="shared" ref="K66:K74" si="31">J66*J$3</f>
+        <v>72.918414201183438</v>
+      </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B67"/>
-      <c r="C67"/>
+      <c r="B67" s="64">
+        <v>63</v>
+      </c>
+      <c r="C67" s="92" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" s="86">
+        <v>1.55</v>
+      </c>
+      <c r="E67" s="41">
+        <f t="shared" si="27"/>
+        <v>0.64516129032258063</v>
+      </c>
+      <c r="F67" s="87">
+        <f t="shared" si="28"/>
+        <v>0.44516129032258062</v>
+      </c>
+      <c r="G67" s="90">
+        <f t="shared" si="29"/>
+        <v>2.2463768115942031</v>
+      </c>
+      <c r="H67" s="88">
+        <v>0</v>
+      </c>
+      <c r="I67" s="88"/>
+      <c r="J67" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B68" s="64">
+        <v>64</v>
+      </c>
+      <c r="C68" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="86">
+        <v>1.34</v>
+      </c>
+      <c r="E68" s="41">
+        <f t="shared" si="27"/>
+        <v>0.74626865671641784</v>
+      </c>
+      <c r="F68" s="87">
+        <f t="shared" si="28"/>
+        <v>0.54626865671641789</v>
+      </c>
+      <c r="G68" s="90">
+        <f t="shared" si="29"/>
+        <v>1.8306010928961749</v>
+      </c>
+      <c r="H68" s="88">
+        <v>0</v>
+      </c>
+      <c r="I68" s="88"/>
+      <c r="J68" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B69" s="64">
+        <v>65</v>
+      </c>
+      <c r="C69" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="86">
+        <v>1.65</v>
+      </c>
+      <c r="E69" s="41">
+        <f t="shared" si="27"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="F69" s="87">
+        <f t="shared" si="28"/>
+        <v>0.40606060606060607</v>
+      </c>
+      <c r="G69" s="90">
+        <f t="shared" si="29"/>
+        <v>2.4626865671641789</v>
+      </c>
+      <c r="H69" s="88">
+        <v>0</v>
+      </c>
+      <c r="I69" s="88"/>
+      <c r="J69" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B70" s="64">
+        <v>66</v>
+      </c>
+      <c r="C70" s="92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="86">
+        <v>1.58</v>
+      </c>
+      <c r="E70" s="41">
+        <f t="shared" si="27"/>
+        <v>0.63291139240506322</v>
+      </c>
+      <c r="F70" s="87">
+        <f t="shared" si="28"/>
+        <v>0.43291139240506321</v>
+      </c>
+      <c r="G70" s="90">
+        <f t="shared" si="29"/>
+        <v>2.3099415204678366</v>
+      </c>
+      <c r="H70" s="88">
+        <v>0</v>
+      </c>
+      <c r="I70" s="88"/>
+      <c r="J70" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B71" s="64">
+        <v>67</v>
+      </c>
+      <c r="C71" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="86">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E71" s="41">
+        <f t="shared" si="27"/>
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="F71" s="87">
+        <f t="shared" si="28"/>
+        <v>0.71743119266055033</v>
+      </c>
+      <c r="G71" s="90">
+        <f t="shared" si="29"/>
+        <v>1.3938618925831205</v>
+      </c>
+      <c r="H71" s="88">
+        <v>0</v>
+      </c>
+      <c r="I71" s="88"/>
+      <c r="J71" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K71" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B72" s="64">
+        <v>68</v>
+      </c>
+      <c r="C72" s="92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="86">
+        <v>1.58</v>
+      </c>
+      <c r="E72" s="41">
+        <f t="shared" si="27"/>
+        <v>0.63291139240506322</v>
+      </c>
+      <c r="F72" s="87">
+        <f t="shared" si="28"/>
+        <v>0.43291139240506321</v>
+      </c>
+      <c r="G72" s="90">
+        <f t="shared" si="29"/>
+        <v>2.3099415204678366</v>
+      </c>
+      <c r="H72" s="88">
+        <v>0</v>
+      </c>
+      <c r="I72" s="88"/>
+      <c r="J72" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B73" s="64">
+        <v>69</v>
+      </c>
+      <c r="C73" s="92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="86">
+        <v>1.71</v>
+      </c>
+      <c r="E73" s="41">
+        <f t="shared" si="27"/>
+        <v>0.58479532163742687</v>
+      </c>
+      <c r="F73" s="87">
+        <f t="shared" si="28"/>
+        <v>0.38479532163742686</v>
+      </c>
+      <c r="G73" s="90">
+        <f t="shared" si="29"/>
+        <v>2.5987841945288759</v>
+      </c>
+      <c r="H73" s="88">
+        <v>0</v>
+      </c>
+      <c r="I73" s="88"/>
+      <c r="J73" s="89">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="27">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="65">
+        <v>70</v>
+      </c>
+      <c r="C74" s="94" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" s="76">
+        <v>1.88</v>
+      </c>
+      <c r="E74" s="42">
+        <f t="shared" si="27"/>
+        <v>0.53191489361702127</v>
+      </c>
+      <c r="F74" s="59">
+        <f t="shared" si="28"/>
+        <v>0.33191489361702126</v>
+      </c>
+      <c r="G74" s="95">
+        <f t="shared" si="29"/>
+        <v>3.0128205128205132</v>
+      </c>
+      <c r="H74" s="9">
+        <v>0</v>
+      </c>
+      <c r="I74" s="9"/>
+      <c r="J74" s="78">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="29">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3552,7 +3891,7 @@
       <c r="C5" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="83">
+      <c r="D5" s="82">
         <v>1.78</v>
       </c>
       <c r="E5" s="20">
@@ -3567,10 +3906,10 @@
         <f>1/F5</f>
         <v>2.7639751552795029</v>
       </c>
-      <c r="H5" s="83">
+      <c r="H5" s="82">
         <v>1</v>
       </c>
-      <c r="I5" s="83" t="s">
+      <c r="I5" s="82" t="s">
         <v>7</v>
       </c>
       <c r="J5" s="24">
@@ -3587,13 +3926,13 @@
       <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="81" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="7">
         <v>1.56</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="80">
         <f>1/D6</f>
         <v>0.64102564102564097</v>
       </c>
@@ -3624,13 +3963,13 @@
       <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="79" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="80">
         <f t="shared" ref="E7:E19" si="0">1/D7</f>
         <v>0.9009009009009008</v>
       </c>
@@ -3661,13 +4000,13 @@
       <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="79" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="7">
         <v>1.42</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="80">
         <f t="shared" si="0"/>
         <v>0.70422535211267612</v>
       </c>
@@ -3698,13 +4037,13 @@
       <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="79" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="7">
         <v>1.46</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="80">
         <f t="shared" si="0"/>
         <v>0.68493150684931503</v>
       </c>
@@ -3735,13 +4074,13 @@
       <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="79" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="7">
         <v>1.06</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="80">
         <f t="shared" si="0"/>
         <v>0.94339622641509424</v>
       </c>
@@ -3772,13 +4111,13 @@
       <c r="B11" s="3">
         <v>7</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="79" t="s">
         <v>51</v>
       </c>
       <c r="D11" s="7">
         <v>1.45</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="80">
         <f t="shared" si="0"/>
         <v>0.68965517241379315</v>
       </c>
@@ -3809,13 +4148,13 @@
       <c r="B12" s="3">
         <v>8</v>
       </c>
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="79" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="7">
         <v>1.36</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="80">
         <f t="shared" si="0"/>
         <v>0.73529411764705876</v>
       </c>
@@ -3846,13 +4185,13 @@
       <c r="B13" s="3">
         <v>9</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="79" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="7">
         <v>1.22</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="80">
         <f t="shared" si="0"/>
         <v>0.81967213114754101</v>
       </c>
@@ -3883,13 +4222,13 @@
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="79" t="s">
         <v>54</v>
       </c>
       <c r="D14" s="7">
         <v>1.89</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="80">
         <f t="shared" si="0"/>
         <v>0.52910052910052918</v>
       </c>
@@ -3919,13 +4258,13 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="79" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="7">
         <v>1.84</v>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="80">
         <f t="shared" si="0"/>
         <v>0.54347826086956519</v>
       </c>
@@ -3955,13 +4294,13 @@
       <c r="B16" s="3">
         <v>12</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="79" t="s">
         <v>50</v>
       </c>
       <c r="D16" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="80">
         <f t="shared" si="0"/>
         <v>0.9174311926605504</v>
       </c>
@@ -3992,13 +4331,13 @@
       <c r="B17" s="3">
         <v>13</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="79" t="s">
         <v>56</v>
       </c>
       <c r="D17" s="7">
         <v>1.84</v>
       </c>
-      <c r="E17" s="81">
+      <c r="E17" s="80">
         <f t="shared" si="0"/>
         <v>0.54347826086956519</v>
       </c>
@@ -4028,13 +4367,13 @@
       <c r="B18" s="3">
         <v>14</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="79" t="s">
         <v>57</v>
       </c>
       <c r="D18" s="7">
         <v>1.79</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="80">
         <f t="shared" si="0"/>
         <v>0.55865921787709494</v>
       </c>
@@ -4064,13 +4403,13 @@
       <c r="B19" s="3">
         <v>15</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="79" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="7">
         <v>1.72</v>
       </c>
-      <c r="E19" s="81">
+      <c r="E19" s="80">
         <f t="shared" si="0"/>
         <v>0.58139534883720934</v>
       </c>
@@ -4101,13 +4440,13 @@
       <c r="B20" s="3">
         <v>16</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="79" t="s">
         <v>58</v>
       </c>
       <c r="D20" s="7">
         <v>1.54</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="80">
         <f t="shared" ref="E20" si="12">1/D20</f>
         <v>0.64935064935064934</v>
       </c>
@@ -4137,13 +4476,13 @@
       <c r="B21" s="3">
         <v>17</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="79" t="s">
         <v>59</v>
       </c>
       <c r="D21" s="7">
         <v>1.52</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="80">
         <f t="shared" ref="E21:E37" si="15">1/D21</f>
         <v>0.65789473684210531</v>
       </c>
@@ -4174,13 +4513,13 @@
       <c r="B22" s="3">
         <v>18</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="79" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="7">
         <v>1.75</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="80">
         <f t="shared" si="15"/>
         <v>0.5714285714285714</v>
       </c>
@@ -4210,13 +4549,13 @@
       <c r="B23" s="3">
         <v>19</v>
       </c>
-      <c r="C23" s="80" t="s">
+      <c r="C23" s="79" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="7">
         <v>1.4</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="80">
         <f t="shared" si="15"/>
         <v>0.7142857142857143</v>
       </c>
@@ -4247,13 +4586,13 @@
       <c r="B24" s="3">
         <v>20</v>
       </c>
-      <c r="C24" s="80" t="s">
+      <c r="C24" s="79" t="s">
         <v>62</v>
       </c>
       <c r="D24" s="7">
         <v>1.3</v>
       </c>
-      <c r="E24" s="81">
+      <c r="E24" s="80">
         <f t="shared" si="15"/>
         <v>0.76923076923076916</v>
       </c>
@@ -4284,13 +4623,13 @@
       <c r="B25" s="3">
         <v>21</v>
       </c>
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="79" t="s">
         <v>63</v>
       </c>
       <c r="D25" s="7">
         <v>1.42</v>
       </c>
-      <c r="E25" s="81">
+      <c r="E25" s="80">
         <f t="shared" si="15"/>
         <v>0.70422535211267612</v>
       </c>
@@ -4321,13 +4660,13 @@
       <c r="B26" s="3">
         <v>22</v>
       </c>
-      <c r="C26" s="80" t="s">
+      <c r="C26" s="79" t="s">
         <v>64</v>
       </c>
       <c r="D26" s="7">
         <v>1.35</v>
       </c>
-      <c r="E26" s="81">
+      <c r="E26" s="80">
         <f t="shared" si="15"/>
         <v>0.7407407407407407</v>
       </c>
@@ -4358,13 +4697,13 @@
       <c r="B27" s="3">
         <v>23</v>
       </c>
-      <c r="C27" s="80" t="s">
+      <c r="C27" s="79" t="s">
         <v>65</v>
       </c>
       <c r="D27" s="7">
         <v>1.63</v>
       </c>
-      <c r="E27" s="81">
+      <c r="E27" s="80">
         <f t="shared" si="15"/>
         <v>0.61349693251533743</v>
       </c>
@@ -4395,13 +4734,13 @@
       <c r="B28" s="4">
         <v>24</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="85">
+      <c r="D28" s="84">
         <v>1.71</v>
       </c>
-      <c r="E28" s="86">
+      <c r="E28" s="85">
         <f t="shared" si="15"/>
         <v>0.58479532163742687</v>
       </c>
@@ -4432,13 +4771,13 @@
       <c r="B29" s="3">
         <v>25</v>
       </c>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="79" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="7">
         <v>1.95</v>
       </c>
-      <c r="E29" s="81">
+      <c r="E29" s="80">
         <f t="shared" si="15"/>
         <v>0.51282051282051289</v>
       </c>
@@ -4469,13 +4808,13 @@
       <c r="B30" s="3">
         <v>26</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="79" t="s">
         <v>68</v>
       </c>
       <c r="D30" s="7">
         <v>1.56</v>
       </c>
-      <c r="E30" s="81">
+      <c r="E30" s="80">
         <f t="shared" si="15"/>
         <v>0.64102564102564097</v>
       </c>
@@ -4505,13 +4844,13 @@
       <c r="B31" s="3">
         <v>27</v>
       </c>
-      <c r="C31" s="80" t="s">
+      <c r="C31" s="79" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="7">
         <v>2</v>
       </c>
-      <c r="E31" s="81">
+      <c r="E31" s="80">
         <f t="shared" si="15"/>
         <v>0.5</v>
       </c>
@@ -4541,13 +4880,13 @@
       <c r="B32" s="3">
         <v>28</v>
       </c>
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="79" t="s">
         <v>53</v>
       </c>
       <c r="D32" s="7">
         <v>1.32</v>
       </c>
-      <c r="E32" s="81">
+      <c r="E32" s="80">
         <f t="shared" si="15"/>
         <v>0.75757575757575757</v>
       </c>
@@ -4574,13 +4913,13 @@
       <c r="B33" s="3">
         <v>29</v>
       </c>
-      <c r="C33" s="80" t="s">
+      <c r="C33" s="79" t="s">
         <v>70</v>
       </c>
       <c r="D33" s="7">
         <v>1.79</v>
       </c>
-      <c r="E33" s="81">
+      <c r="E33" s="80">
         <f t="shared" si="15"/>
         <v>0.55865921787709494</v>
       </c>
@@ -4610,13 +4949,13 @@
       <c r="B34" s="3">
         <v>30</v>
       </c>
-      <c r="C34" s="80" t="s">
+      <c r="C34" s="79" t="s">
         <v>71</v>
       </c>
       <c r="D34" s="7">
         <v>2</v>
       </c>
-      <c r="E34" s="81">
+      <c r="E34" s="80">
         <f t="shared" si="15"/>
         <v>0.5</v>
       </c>
@@ -4646,13 +4985,13 @@
       <c r="B35" s="3">
         <v>31</v>
       </c>
-      <c r="C35" s="80" t="s">
+      <c r="C35" s="79" t="s">
         <v>72</v>
       </c>
       <c r="D35" s="7">
         <v>1.4</v>
       </c>
-      <c r="E35" s="81">
+      <c r="E35" s="80">
         <f t="shared" si="15"/>
         <v>0.7142857142857143</v>
       </c>
@@ -4679,13 +5018,13 @@
       <c r="B36" s="3">
         <v>32</v>
       </c>
-      <c r="C36" s="80" t="s">
+      <c r="C36" s="79" t="s">
         <v>73</v>
       </c>
       <c r="D36" s="7">
         <v>1.52</v>
       </c>
-      <c r="E36" s="81">
+      <c r="E36" s="80">
         <f t="shared" si="15"/>
         <v>0.65789473684210531</v>
       </c>
@@ -4716,13 +5055,13 @@
       <c r="B37" s="3">
         <v>33</v>
       </c>
-      <c r="C37" s="80" t="s">
+      <c r="C37" s="79" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="7">
         <v>2</v>
       </c>
-      <c r="E37" s="81">
+      <c r="E37" s="80">
         <f t="shared" si="15"/>
         <v>0.5</v>
       </c>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F837BF-F31C-40D5-898D-F7905AFBA1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFE8CCC-F383-42CA-A714-63FCA46FC172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -324,6 +324,24 @@
   </si>
   <si>
     <t>Bombers</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Kalinina</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>Korneeva</t>
+  </si>
+  <si>
+    <t>Neumayer</t>
+  </si>
+  <si>
+    <t>Mboko</t>
   </si>
 </sst>
 </file>
@@ -3557,8 +3575,7 @@
         <v>0.44516129032258062</v>
       </c>
       <c r="G67" s="90">
-        <f t="shared" si="29"/>
-        <v>2.2463768115942031</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="H67" s="88">
         <v>0</v>
@@ -3662,8 +3679,7 @@
         <v>0.43291139240506321</v>
       </c>
       <c r="G70" s="90">
-        <f t="shared" si="29"/>
-        <v>2.3099415204678366</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="H70" s="88">
         <v>0</v>
@@ -3732,8 +3748,7 @@
         <v>0.43291139240506321</v>
       </c>
       <c r="G72" s="90">
-        <f t="shared" si="29"/>
-        <v>2.3099415204678366</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="H72" s="88">
         <v>0</v>
@@ -3802,8 +3817,7 @@
         <v>0.33191489361702126</v>
       </c>
       <c r="G74" s="95">
-        <f t="shared" si="29"/>
-        <v>3.0128205128205132</v>
+        <v>3.05</v>
       </c>
       <c r="H74" s="9">
         <v>0</v>
@@ -3826,7 +3840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L37"/>
+  <dimension ref="B2:L44"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -4483,11 +4497,11 @@
         <v>1.52</v>
       </c>
       <c r="E21" s="80">
-        <f t="shared" ref="E21:E37" si="15">1/D21</f>
+        <f t="shared" ref="E21:E44" si="15">1/D21</f>
         <v>0.65789473684210531</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" ref="F21:F37" si="16">E21-0.2</f>
+        <f t="shared" ref="F21:F44" si="16">E21-0.2</f>
         <v>0.4578947368421053</v>
       </c>
       <c r="G21" s="52">
@@ -4898,15 +4912,19 @@
         <f t="shared" ref="G32:G36" si="22">1/F32</f>
         <v>1.7934782608695652</v>
       </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J32" s="26">
         <f t="shared" ref="J32" si="23">IF(H32=0,0,IF(I32="WON",(G32*0.94-1),-1))</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K32" s="27">
         <f t="shared" ref="K32" si="24">J32*J$3</f>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
@@ -5003,8 +5021,12 @@
         <f t="shared" si="22"/>
         <v>1.9444444444444446</v>
       </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J35" s="26">
         <f t="shared" ref="J35" si="29">IF(H35=0,0,IF(I35="WON",(G35*0.94-1),-1))</f>
         <v>0</v>
@@ -5084,6 +5106,263 @@
       </c>
       <c r="K37" s="27">
         <f t="shared" ref="K37" si="34">J37*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="3">
+        <v>34</v>
+      </c>
+      <c r="C38" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="7">
+        <v>1.46</v>
+      </c>
+      <c r="E38" s="80">
+        <f t="shared" si="15"/>
+        <v>0.68493150684931503</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" si="16"/>
+        <v>0.48493150684931502</v>
+      </c>
+      <c r="G38" s="52">
+        <f>1/F38</f>
+        <v>2.0621468926553677</v>
+      </c>
+      <c r="H38" s="1">
+        <v>999</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="26">
+        <f t="shared" ref="J38:J39" si="35">IF(H38=0,0,IF(I38="WON",(G38*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K38" s="27">
+        <f t="shared" ref="K38:K39" si="36">J38*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
+        <v>35</v>
+      </c>
+      <c r="C39" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="E39" s="80">
+        <f t="shared" si="15"/>
+        <v>0.72992700729927007</v>
+      </c>
+      <c r="F39" s="6">
+        <f t="shared" si="16"/>
+        <v>0.52992700729927011</v>
+      </c>
+      <c r="G39" s="52">
+        <f>1/F39</f>
+        <v>1.887052341597796</v>
+      </c>
+      <c r="H39" s="1">
+        <v>999</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="26">
+        <f t="shared" si="35"/>
+        <v>-1</v>
+      </c>
+      <c r="K39" s="27">
+        <f t="shared" si="36"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="3">
+        <v>36</v>
+      </c>
+      <c r="C40" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1.84</v>
+      </c>
+      <c r="E40" s="80">
+        <f t="shared" si="15"/>
+        <v>0.54347826086956519</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" si="16"/>
+        <v>0.34347826086956518</v>
+      </c>
+      <c r="G40" s="52">
+        <v>2.92</v>
+      </c>
+      <c r="H40" s="1">
+        <v>999</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J40" s="26">
+        <f t="shared" ref="J40:J44" si="37">IF(H40=0,0,IF(I40="WON",(G40*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K40" s="27">
+        <f t="shared" ref="K40:K44" si="38">J40*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="3">
+        <v>37</v>
+      </c>
+      <c r="C41" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="E41" s="80">
+        <f t="shared" si="15"/>
+        <v>0.73529411764705876</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" si="16"/>
+        <v>0.5352941176470587</v>
+      </c>
+      <c r="G41" s="52">
+        <f>1/F41</f>
+        <v>1.8681318681318686</v>
+      </c>
+      <c r="H41" s="1">
+        <v>999</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="26">
+        <f t="shared" si="37"/>
+        <v>-1</v>
+      </c>
+      <c r="K41" s="27">
+        <f t="shared" si="38"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="3">
+        <v>38</v>
+      </c>
+      <c r="C42" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="E42" s="80">
+        <f t="shared" si="15"/>
+        <v>0.56818181818181823</v>
+      </c>
+      <c r="F42" s="6">
+        <f t="shared" si="16"/>
+        <v>0.36818181818181822</v>
+      </c>
+      <c r="G42" s="52">
+        <f t="shared" ref="G42" si="39">1/F42</f>
+        <v>2.716049382716049</v>
+      </c>
+      <c r="H42" s="1">
+        <v>999</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J42" s="26">
+        <f t="shared" si="37"/>
+        <v>-1</v>
+      </c>
+      <c r="K42" s="27">
+        <f t="shared" si="38"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="3">
+        <v>39</v>
+      </c>
+      <c r="C43" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="E43" s="80">
+        <f t="shared" si="15"/>
+        <v>0.52356020942408377</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="16"/>
+        <v>0.32356020942408376</v>
+      </c>
+      <c r="G43" s="52">
+        <v>3.1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>999</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43" s="26">
+        <f t="shared" si="37"/>
+        <v>-1</v>
+      </c>
+      <c r="K43" s="27">
+        <f t="shared" si="38"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="3">
+        <v>40</v>
+      </c>
+      <c r="C44" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="E44" s="80">
+        <f t="shared" si="15"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="F44" s="6">
+        <f t="shared" si="16"/>
+        <v>0.40606060606060607</v>
+      </c>
+      <c r="G44" s="52">
+        <f>1/F44</f>
+        <v>2.4626865671641789</v>
+      </c>
+      <c r="H44" s="1">
+        <v>999</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="26">
+        <f t="shared" si="37"/>
+        <v>-1</v>
+      </c>
+      <c r="K44" s="27">
+        <f t="shared" si="38"/>
         <v>-55.55</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -1,42 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFE8CCC-F383-42CA-A714-63FCA46FC172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AB6A4B-4C08-4D0D-AFEE-AA8AC5B96FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
     <sheet name="Tennis" sheetId="2" r:id="rId2"/>
     <sheet name="Shares" sheetId="13" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -598,7 +589,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -853,25 +844,13 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3157,14 +3136,14 @@
       <c r="C56" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="88">
+      <c r="D56" s="51">
         <v>1.17</v>
       </c>
       <c r="E56" s="41">
         <f t="shared" si="17"/>
         <v>0.85470085470085477</v>
       </c>
-      <c r="F56" s="87">
+      <c r="F56" s="54">
         <f t="shared" si="18"/>
         <v>0.65470085470085482</v>
       </c>
@@ -3205,7 +3184,7 @@
         <f t="shared" ref="F57:F65" si="23">E57-0.2</f>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G57" s="91">
+      <c r="G57" s="87">
         <f t="shared" ref="G57:G65" si="24">1/F57</f>
         <v>1.4432989690721649</v>
       </c>
@@ -3231,7 +3210,7 @@
       <c r="C58" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="86">
+      <c r="D58" s="1">
         <v>1.18</v>
       </c>
       <c r="E58" s="41">
@@ -3242,7 +3221,7 @@
         <f t="shared" si="23"/>
         <v>0.64745762711864407</v>
       </c>
-      <c r="G58" s="90">
+      <c r="G58" s="86">
         <f t="shared" si="24"/>
         <v>1.544502617801047</v>
       </c>
@@ -3268,7 +3247,7 @@
       <c r="C59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="86">
+      <c r="D59" s="1">
         <v>1.25</v>
       </c>
       <c r="E59" s="41">
@@ -3279,7 +3258,7 @@
         <f t="shared" si="23"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G59" s="90">
+      <c r="G59" s="86">
         <f t="shared" si="24"/>
         <v>1.6666666666666665</v>
       </c>
@@ -3305,7 +3284,7 @@
       <c r="C60" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="86">
+      <c r="D60" s="1">
         <v>1.53</v>
       </c>
       <c r="E60" s="41">
@@ -3316,7 +3295,7 @@
         <f t="shared" si="23"/>
         <v>0.45359477124183006</v>
       </c>
-      <c r="G60" s="90">
+      <c r="G60" s="86">
         <f t="shared" si="24"/>
         <v>2.2046109510086453</v>
       </c>
@@ -3342,7 +3321,7 @@
       <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="86">
+      <c r="D61" s="1">
         <v>1.49</v>
       </c>
       <c r="E61" s="41">
@@ -3353,7 +3332,7 @@
         <f t="shared" si="23"/>
         <v>0.47114093959731546</v>
       </c>
-      <c r="G61" s="90">
+      <c r="G61" s="86">
         <f t="shared" si="24"/>
         <v>2.1225071225071224</v>
       </c>
@@ -3379,7 +3358,7 @@
       <c r="C62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="86">
+      <c r="D62" s="1">
         <v>1.74</v>
       </c>
       <c r="E62" s="41">
@@ -3390,7 +3369,7 @@
         <f t="shared" si="23"/>
         <v>0.37471264367816087</v>
       </c>
-      <c r="G62" s="90">
+      <c r="G62" s="86">
         <v>2.68</v>
       </c>
       <c r="H62" s="51">
@@ -3415,7 +3394,7 @@
       <c r="C63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="86">
+      <c r="D63" s="1">
         <v>1.21</v>
       </c>
       <c r="E63" s="41">
@@ -3426,7 +3405,7 @@
         <f t="shared" si="23"/>
         <v>0.62644628099173549</v>
       </c>
-      <c r="G63" s="90">
+      <c r="G63" s="86">
         <f t="shared" si="24"/>
         <v>1.5963060686015833</v>
       </c>
@@ -3452,7 +3431,7 @@
       <c r="C64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="86">
+      <c r="D64" s="1">
         <v>1.1200000000000001</v>
       </c>
       <c r="E64" s="41">
@@ -3463,7 +3442,7 @@
         <f t="shared" si="23"/>
         <v>0.69285714285714284</v>
       </c>
-      <c r="G64" s="90">
+      <c r="G64" s="86">
         <f t="shared" si="24"/>
         <v>1.4432989690721649</v>
       </c>
@@ -3489,7 +3468,7 @@
       <c r="C65" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D65" s="86">
+      <c r="D65" s="1">
         <v>1.28</v>
       </c>
       <c r="E65" s="41">
@@ -3500,17 +3479,17 @@
         <f t="shared" si="23"/>
         <v>0.58125000000000004</v>
       </c>
-      <c r="G65" s="90">
+      <c r="G65" s="86">
         <f t="shared" si="24"/>
         <v>1.7204301075268815</v>
       </c>
-      <c r="H65" s="88">
+      <c r="H65" s="51">
         <v>1</v>
       </c>
       <c r="I65" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="J65" s="89">
+      <c r="J65" s="77">
         <f t="shared" si="25"/>
         <v>-1</v>
       </c>
@@ -3523,7 +3502,7 @@
       <c r="B66" s="63">
         <v>62</v>
       </c>
-      <c r="C66" s="93" t="s">
+      <c r="C66" s="89" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="75">
@@ -3537,8 +3516,8 @@
         <f t="shared" ref="F66:F74" si="28">E66-0.2</f>
         <v>0.41728395061728391</v>
       </c>
-      <c r="G66" s="91">
-        <f t="shared" ref="G66:G74" si="29">1/F66</f>
+      <c r="G66" s="87">
+        <f t="shared" ref="G66:G73" si="29">1/F66</f>
         <v>2.3964497041420123</v>
       </c>
       <c r="H66" s="23">
@@ -3560,98 +3539,102 @@
       <c r="B67" s="64">
         <v>63</v>
       </c>
-      <c r="C67" s="92" t="s">
+      <c r="C67" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="86">
+      <c r="D67" s="1">
         <v>1.55</v>
       </c>
       <c r="E67" s="41">
         <f t="shared" si="27"/>
         <v>0.64516129032258063</v>
       </c>
-      <c r="F67" s="87">
+      <c r="F67" s="54">
         <f t="shared" si="28"/>
         <v>0.44516129032258062</v>
       </c>
-      <c r="G67" s="90">
+      <c r="G67" s="86">
         <v>2.2599999999999998</v>
       </c>
-      <c r="H67" s="88">
-        <v>0</v>
-      </c>
-      <c r="I67" s="88"/>
-      <c r="J67" s="89">
+      <c r="H67" s="51">
+        <v>1</v>
+      </c>
+      <c r="I67" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J67" s="77">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K67" s="27">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" s="64">
         <v>64</v>
       </c>
-      <c r="C68" s="92" t="s">
+      <c r="C68" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="86">
+      <c r="D68" s="1">
         <v>1.34</v>
       </c>
       <c r="E68" s="41">
         <f t="shared" si="27"/>
         <v>0.74626865671641784</v>
       </c>
-      <c r="F68" s="87">
+      <c r="F68" s="54">
         <f t="shared" si="28"/>
         <v>0.54626865671641789</v>
       </c>
-      <c r="G68" s="90">
+      <c r="G68" s="86">
         <f t="shared" si="29"/>
         <v>1.8306010928961749</v>
       </c>
-      <c r="H68" s="88">
-        <v>0</v>
-      </c>
-      <c r="I68" s="88"/>
-      <c r="J68" s="89">
+      <c r="H68" s="51">
+        <v>1</v>
+      </c>
+      <c r="I68" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="J68" s="77">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>0.78076502732240438</v>
       </c>
       <c r="K68" s="27">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>43.371497267759558</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="64">
         <v>65</v>
       </c>
-      <c r="C69" s="92" t="s">
+      <c r="C69" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="D69" s="86">
+      <c r="D69" s="1">
         <v>1.65</v>
       </c>
       <c r="E69" s="41">
         <f t="shared" si="27"/>
         <v>0.60606060606060608</v>
       </c>
-      <c r="F69" s="87">
+      <c r="F69" s="54">
         <f t="shared" si="28"/>
         <v>0.40606060606060607</v>
       </c>
-      <c r="G69" s="90">
+      <c r="G69" s="86">
         <f t="shared" si="29"/>
         <v>2.4626865671641789</v>
       </c>
-      <c r="H69" s="88">
-        <v>0</v>
-      </c>
-      <c r="I69" s="88"/>
-      <c r="J69" s="89">
+      <c r="H69" s="51">
+        <v>0</v>
+      </c>
+      <c r="I69" s="51"/>
+      <c r="J69" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -3664,28 +3647,28 @@
       <c r="B70" s="64">
         <v>66</v>
       </c>
-      <c r="C70" s="92" t="s">
+      <c r="C70" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D70" s="86">
+      <c r="D70" s="1">
         <v>1.58</v>
       </c>
       <c r="E70" s="41">
         <f t="shared" si="27"/>
         <v>0.63291139240506322</v>
       </c>
-      <c r="F70" s="87">
+      <c r="F70" s="54">
         <f t="shared" si="28"/>
         <v>0.43291139240506321</v>
       </c>
-      <c r="G70" s="90">
+      <c r="G70" s="86">
         <v>2.3199999999999998</v>
       </c>
-      <c r="H70" s="88">
-        <v>0</v>
-      </c>
-      <c r="I70" s="88"/>
-      <c r="J70" s="89">
+      <c r="H70" s="51">
+        <v>0</v>
+      </c>
+      <c r="I70" s="51"/>
+      <c r="J70" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -3698,29 +3681,29 @@
       <c r="B71" s="64">
         <v>67</v>
       </c>
-      <c r="C71" s="92" t="s">
+      <c r="C71" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="D71" s="86">
+      <c r="D71" s="1">
         <v>1.0900000000000001</v>
       </c>
       <c r="E71" s="41">
         <f t="shared" si="27"/>
         <v>0.9174311926605504</v>
       </c>
-      <c r="F71" s="87">
+      <c r="F71" s="54">
         <f t="shared" si="28"/>
         <v>0.71743119266055033</v>
       </c>
-      <c r="G71" s="90">
+      <c r="G71" s="86">
         <f t="shared" si="29"/>
         <v>1.3938618925831205</v>
       </c>
-      <c r="H71" s="88">
-        <v>0</v>
-      </c>
-      <c r="I71" s="88"/>
-      <c r="J71" s="89">
+      <c r="H71" s="51">
+        <v>0</v>
+      </c>
+      <c r="I71" s="51"/>
+      <c r="J71" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -3733,28 +3716,28 @@
       <c r="B72" s="64">
         <v>68</v>
       </c>
-      <c r="C72" s="92" t="s">
+      <c r="C72" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="D72" s="86">
+      <c r="D72" s="1">
         <v>1.58</v>
       </c>
       <c r="E72" s="41">
         <f t="shared" si="27"/>
         <v>0.63291139240506322</v>
       </c>
-      <c r="F72" s="87">
+      <c r="F72" s="54">
         <f t="shared" si="28"/>
         <v>0.43291139240506321</v>
       </c>
-      <c r="G72" s="90">
+      <c r="G72" s="86">
         <v>2.3199999999999998</v>
       </c>
-      <c r="H72" s="88">
-        <v>0</v>
-      </c>
-      <c r="I72" s="88"/>
-      <c r="J72" s="89">
+      <c r="H72" s="51">
+        <v>0</v>
+      </c>
+      <c r="I72" s="51"/>
+      <c r="J72" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -3767,29 +3750,29 @@
       <c r="B73" s="64">
         <v>69</v>
       </c>
-      <c r="C73" s="92" t="s">
+      <c r="C73" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="86">
+      <c r="D73" s="1">
         <v>1.71</v>
       </c>
       <c r="E73" s="41">
         <f t="shared" si="27"/>
         <v>0.58479532163742687</v>
       </c>
-      <c r="F73" s="87">
+      <c r="F73" s="54">
         <f t="shared" si="28"/>
         <v>0.38479532163742686</v>
       </c>
-      <c r="G73" s="90">
+      <c r="G73" s="86">
         <f t="shared" si="29"/>
         <v>2.5987841945288759</v>
       </c>
-      <c r="H73" s="88">
-        <v>0</v>
-      </c>
-      <c r="I73" s="88"/>
-      <c r="J73" s="89">
+      <c r="H73" s="51">
+        <v>0</v>
+      </c>
+      <c r="I73" s="51"/>
+      <c r="J73" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -3802,7 +3785,7 @@
       <c r="B74" s="65">
         <v>70</v>
       </c>
-      <c r="C74" s="94" t="s">
+      <c r="C74" s="90" t="s">
         <v>33</v>
       </c>
       <c r="D74" s="76">
@@ -3816,7 +3799,7 @@
         <f t="shared" si="28"/>
         <v>0.33191489361702126</v>
       </c>
-      <c r="G74" s="95">
+      <c r="G74" s="91">
         <v>3.05</v>
       </c>
       <c r="H74" s="9">
@@ -5132,18 +5115,18 @@
         <v>2.0621468926553677</v>
       </c>
       <c r="H38" s="1">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J38" s="26">
         <f t="shared" ref="J38:J39" si="35">IF(H38=0,0,IF(I38="WON",(G38*0.94-1),-1))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="27">
         <f t="shared" ref="K38:K39" si="36">J38*J$3</f>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
@@ -5169,18 +5152,18 @@
         <v>1.887052341597796</v>
       </c>
       <c r="H39" s="1">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J39" s="26">
         <f t="shared" si="35"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="27">
         <f t="shared" si="36"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
@@ -5205,18 +5188,18 @@
         <v>2.92</v>
       </c>
       <c r="H40" s="1">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J40" s="26">
         <f t="shared" ref="J40:J44" si="37">IF(H40=0,0,IF(I40="WON",(G40*0.94-1),-1))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="27">
         <f t="shared" ref="K40:K44" si="38">J40*J$3</f>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
@@ -5242,18 +5225,18 @@
         <v>1.8681318681318686</v>
       </c>
       <c r="H41" s="1">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J41" s="26">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>0.75604395604395647</v>
       </c>
       <c r="K41" s="27">
         <f t="shared" si="38"/>
-        <v>-55.55</v>
+        <v>41.998241758241782</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
@@ -5279,18 +5262,18 @@
         <v>2.716049382716049</v>
       </c>
       <c r="H42" s="1">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J42" s="26">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="27">
         <f t="shared" si="38"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
@@ -5315,7 +5298,7 @@
         <v>3.1</v>
       </c>
       <c r="H43" s="1">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -5352,18 +5335,18 @@
         <v>2.4626865671641789</v>
       </c>
       <c r="H44" s="1">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J44" s="26">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="27">
         <f t="shared" si="38"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,26 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AB6A4B-4C08-4D0D-AFEE-AA8AC5B96FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA3E12C-4F9C-427C-BB38-7A943A260046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
     <sheet name="Tennis" sheetId="2" r:id="rId2"/>
     <sheet name="Shares" sheetId="13" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="88">
   <si>
     <t>ID</t>
   </si>
@@ -333,6 +342,24 @@
   </si>
   <si>
     <t>Mboko</t>
+  </si>
+  <si>
+    <t>Guerrieri</t>
+  </si>
+  <si>
+    <t>Jacquet</t>
+  </si>
+  <si>
+    <t>Wang</t>
+  </si>
+  <si>
+    <t>Buse</t>
+  </si>
+  <si>
+    <t>Bublik</t>
+  </si>
+  <si>
+    <t>De Minaur</t>
   </si>
 </sst>
 </file>
@@ -3823,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L44"/>
+  <dimension ref="B2:L51"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -4480,11 +4507,11 @@
         <v>1.52</v>
       </c>
       <c r="E21" s="80">
-        <f t="shared" ref="E21:E44" si="15">1/D21</f>
+        <f t="shared" ref="E21:E51" si="15">1/D21</f>
         <v>0.65789473684210531</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" ref="F21:F44" si="16">E21-0.2</f>
+        <f t="shared" ref="F21:F51" si="16">E21-0.2</f>
         <v>0.4578947368421053</v>
       </c>
       <c r="G21" s="52">
@@ -5347,6 +5374,247 @@
       <c r="K44" s="27">
         <f t="shared" si="38"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="3">
+        <v>41</v>
+      </c>
+      <c r="C45" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="E45" s="80">
+        <f t="shared" si="15"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" si="16"/>
+        <v>0.32631578947368417</v>
+      </c>
+      <c r="G45" s="52">
+        <v>3.1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>999</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="26">
+        <f t="shared" ref="J45:J51" si="40">IF(H45=0,0,IF(I45="WON",(G45*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K45" s="27">
+        <f t="shared" ref="K45:K51" si="41">J45*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="3">
+        <v>42</v>
+      </c>
+      <c r="C46" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1.73</v>
+      </c>
+      <c r="E46" s="80">
+        <f t="shared" si="15"/>
+        <v>0.5780346820809249</v>
+      </c>
+      <c r="F46" s="6">
+        <f t="shared" si="16"/>
+        <v>0.37803468208092489</v>
+      </c>
+      <c r="G46" s="52">
+        <v>2.66</v>
+      </c>
+      <c r="H46" s="1">
+        <v>999</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="26">
+        <f t="shared" si="40"/>
+        <v>-1</v>
+      </c>
+      <c r="K46" s="27">
+        <f t="shared" si="41"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="3">
+        <v>43</v>
+      </c>
+      <c r="C47" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="E47" s="80">
+        <f t="shared" si="15"/>
+        <v>0.59523809523809523</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="16"/>
+        <v>0.39523809523809522</v>
+      </c>
+      <c r="G47" s="52">
+        <v>2.54</v>
+      </c>
+      <c r="H47" s="1">
+        <v>999</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="26">
+        <f t="shared" si="40"/>
+        <v>-1</v>
+      </c>
+      <c r="K47" s="27">
+        <f t="shared" si="41"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="3">
+        <v>44</v>
+      </c>
+      <c r="C48" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="E48" s="80">
+        <f t="shared" si="15"/>
+        <v>0.72992700729927007</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="shared" si="16"/>
+        <v>0.52992700729927011</v>
+      </c>
+      <c r="G48" s="52">
+        <f t="shared" ref="G48:G51" si="42">1/F48</f>
+        <v>1.887052341597796</v>
+      </c>
+      <c r="H48" s="1">
+        <v>999</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="26">
+        <f t="shared" si="40"/>
+        <v>-1</v>
+      </c>
+      <c r="K48" s="27">
+        <f t="shared" si="41"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="3">
+        <v>45</v>
+      </c>
+      <c r="C49" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="E49" s="80">
+        <f t="shared" si="15"/>
+        <v>0.57471264367816088</v>
+      </c>
+      <c r="F49" s="6">
+        <f t="shared" si="16"/>
+        <v>0.37471264367816087</v>
+      </c>
+      <c r="G49" s="52">
+        <v>2.68</v>
+      </c>
+      <c r="H49" s="1">
+        <v>999</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="26">
+        <f t="shared" si="40"/>
+        <v>-1</v>
+      </c>
+      <c r="K49" s="27">
+        <f t="shared" si="41"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="3">
+        <v>46</v>
+      </c>
+      <c r="C50" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="E50" s="80">
+        <f t="shared" si="15"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F50" s="6">
+        <f t="shared" si="16"/>
+        <v>0.51428571428571423</v>
+      </c>
+      <c r="G50" s="52">
+        <f t="shared" si="42"/>
+        <v>1.9444444444444446</v>
+      </c>
+      <c r="H50" s="1">
+        <v>999</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="26">
+        <f t="shared" si="40"/>
+        <v>-1</v>
+      </c>
+      <c r="K50" s="27">
+        <f t="shared" si="41"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B51" s="3">
+        <v>47</v>
+      </c>
+      <c r="C51" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="E51" s="80">
+        <f t="shared" si="15"/>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="F51" s="6">
+        <f t="shared" si="16"/>
+        <v>0.38823529411764707</v>
+      </c>
+      <c r="G51" s="52">
+        <f t="shared" si="42"/>
+        <v>2.5757575757575757</v>
+      </c>
+      <c r="H51" s="1">
+        <v>999</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="26">
+        <f t="shared" si="40"/>
+        <v>-1</v>
+      </c>
+      <c r="K51" s="27">
+        <f t="shared" si="41"/>
+        <v>-55.55</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA3E12C-4F9C-427C-BB38-7A943A260046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81E22A1-F22E-45C9-92D5-95E90222D48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="88">
   <si>
     <t>ID</t>
   </si>
@@ -3660,7 +3660,9 @@
       <c r="H69" s="51">
         <v>0</v>
       </c>
-      <c r="I69" s="51"/>
+      <c r="I69" s="51" t="s">
+        <v>10</v>
+      </c>
       <c r="J69" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3694,7 +3696,9 @@
       <c r="H70" s="51">
         <v>0</v>
       </c>
-      <c r="I70" s="51"/>
+      <c r="I70" s="51" t="s">
+        <v>7</v>
+      </c>
       <c r="J70" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3729,7 +3733,9 @@
       <c r="H71" s="51">
         <v>0</v>
       </c>
-      <c r="I71" s="51"/>
+      <c r="I71" s="51" t="s">
+        <v>7</v>
+      </c>
       <c r="J71" s="77">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3761,16 +3767,18 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="H72" s="51">
-        <v>0</v>
-      </c>
-      <c r="I72" s="51"/>
+        <v>1</v>
+      </c>
+      <c r="I72" s="51" t="s">
+        <v>10</v>
+      </c>
       <c r="J72" s="77">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K72" s="27">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
@@ -3796,16 +3804,18 @@
         <v>2.5987841945288759</v>
       </c>
       <c r="H73" s="51">
-        <v>0</v>
-      </c>
-      <c r="I73" s="51"/>
+        <v>1</v>
+      </c>
+      <c r="I73" s="51" t="s">
+        <v>10</v>
+      </c>
       <c r="J73" s="77">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K73" s="27">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3830,16 +3840,18 @@
         <v>3.05</v>
       </c>
       <c r="H74" s="9">
-        <v>0</v>
-      </c>
-      <c r="I74" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="I74" s="51" t="s">
+        <v>10</v>
+      </c>
       <c r="J74" s="78">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K74" s="29">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
   </sheetData>
@@ -5398,9 +5410,11 @@
         <v>3.1</v>
       </c>
       <c r="H45" s="1">
-        <v>999</v>
-      </c>
-      <c r="I45" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J45" s="26">
         <f t="shared" ref="J45:J51" si="40">IF(H45=0,0,IF(I45="WON",(G45*0.94-1),-1))</f>
         <v>-1</v>
@@ -5432,16 +5446,18 @@
         <v>2.66</v>
       </c>
       <c r="H46" s="1">
-        <v>999</v>
-      </c>
-      <c r="I46" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J46" s="26">
         <f t="shared" si="40"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="27">
         <f t="shared" si="41"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
@@ -5466,16 +5482,18 @@
         <v>2.54</v>
       </c>
       <c r="H47" s="1">
-        <v>999</v>
-      </c>
-      <c r="I47" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J47" s="26">
         <f t="shared" si="40"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="27">
         <f t="shared" si="41"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
@@ -5501,16 +5519,18 @@
         <v>1.887052341597796</v>
       </c>
       <c r="H48" s="1">
-        <v>999</v>
-      </c>
-      <c r="I48" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J48" s="26">
         <f t="shared" si="40"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="27">
         <f t="shared" si="41"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
@@ -5535,9 +5555,11 @@
         <v>2.68</v>
       </c>
       <c r="H49" s="1">
-        <v>999</v>
-      </c>
-      <c r="I49" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J49" s="26">
         <f t="shared" si="40"/>
         <v>-1</v>
@@ -5570,16 +5592,18 @@
         <v>1.9444444444444446</v>
       </c>
       <c r="H50" s="1">
-        <v>999</v>
-      </c>
-      <c r="I50" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J50" s="26">
         <f t="shared" si="40"/>
-        <v>-1</v>
+        <v>0.82777777777777795</v>
       </c>
       <c r="K50" s="27">
         <f t="shared" si="41"/>
-        <v>-55.55</v>
+        <v>45.983055555555559</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
@@ -5605,9 +5629,11 @@
         <v>2.5757575757575757</v>
       </c>
       <c r="H51" s="1">
-        <v>999</v>
-      </c>
-      <c r="I51" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J51" s="26">
         <f t="shared" si="40"/>
         <v>-1</v>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81E22A1-F22E-45C9-92D5-95E90222D48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B3AFEE-C8B2-4D74-BA35-644A8561F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
   <sheets>
     <sheet name="AFL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -360,6 +360,33 @@
   </si>
   <si>
     <t>De Minaur</t>
+  </si>
+  <si>
+    <t>Djokovic</t>
+  </si>
+  <si>
+    <t>Baptiste</t>
+  </si>
+  <si>
+    <t>Fritz</t>
+  </si>
+  <si>
+    <t>Halys</t>
+  </si>
+  <si>
+    <t>Medjedovic</t>
+  </si>
+  <si>
+    <t>Cina</t>
+  </si>
+  <si>
+    <t>Machac</t>
+  </si>
+  <si>
+    <t>Volynets</t>
+  </si>
+  <si>
+    <t>Rublev</t>
   </si>
 </sst>
 </file>
@@ -3862,7 +3889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L51"/>
+  <dimension ref="B2:L61"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -4519,11 +4546,11 @@
         <v>1.52</v>
       </c>
       <c r="E21" s="80">
-        <f t="shared" ref="E21:E51" si="15">1/D21</f>
+        <f t="shared" ref="E21:E61" si="15">1/D21</f>
         <v>0.65789473684210531</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" ref="F21:F51" si="16">E21-0.2</f>
+        <f t="shared" ref="F21:F61" si="16">E21-0.2</f>
         <v>0.4578947368421053</v>
       </c>
       <c r="G21" s="52">
@@ -5640,6 +5667,374 @@
       </c>
       <c r="K51" s="27">
         <f t="shared" si="41"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="3">
+        <v>48</v>
+      </c>
+      <c r="C52" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E52" s="80">
+        <f t="shared" si="15"/>
+        <v>0.87719298245614041</v>
+      </c>
+      <c r="F52" s="6">
+        <f t="shared" si="16"/>
+        <v>0.67719298245614046</v>
+      </c>
+      <c r="G52" s="52">
+        <f>1/F52</f>
+        <v>1.4766839378238339</v>
+      </c>
+      <c r="H52" s="1">
+        <v>999</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J52" s="26">
+        <f t="shared" ref="J52:J61" si="43">IF(H52=0,0,IF(I52="WON",(G52*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K52" s="27">
+        <f t="shared" ref="K52:K61" si="44">J52*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="3">
+        <v>49</v>
+      </c>
+      <c r="C53" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1.85</v>
+      </c>
+      <c r="E53" s="80">
+        <f t="shared" si="15"/>
+        <v>0.54054054054054046</v>
+      </c>
+      <c r="F53" s="6">
+        <f t="shared" si="16"/>
+        <v>0.34054054054054045</v>
+      </c>
+      <c r="G53" s="52">
+        <f t="shared" ref="G53:G61" si="45">1/F53</f>
+        <v>2.9365079365079372</v>
+      </c>
+      <c r="H53" s="1">
+        <v>999</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J53" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K53" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B54" s="3">
+        <v>50</v>
+      </c>
+      <c r="C54" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="7">
+        <v>1.27</v>
+      </c>
+      <c r="E54" s="80">
+        <f t="shared" si="15"/>
+        <v>0.78740157480314954</v>
+      </c>
+      <c r="F54" s="6">
+        <f t="shared" si="16"/>
+        <v>0.58740157480314958</v>
+      </c>
+      <c r="G54" s="52">
+        <f t="shared" si="45"/>
+        <v>1.7024128686327078</v>
+      </c>
+      <c r="H54" s="1">
+        <v>999</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J54" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K54" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B55" s="3">
+        <v>51</v>
+      </c>
+      <c r="C55" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="E55" s="80">
+        <f t="shared" si="15"/>
+        <v>0.94339622641509424</v>
+      </c>
+      <c r="F55" s="6">
+        <f t="shared" si="16"/>
+        <v>0.74339622641509417</v>
+      </c>
+      <c r="G55" s="52">
+        <f t="shared" si="45"/>
+        <v>1.3451776649746197</v>
+      </c>
+      <c r="H55" s="1">
+        <v>999</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J55" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K55" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="3">
+        <v>52</v>
+      </c>
+      <c r="C56" s="79" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="E56" s="80">
+        <f t="shared" si="15"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="F56" s="6">
+        <f t="shared" si="16"/>
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="G56" s="52">
+        <v>2.82</v>
+      </c>
+      <c r="H56" s="1">
+        <v>999</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J56" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K56" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="3">
+        <v>53</v>
+      </c>
+      <c r="C57" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57" s="7">
+        <v>1.62</v>
+      </c>
+      <c r="E57" s="80">
+        <f t="shared" si="15"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F57" s="6">
+        <f t="shared" si="16"/>
+        <v>0.41728395061728391</v>
+      </c>
+      <c r="G57" s="52">
+        <f t="shared" si="45"/>
+        <v>2.3964497041420123</v>
+      </c>
+      <c r="H57" s="1">
+        <v>999</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K57" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="3">
+        <v>54</v>
+      </c>
+      <c r="C58" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="D58" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="E58" s="80">
+        <f t="shared" si="15"/>
+        <v>0.65789473684210531</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" si="16"/>
+        <v>0.4578947368421053</v>
+      </c>
+      <c r="G58" s="52">
+        <f t="shared" si="45"/>
+        <v>2.1839080459770113</v>
+      </c>
+      <c r="H58" s="1">
+        <v>999</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J58" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K58" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B59" s="3">
+        <v>55</v>
+      </c>
+      <c r="C59" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="E59" s="80">
+        <f t="shared" si="15"/>
+        <v>0.57471264367816088</v>
+      </c>
+      <c r="F59" s="6">
+        <f t="shared" si="16"/>
+        <v>0.37471264367816087</v>
+      </c>
+      <c r="G59" s="52">
+        <v>2.68</v>
+      </c>
+      <c r="H59" s="1">
+        <v>999</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K59" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B60" s="3">
+        <v>56</v>
+      </c>
+      <c r="C60" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="E60" s="80">
+        <f t="shared" si="15"/>
+        <v>0.8</v>
+      </c>
+      <c r="F60" s="6">
+        <f t="shared" si="16"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G60" s="52">
+        <f t="shared" si="45"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="H60" s="1">
+        <v>999</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J60" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K60" s="27">
+        <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61" s="3">
+        <v>57</v>
+      </c>
+      <c r="C61" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="E61" s="80">
+        <f t="shared" si="15"/>
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="F61" s="6">
+        <f t="shared" si="16"/>
+        <v>0.49444444444444441</v>
+      </c>
+      <c r="G61" s="52">
+        <f t="shared" si="45"/>
+        <v>2.0224719101123596</v>
+      </c>
+      <c r="H61" s="1">
+        <v>999</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J61" s="26">
+        <f t="shared" si="43"/>
+        <v>-1</v>
+      </c>
+      <c r="K61" s="27">
+        <f t="shared" si="44"/>
         <v>-55.55</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B3AFEE-C8B2-4D74-BA35-644A8561F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211BFC10-7E2B-49E9-A8C0-187476673DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -5695,9 +5695,7 @@
       <c r="H52" s="1">
         <v>999</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I52" s="1"/>
       <c r="J52" s="26">
         <f t="shared" ref="J52:J61" si="43">IF(H52=0,0,IF(I52="WON",(G52*0.94-1),-1))</f>
         <v>-1</v>
@@ -5732,9 +5730,7 @@
       <c r="H53" s="1">
         <v>999</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I53" s="1"/>
       <c r="J53" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5769,9 +5765,7 @@
       <c r="H54" s="1">
         <v>999</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I54" s="1"/>
       <c r="J54" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5806,9 +5800,7 @@
       <c r="H55" s="1">
         <v>999</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I55" s="1"/>
       <c r="J55" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5842,9 +5834,7 @@
       <c r="H56" s="1">
         <v>999</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I56" s="1"/>
       <c r="J56" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5879,9 +5869,7 @@
       <c r="H57" s="1">
         <v>999</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I57" s="1"/>
       <c r="J57" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5916,9 +5904,7 @@
       <c r="H58" s="1">
         <v>999</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I58" s="1"/>
       <c r="J58" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5952,9 +5938,7 @@
       <c r="H59" s="1">
         <v>999</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I59" s="1"/>
       <c r="J59" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5989,9 +5973,7 @@
       <c r="H60" s="1">
         <v>999</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I60" s="1"/>
       <c r="J60" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -6026,9 +6008,7 @@
       <c r="H61" s="1">
         <v>999</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I61" s="1"/>
       <c r="J61" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211BFC10-7E2B-49E9-A8C0-187476673DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856CB87F-BAB1-4030-B1C7-2C527459C098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -387,6 +387,33 @@
   </si>
   <si>
     <t>Rublev</t>
+  </si>
+  <si>
+    <t>Hurkacz</t>
+  </si>
+  <si>
+    <t>Nakashima</t>
+  </si>
+  <si>
+    <t>De Jong</t>
+  </si>
+  <si>
+    <t>Tiafoe</t>
+  </si>
+  <si>
+    <t>Atmane</t>
+  </si>
+  <si>
+    <t>Ostapenko</t>
+  </si>
+  <si>
+    <t>Udvardy</t>
+  </si>
+  <si>
+    <t>Anisimova</t>
+  </si>
+  <si>
+    <t>Shelton</t>
   </si>
 </sst>
 </file>
@@ -3889,7 +3916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L61"/>
+  <dimension ref="B2:L73"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -5693,16 +5720,18 @@
         <v>1.4766839378238339</v>
       </c>
       <c r="H52" s="1">
-        <v>999</v>
-      </c>
-      <c r="I52" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J52" s="26">
         <f t="shared" ref="J52:J61" si="43">IF(H52=0,0,IF(I52="WON",(G52*0.94-1),-1))</f>
-        <v>-1</v>
+        <v>0.38808290155440384</v>
       </c>
       <c r="K52" s="27">
         <f t="shared" ref="K52:K61" si="44">J52*J$3</f>
-        <v>-55.55</v>
+        <v>21.558005181347131</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -5728,16 +5757,18 @@
         <v>2.9365079365079372</v>
       </c>
       <c r="H53" s="1">
-        <v>999</v>
-      </c>
-      <c r="I53" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J53" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>1.7603174603174607</v>
       </c>
       <c r="K53" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>97.785634920634934</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
@@ -5763,9 +5794,11 @@
         <v>1.7024128686327078</v>
       </c>
       <c r="H54" s="1">
-        <v>999</v>
-      </c>
-      <c r="I54" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J54" s="26">
         <f t="shared" si="43"/>
         <v>-1</v>
@@ -5798,16 +5831,18 @@
         <v>1.3451776649746197</v>
       </c>
       <c r="H55" s="1">
-        <v>999</v>
-      </c>
-      <c r="I55" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J55" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.3">
@@ -5832,16 +5867,18 @@
         <v>2.82</v>
       </c>
       <c r="H56" s="1">
-        <v>999</v>
-      </c>
-      <c r="I56" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J56" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K56" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
@@ -5867,16 +5904,18 @@
         <v>2.3964497041420123</v>
       </c>
       <c r="H57" s="1">
-        <v>999</v>
-      </c>
-      <c r="I57" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J57" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K57" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.3">
@@ -5902,16 +5941,18 @@
         <v>2.1839080459770113</v>
       </c>
       <c r="H58" s="1">
-        <v>999</v>
-      </c>
-      <c r="I58" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J58" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>1.0528735632183905</v>
       </c>
       <c r="K58" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>58.487126436781594</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
@@ -5936,16 +5977,18 @@
         <v>2.68</v>
       </c>
       <c r="H59" s="1">
-        <v>999</v>
-      </c>
-      <c r="I59" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J59" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K59" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
@@ -5971,16 +6014,18 @@
         <v>1.6666666666666665</v>
       </c>
       <c r="H60" s="1">
-        <v>999</v>
-      </c>
-      <c r="I60" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J60" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K60" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
@@ -6015,6 +6060,418 @@
       </c>
       <c r="K61" s="27">
         <f t="shared" si="44"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B62" s="3">
+        <v>58</v>
+      </c>
+      <c r="C62" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1.78</v>
+      </c>
+      <c r="E62" s="80">
+        <f t="shared" ref="E62:E73" si="46">1/D62</f>
+        <v>0.5617977528089888</v>
+      </c>
+      <c r="F62" s="6">
+        <f t="shared" ref="F62:F73" si="47">E62-0.2</f>
+        <v>0.36179775280898879</v>
+      </c>
+      <c r="G62" s="52">
+        <f t="shared" ref="G62:G73" si="48">1/F62</f>
+        <v>2.7639751552795029</v>
+      </c>
+      <c r="H62" s="1">
+        <v>999</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="26">
+        <f t="shared" ref="J62:J73" si="49">IF(H62=0,0,IF(I62="WON",(G62*0.94-1),-1))</f>
+        <v>-1</v>
+      </c>
+      <c r="K62" s="27">
+        <f t="shared" ref="K62:K73" si="50">J62*J$3</f>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B63" s="3">
+        <v>59</v>
+      </c>
+      <c r="C63" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="E63" s="80">
+        <f t="shared" si="46"/>
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="F63" s="6">
+        <f t="shared" si="47"/>
+        <v>0.54074074074074074</v>
+      </c>
+      <c r="G63" s="52">
+        <f t="shared" si="48"/>
+        <v>1.8493150684931507</v>
+      </c>
+      <c r="H63" s="1">
+        <v>999</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K63" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="3">
+        <v>60</v>
+      </c>
+      <c r="C64" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="E64" s="80">
+        <f t="shared" si="46"/>
+        <v>0.59171597633136097</v>
+      </c>
+      <c r="F64" s="6">
+        <f t="shared" si="47"/>
+        <v>0.39171597633136096</v>
+      </c>
+      <c r="G64" s="52">
+        <v>2.56</v>
+      </c>
+      <c r="H64" s="1">
+        <v>999</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K64" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B65" s="3">
+        <v>61</v>
+      </c>
+      <c r="C65" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" s="7">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E65" s="80">
+        <f t="shared" si="46"/>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F65" s="6">
+        <f t="shared" si="47"/>
+        <v>0.70090090090090085</v>
+      </c>
+      <c r="G65" s="52">
+        <f t="shared" si="48"/>
+        <v>1.4267352185089976</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K65" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B66" s="3">
+        <v>62</v>
+      </c>
+      <c r="C66" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="E66" s="80">
+        <f t="shared" si="46"/>
+        <v>0.76923076923076916</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="47"/>
+        <v>0.56923076923076921</v>
+      </c>
+      <c r="G66" s="52">
+        <f t="shared" si="48"/>
+        <v>1.7567567567567568</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K66" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B67" s="3">
+        <v>63</v>
+      </c>
+      <c r="C67" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="D67" s="7">
+        <v>1.24</v>
+      </c>
+      <c r="E67" s="80">
+        <f t="shared" si="46"/>
+        <v>0.80645161290322587</v>
+      </c>
+      <c r="F67" s="6">
+        <f t="shared" si="47"/>
+        <v>0.6064516129032258</v>
+      </c>
+      <c r="G67" s="52">
+        <f t="shared" si="48"/>
+        <v>1.6489361702127661</v>
+      </c>
+      <c r="H67" s="1">
+        <v>999</v>
+      </c>
+      <c r="J67" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K67" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B68" s="3">
+        <v>64</v>
+      </c>
+      <c r="C68" s="79" t="s">
+        <v>103</v>
+      </c>
+      <c r="D68" s="7">
+        <v>1.78</v>
+      </c>
+      <c r="E68" s="80">
+        <f t="shared" si="46"/>
+        <v>0.5617977528089888</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" si="47"/>
+        <v>0.36179775280898879</v>
+      </c>
+      <c r="G68" s="52">
+        <f t="shared" si="48"/>
+        <v>2.7639751552795029</v>
+      </c>
+      <c r="H68" s="1">
+        <v>999</v>
+      </c>
+      <c r="J68" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K68" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B69" s="3">
+        <v>65</v>
+      </c>
+      <c r="C69" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="D69" s="7">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E69" s="80">
+        <f t="shared" si="46"/>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F69" s="6">
+        <f t="shared" si="47"/>
+        <v>0.70090090090090085</v>
+      </c>
+      <c r="G69" s="52">
+        <f t="shared" si="48"/>
+        <v>1.4267352185089976</v>
+      </c>
+      <c r="H69" s="1">
+        <v>999</v>
+      </c>
+      <c r="J69" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K69" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B70" s="3">
+        <v>66</v>
+      </c>
+      <c r="C70" s="79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D70" s="7">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E70" s="80">
+        <f t="shared" si="46"/>
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="F70" s="6">
+        <f t="shared" si="47"/>
+        <v>0.71743119266055033</v>
+      </c>
+      <c r="G70" s="52">
+        <f t="shared" si="48"/>
+        <v>1.3938618925831205</v>
+      </c>
+      <c r="H70" s="1">
+        <v>999</v>
+      </c>
+      <c r="J70" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K70" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B71" s="3">
+        <v>67</v>
+      </c>
+      <c r="C71" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="D71" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="E71" s="80">
+        <f t="shared" si="46"/>
+        <v>0.77519379844961234</v>
+      </c>
+      <c r="F71" s="6">
+        <f t="shared" si="47"/>
+        <v>0.57519379844961227</v>
+      </c>
+      <c r="G71" s="52">
+        <f t="shared" si="48"/>
+        <v>1.7385444743935314</v>
+      </c>
+      <c r="H71" s="1">
+        <v>999</v>
+      </c>
+      <c r="J71" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K71" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B72" s="3">
+        <v>68</v>
+      </c>
+      <c r="C72" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72" s="7">
+        <v>1.07</v>
+      </c>
+      <c r="E72" s="80">
+        <f t="shared" si="46"/>
+        <v>0.93457943925233644</v>
+      </c>
+      <c r="F72" s="6">
+        <f t="shared" si="47"/>
+        <v>0.73457943925233637</v>
+      </c>
+      <c r="G72" s="52">
+        <f t="shared" si="48"/>
+        <v>1.3613231552162852</v>
+      </c>
+      <c r="H72" s="1">
+        <v>999</v>
+      </c>
+      <c r="J72" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K72" s="27">
+        <f t="shared" si="50"/>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B73" s="3">
+        <v>69</v>
+      </c>
+      <c r="C73" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="D73" s="7">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E73" s="80">
+        <f t="shared" si="46"/>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F73" s="6">
+        <f t="shared" si="47"/>
+        <v>0.70090090090090085</v>
+      </c>
+      <c r="G73" s="52">
+        <f t="shared" si="48"/>
+        <v>1.4267352185089976</v>
+      </c>
+      <c r="H73" s="1">
+        <v>999</v>
+      </c>
+      <c r="J73" s="26">
+        <f t="shared" si="49"/>
+        <v>-1</v>
+      </c>
+      <c r="K73" s="27">
+        <f t="shared" si="50"/>
         <v>-55.55</v>
       </c>
     </row>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856CB87F-BAB1-4030-B1C7-2C527459C098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF92D90-C171-48F3-9704-65153769D640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -6051,16 +6051,18 @@
         <v>2.0224719101123596</v>
       </c>
       <c r="H61" s="1">
-        <v>999</v>
-      </c>
-      <c r="I61" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J61" s="26">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0.90112359550561782</v>
       </c>
       <c r="K61" s="27">
         <f t="shared" si="44"/>
-        <v>-55.55</v>
+        <v>50.05741573033707</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.3">
@@ -6086,16 +6088,18 @@
         <v>2.7639751552795029</v>
       </c>
       <c r="H62" s="1">
-        <v>999</v>
-      </c>
-      <c r="I62" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J62" s="26">
         <f t="shared" ref="J62:J73" si="49">IF(H62=0,0,IF(I62="WON",(G62*0.94-1),-1))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K62" s="27">
         <f t="shared" ref="K62:K73" si="50">J62*J$3</f>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
@@ -6121,16 +6125,18 @@
         <v>1.8493150684931507</v>
       </c>
       <c r="H63" s="1">
-        <v>999</v>
-      </c>
-      <c r="I63" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J63" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
@@ -6155,16 +6161,18 @@
         <v>2.56</v>
       </c>
       <c r="H64" s="1">
-        <v>999</v>
-      </c>
-      <c r="I64" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J64" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.3">
@@ -6192,14 +6200,16 @@
       <c r="H65" s="1">
         <v>1</v>
       </c>
-      <c r="I65" s="1"/>
+      <c r="I65" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J65" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0.34113110539845781</v>
       </c>
       <c r="K65" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>18.949832904884332</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
@@ -6227,7 +6237,9 @@
       <c r="H66" s="1">
         <v>1</v>
       </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J66" s="26">
         <f t="shared" si="49"/>
         <v>-1</v>
@@ -6260,15 +6272,18 @@
         <v>1.6489361702127661</v>
       </c>
       <c r="H67" s="1">
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J67" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K67" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.3">
@@ -6294,7 +6309,10 @@
         <v>2.7639751552795029</v>
       </c>
       <c r="H68" s="1">
-        <v>999</v>
+        <v>1</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J68" s="26">
         <f t="shared" si="49"/>
@@ -6328,15 +6346,18 @@
         <v>1.4267352185089976</v>
       </c>
       <c r="H69" s="1">
-        <v>999</v>
+        <v>1</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J69" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0.34113110539845781</v>
       </c>
       <c r="K69" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>18.949832904884332</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.3">
@@ -6362,15 +6383,18 @@
         <v>1.3938618925831205</v>
       </c>
       <c r="H70" s="1">
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J70" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K70" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.3">
@@ -6396,15 +6420,18 @@
         <v>1.7385444743935314</v>
       </c>
       <c r="H71" s="1">
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J71" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K71" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.3">
@@ -6430,15 +6457,18 @@
         <v>1.3613231552162852</v>
       </c>
       <c r="H72" s="1">
-        <v>999</v>
+        <v>1</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J72" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0.27964376590330797</v>
       </c>
       <c r="K72" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>15.534211195928757</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
@@ -6464,15 +6494,18 @@
         <v>1.4267352185089976</v>
       </c>
       <c r="H73" s="1">
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J73" s="26">
         <f t="shared" si="49"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="27">
         <f t="shared" si="50"/>
-        <v>-55.55</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF92D90-C171-48F3-9704-65153769D640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA93D05-02DC-4FDE-9421-FB33F8151E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="111">
   <si>
     <t>ID</t>
   </si>
@@ -414,6 +414,21 @@
   </si>
   <si>
     <t>Shelton</t>
+  </si>
+  <si>
+    <t>Tirante</t>
+  </si>
+  <si>
+    <t>Cilic</t>
+  </si>
+  <si>
+    <t>Medvedev</t>
+  </si>
+  <si>
+    <t>Sabalenka</t>
+  </si>
+  <si>
+    <t>Moutet</t>
   </si>
 </sst>
 </file>
@@ -3916,7 +3931,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L73"/>
+  <dimension ref="B2:L84"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -6076,15 +6091,15 @@
         <v>1.78</v>
       </c>
       <c r="E62" s="80">
-        <f t="shared" ref="E62:E73" si="46">1/D62</f>
+        <f t="shared" ref="E62:E78" si="46">1/D62</f>
         <v>0.5617977528089888</v>
       </c>
       <c r="F62" s="6">
-        <f t="shared" ref="F62:F73" si="47">E62-0.2</f>
+        <f t="shared" ref="F62:F78" si="47">E62-0.2</f>
         <v>0.36179775280898879</v>
       </c>
       <c r="G62" s="52">
-        <f t="shared" ref="G62:G73" si="48">1/F62</f>
+        <f t="shared" ref="G62:G74" si="48">1/F62</f>
         <v>2.7639751552795029</v>
       </c>
       <c r="H62" s="1">
@@ -6506,6 +6521,149 @@
       <c r="K73" s="27">
         <f t="shared" si="50"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B74" s="3">
+        <v>70</v>
+      </c>
+      <c r="C74" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="E74" s="80">
+        <f t="shared" si="46"/>
+        <v>0.52356020942408377</v>
+      </c>
+      <c r="F74" s="6">
+        <f t="shared" si="47"/>
+        <v>0.32356020942408376</v>
+      </c>
+      <c r="G74" s="52">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B75" s="3">
+        <v>71</v>
+      </c>
+      <c r="C75" s="79" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="E75" s="80">
+        <f t="shared" si="46"/>
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="F75" s="6">
+        <f t="shared" si="47"/>
+        <v>0.55757575757575761</v>
+      </c>
+      <c r="G75" s="52">
+        <f>1/F75</f>
+        <v>1.7934782608695652</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B76" s="3">
+        <v>72</v>
+      </c>
+      <c r="C76" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="E76" s="80">
+        <f t="shared" si="46"/>
+        <v>0.94339622641509424</v>
+      </c>
+      <c r="F76" s="6">
+        <f t="shared" si="47"/>
+        <v>0.74339622641509417</v>
+      </c>
+      <c r="G76" s="52">
+        <f>1/F76</f>
+        <v>1.3451776649746197</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B77" s="3">
+        <v>73</v>
+      </c>
+      <c r="C77" s="79" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="E77" s="80">
+        <f t="shared" si="46"/>
+        <v>0.94339622641509424</v>
+      </c>
+      <c r="F77" s="6">
+        <f t="shared" si="47"/>
+        <v>0.74339622641509417</v>
+      </c>
+      <c r="G77" s="52">
+        <f>1/F77</f>
+        <v>1.3451776649746197</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B78" s="3">
+        <v>74</v>
+      </c>
+      <c r="C78" s="79" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" s="7">
+        <v>1.66</v>
+      </c>
+      <c r="E78" s="80">
+        <f t="shared" si="46"/>
+        <v>0.60240963855421692</v>
+      </c>
+      <c r="F78" s="6">
+        <f t="shared" si="47"/>
+        <v>0.40240963855421691</v>
+      </c>
+      <c r="G78" s="52">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B79" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B80" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B83" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B84" s="3">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA93D05-02DC-4FDE-9421-FB33F8151E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F344700E-0738-47CC-8053-4555535B23BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -429,6 +429,18 @@
   </si>
   <si>
     <t>Moutet</t>
+  </si>
+  <si>
+    <t>Cerundolo</t>
+  </si>
+  <si>
+    <t>Olinykova</t>
+  </si>
+  <si>
+    <t>Auger-Aliassime</t>
+  </si>
+  <si>
+    <t>Rybakina</t>
   </si>
 </sst>
 </file>
@@ -6091,15 +6103,15 @@
         <v>1.78</v>
       </c>
       <c r="E62" s="80">
-        <f t="shared" ref="E62:E78" si="46">1/D62</f>
+        <f t="shared" ref="E62:E84" si="46">1/D62</f>
         <v>0.5617977528089888</v>
       </c>
       <c r="F62" s="6">
-        <f t="shared" ref="F62:F78" si="47">E62-0.2</f>
+        <f t="shared" ref="F62:F84" si="47">E62-0.2</f>
         <v>0.36179775280898879</v>
       </c>
       <c r="G62" s="52">
-        <f t="shared" ref="G62:G74" si="48">1/F62</f>
+        <f t="shared" ref="G62:G73" si="48">1/F62</f>
         <v>2.7639751552795029</v>
       </c>
       <c r="H62" s="1">
@@ -6544,6 +6556,20 @@
       <c r="G74" s="52">
         <v>3.1</v>
       </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J74" s="26">
+        <f t="shared" ref="J74:J84" si="51">IF(H74=0,0,IF(I74="WON",(G74*0.94-1),-1))</f>
+        <v>1.9139999999999997</v>
+      </c>
+      <c r="K74" s="27">
+        <f t="shared" ref="K74:K84" si="52">J74*J$3</f>
+        <v>106.32269999999998</v>
+      </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="3">
@@ -6567,6 +6593,20 @@
         <f>1/F75</f>
         <v>1.7934782608695652</v>
       </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J75" s="26">
+        <f t="shared" si="51"/>
+        <v>-1</v>
+      </c>
+      <c r="K75" s="27">
+        <f t="shared" si="52"/>
+        <v>-55.55</v>
+      </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="3">
@@ -6590,6 +6630,20 @@
         <f>1/F76</f>
         <v>1.3451776649746197</v>
       </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" s="26">
+        <f t="shared" si="51"/>
+        <v>-1</v>
+      </c>
+      <c r="K76" s="27">
+        <f t="shared" si="52"/>
+        <v>-55.55</v>
+      </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="3">
@@ -6613,6 +6667,20 @@
         <f>1/F77</f>
         <v>1.3451776649746197</v>
       </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J77" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="3">
@@ -6635,35 +6703,241 @@
       <c r="G78" s="52">
         <v>2.5</v>
       </c>
+      <c r="H78" s="1">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J78" s="26">
+        <f t="shared" si="51"/>
+        <v>-1</v>
+      </c>
+      <c r="K78" s="27">
+        <f t="shared" si="52"/>
+        <v>-55.55</v>
+      </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="3">
         <v>75</v>
       </c>
+      <c r="C79" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="D79" s="7">
+        <v>1.28</v>
+      </c>
+      <c r="E79" s="80">
+        <f t="shared" si="46"/>
+        <v>0.78125</v>
+      </c>
+      <c r="F79" s="6">
+        <f t="shared" si="47"/>
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="G79" s="52">
+        <f t="shared" ref="G79:G84" si="53">1/F79</f>
+        <v>1.7204301075268815</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J79" s="26">
+        <f t="shared" si="51"/>
+        <v>-1</v>
+      </c>
+      <c r="K79" s="27">
+        <f t="shared" si="52"/>
+        <v>-55.55</v>
+      </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="3">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C80" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D80" s="7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E80" s="80">
+        <f t="shared" si="46"/>
+        <v>0.86956521739130443</v>
+      </c>
+      <c r="F80" s="6">
+        <f t="shared" si="47"/>
+        <v>0.66956521739130448</v>
+      </c>
+      <c r="G80" s="52">
+        <f t="shared" si="53"/>
+        <v>1.4935064935064932</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J80" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="3">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C81" s="79" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="7">
+        <v>1.27</v>
+      </c>
+      <c r="E81" s="80">
+        <f t="shared" si="46"/>
+        <v>0.78740157480314954</v>
+      </c>
+      <c r="F81" s="6">
+        <f t="shared" si="47"/>
+        <v>0.58740157480314958</v>
+      </c>
+      <c r="G81" s="52">
+        <f t="shared" si="53"/>
+        <v>1.7024128686327078</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J81" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K81" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="3">
         <v>78</v>
       </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C82" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="E82" s="80">
+        <f t="shared" si="46"/>
+        <v>0.66225165562913912</v>
+      </c>
+      <c r="F82" s="6">
+        <f t="shared" si="47"/>
+        <v>0.46225165562913911</v>
+      </c>
+      <c r="G82" s="52">
+        <f t="shared" si="53"/>
+        <v>2.1633237822349569</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J82" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="3">
         <v>79</v>
       </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C83" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="D83" s="7">
+        <v>1.34</v>
+      </c>
+      <c r="E83" s="80">
+        <f t="shared" si="46"/>
+        <v>0.74626865671641784</v>
+      </c>
+      <c r="F83" s="6">
+        <f t="shared" si="47"/>
+        <v>0.54626865671641789</v>
+      </c>
+      <c r="G83" s="52">
+        <f t="shared" si="53"/>
+        <v>1.8306010928961749</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J83" s="26">
+        <f t="shared" si="51"/>
+        <v>0.72076502732240422</v>
+      </c>
+      <c r="K83" s="27">
+        <f t="shared" si="52"/>
+        <v>40.038497267759553</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="3">
         <v>80</v>
+      </c>
+      <c r="C84" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" s="7">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E84" s="80">
+        <f t="shared" si="46"/>
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="F84" s="6">
+        <f t="shared" si="47"/>
+        <v>0.71743119266055033</v>
+      </c>
+      <c r="G84" s="52">
+        <f t="shared" si="53"/>
+        <v>1.3938618925831205</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J84" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K84" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F344700E-0738-47CC-8053-4555535B23BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28264E47-3593-4465-8AF9-894880A65E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="123">
   <si>
     <t>ID</t>
   </si>
@@ -441,6 +441,30 @@
   </si>
   <si>
     <t>Rybakina</t>
+  </si>
+  <si>
+    <t>Humbert</t>
+  </si>
+  <si>
+    <t>Carreno Busta</t>
+  </si>
+  <si>
+    <t>Jodar</t>
+  </si>
+  <si>
+    <t>Kecmanovic</t>
+  </si>
+  <si>
+    <t>Prizmic</t>
+  </si>
+  <si>
+    <t>Michelsen</t>
+  </si>
+  <si>
+    <t>Cirstea</t>
+  </si>
+  <si>
+    <t>Frech</t>
   </si>
 </sst>
 </file>
@@ -3943,7 +3967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L84"/>
+  <dimension ref="B2:L94"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -6103,11 +6127,11 @@
         <v>1.78</v>
       </c>
       <c r="E62" s="80">
-        <f t="shared" ref="E62:E84" si="46">1/D62</f>
+        <f t="shared" ref="E62:E94" si="46">1/D62</f>
         <v>0.5617977528089888</v>
       </c>
       <c r="F62" s="6">
-        <f t="shared" ref="F62:F84" si="47">E62-0.2</f>
+        <f t="shared" ref="F62:F94" si="47">E62-0.2</f>
         <v>0.36179775280898879</v>
       </c>
       <c r="G62" s="52">
@@ -6563,11 +6587,11 @@
         <v>7</v>
       </c>
       <c r="J74" s="26">
-        <f t="shared" ref="J74:J84" si="51">IF(H74=0,0,IF(I74="WON",(G74*0.94-1),-1))</f>
+        <f t="shared" ref="J74:J94" si="51">IF(H74=0,0,IF(I74="WON",(G74*0.94-1),-1))</f>
         <v>1.9139999999999997</v>
       </c>
       <c r="K74" s="27">
-        <f t="shared" ref="K74:K84" si="52">J74*J$3</f>
+        <f t="shared" ref="K74:K94" si="52">J74*J$3</f>
         <v>106.32269999999998</v>
       </c>
     </row>
@@ -6737,7 +6761,7 @@
         <v>0.58125000000000004</v>
       </c>
       <c r="G79" s="52">
-        <f t="shared" ref="G79:G84" si="53">1/F79</f>
+        <f t="shared" ref="G79:G94" si="53">1/F79</f>
         <v>1.7204301075268815</v>
       </c>
       <c r="H79" s="1">
@@ -6928,14 +6952,349 @@
       <c r="H84" s="1">
         <v>0</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="I84" s="1"/>
       <c r="J84" s="26">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="K84" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B85" s="3">
+        <v>81</v>
+      </c>
+      <c r="C85" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="D85" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="E85" s="80">
+        <f t="shared" si="46"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F85" s="6">
+        <f t="shared" si="47"/>
+        <v>0.37142857142857139</v>
+      </c>
+      <c r="G85" s="52">
+        <v>2.7</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="J85" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B86" s="3">
+        <v>82</v>
+      </c>
+      <c r="C86" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="E86" s="80">
+        <f t="shared" si="46"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F86" s="6">
+        <f t="shared" si="47"/>
+        <v>0.51428571428571423</v>
+      </c>
+      <c r="G86" s="52">
+        <f t="shared" si="53"/>
+        <v>1.9444444444444446</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="J86" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B87" s="3">
+        <v>83</v>
+      </c>
+      <c r="C87" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="D87" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="E87" s="80">
+        <f t="shared" si="46"/>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="F87" s="6">
+        <f t="shared" si="47"/>
+        <v>0.75238095238095237</v>
+      </c>
+      <c r="G87" s="52">
+        <f t="shared" si="53"/>
+        <v>1.3291139240506329</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+      <c r="J87" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K87" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B88" s="3">
+        <v>84</v>
+      </c>
+      <c r="C88" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="D88" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="E88" s="80">
+        <f t="shared" si="46"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="F88" s="6">
+        <f t="shared" si="47"/>
+        <v>0.40606060606060607</v>
+      </c>
+      <c r="G88" s="52">
+        <f t="shared" si="53"/>
+        <v>2.4626865671641789</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B89" s="3">
+        <v>85</v>
+      </c>
+      <c r="C89" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="D89" s="7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E89" s="80">
+        <f t="shared" si="46"/>
+        <v>0.87719298245614041</v>
+      </c>
+      <c r="F89" s="6">
+        <f t="shared" si="47"/>
+        <v>0.67719298245614046</v>
+      </c>
+      <c r="G89" s="52">
+        <f t="shared" si="53"/>
+        <v>1.4766839378238339</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+      <c r="J89" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K89" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B90" s="3">
+        <v>86</v>
+      </c>
+      <c r="C90" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="D90" s="7">
+        <v>1.96</v>
+      </c>
+      <c r="E90" s="80">
+        <f t="shared" si="46"/>
+        <v>0.51020408163265307</v>
+      </c>
+      <c r="F90" s="6">
+        <f t="shared" si="47"/>
+        <v>0.31020408163265306</v>
+      </c>
+      <c r="G90" s="52">
+        <v>3.25</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+      <c r="J90" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B91" s="3">
+        <v>87</v>
+      </c>
+      <c r="C91" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="D91" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="E91" s="80">
+        <f t="shared" si="46"/>
+        <v>0.64102564102564097</v>
+      </c>
+      <c r="F91" s="6">
+        <f t="shared" si="47"/>
+        <v>0.44102564102564096</v>
+      </c>
+      <c r="G91" s="52">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="J91" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K91" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B92" s="3">
+        <v>88</v>
+      </c>
+      <c r="C92" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" s="7">
+        <v>1.07</v>
+      </c>
+      <c r="E92" s="80">
+        <f t="shared" si="46"/>
+        <v>0.93457943925233644</v>
+      </c>
+      <c r="F92" s="6">
+        <f t="shared" si="47"/>
+        <v>0.73457943925233637</v>
+      </c>
+      <c r="G92" s="52">
+        <f t="shared" si="53"/>
+        <v>1.3613231552162852</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="J92" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K92" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B93" s="3">
+        <v>89</v>
+      </c>
+      <c r="C93" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="D93" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="E93" s="80">
+        <f t="shared" si="46"/>
+        <v>0.8</v>
+      </c>
+      <c r="F93" s="6">
+        <f t="shared" si="47"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G93" s="52">
+        <f t="shared" si="53"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+      <c r="J93" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K93" s="27">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B94" s="3">
+        <v>90</v>
+      </c>
+      <c r="C94" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="D94" s="7">
+        <v>1.71</v>
+      </c>
+      <c r="E94" s="80">
+        <f t="shared" si="46"/>
+        <v>0.58479532163742687</v>
+      </c>
+      <c r="F94" s="6">
+        <f t="shared" si="47"/>
+        <v>0.38479532163742686</v>
+      </c>
+      <c r="G94" s="52">
+        <f t="shared" si="53"/>
+        <v>2.5987841945288759</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="J94" s="26">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="27">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28264E47-3593-4465-8AF9-894880A65E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C875868C-5CB4-4F8B-9332-14BBF871F63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="125">
   <si>
     <t>ID</t>
   </si>
@@ -465,6 +465,12 @@
   </si>
   <si>
     <t>Frech</t>
+  </si>
+  <si>
+    <t>Darderi</t>
+  </si>
+  <si>
+    <t>Tsitsipas</t>
   </si>
 </sst>
 </file>
@@ -721,7 +727,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -993,6 +999,18 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1334,7 +1352,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K74"/>
+  <dimension ref="B2:K81"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -3641,11 +3659,11 @@
         <v>1.62</v>
       </c>
       <c r="E66" s="40">
-        <f t="shared" ref="E66:E74" si="27">1/D66</f>
+        <f t="shared" ref="E66:E76" si="27">1/D66</f>
         <v>0.61728395061728392</v>
       </c>
       <c r="F66" s="58">
-        <f t="shared" ref="F66:F74" si="28">E66-0.2</f>
+        <f t="shared" ref="F66:F76" si="28">E66-0.2</f>
         <v>0.41728395061728391</v>
       </c>
       <c r="G66" s="87">
@@ -3924,7 +3942,7 @@
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="65">
+      <c r="B74" s="64">
         <v>70</v>
       </c>
       <c r="C74" s="90" t="s">
@@ -3957,6 +3975,139 @@
       <c r="K74" s="29">
         <f t="shared" si="31"/>
         <v>-55.55</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="63">
+        <v>71</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="92">
+        <v>1.37</v>
+      </c>
+      <c r="E75" s="41">
+        <f t="shared" si="27"/>
+        <v>0.72992700729927007</v>
+      </c>
+      <c r="F75" s="93">
+        <f t="shared" si="28"/>
+        <v>0.52992700729927011</v>
+      </c>
+      <c r="G75" s="91">
+        <f>1/F75</f>
+        <v>1.887052341597796</v>
+      </c>
+      <c r="H75" s="94">
+        <v>0</v>
+      </c>
+      <c r="I75" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="78">
+        <f t="shared" ref="J75:J81" si="32">IF(H75=0,0,IF(I75="WON",(G75-1)*0.94,-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K75" s="29">
+        <f t="shared" ref="K75:K81" si="33">J75*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="64">
+        <v>72</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="92">
+        <v>1.29</v>
+      </c>
+      <c r="E76" s="41">
+        <f t="shared" si="27"/>
+        <v>0.77519379844961234</v>
+      </c>
+      <c r="F76" s="93">
+        <f t="shared" si="28"/>
+        <v>0.57519379844961227</v>
+      </c>
+      <c r="G76" s="91">
+        <f>1/F76</f>
+        <v>1.7385444743935314</v>
+      </c>
+      <c r="J76" s="78">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K76" s="29">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="64">
+        <v>73</v>
+      </c>
+      <c r="J77" s="78">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="29">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="64">
+        <v>74</v>
+      </c>
+      <c r="J78" s="78">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="29">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="64">
+        <v>75</v>
+      </c>
+      <c r="J79" s="78">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="29">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="64">
+        <v>76</v>
+      </c>
+      <c r="J80" s="78">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="29">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="65">
+        <v>77</v>
+      </c>
+      <c r="J81" s="78">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K81" s="29">
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3967,7 +4118,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L94"/>
+  <dimension ref="B2:L102"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -6127,11 +6278,11 @@
         <v>1.78</v>
       </c>
       <c r="E62" s="80">
-        <f t="shared" ref="E62:E94" si="46">1/D62</f>
+        <f t="shared" ref="E62:E101" si="46">1/D62</f>
         <v>0.5617977528089888</v>
       </c>
       <c r="F62" s="6">
-        <f t="shared" ref="F62:F94" si="47">E62-0.2</f>
+        <f t="shared" ref="F62:F101" si="47">E62-0.2</f>
         <v>0.36179775280898879</v>
       </c>
       <c r="G62" s="52">
@@ -6761,7 +6912,7 @@
         <v>0.58125000000000004</v>
       </c>
       <c r="G79" s="52">
-        <f t="shared" ref="G79:G94" si="53">1/F79</f>
+        <f t="shared" ref="G79:G102" si="53">1/F79</f>
         <v>1.7204301075268815</v>
       </c>
       <c r="H79" s="1">
@@ -6950,16 +7101,18 @@
         <v>1.3938618925831205</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
-      </c>
-      <c r="I84" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J84" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K84" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
@@ -6984,15 +7137,18 @@
         <v>2.7</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J85" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K85" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.3">
@@ -7020,6 +7176,9 @@
       <c r="H86" s="1">
         <v>0</v>
       </c>
+      <c r="I86" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J86" s="26">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -7052,15 +7211,18 @@
         <v>1.3291139240506329</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J87" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.24936708860759493</v>
       </c>
       <c r="K87" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>13.852341772151897</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
@@ -7088,6 +7250,9 @@
       <c r="H88" s="1">
         <v>0</v>
       </c>
+      <c r="I88" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J88" s="26">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -7122,6 +7287,9 @@
       <c r="H89" s="1">
         <v>0</v>
       </c>
+      <c r="I89" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J89" s="26">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -7153,15 +7321,18 @@
         <v>3.25</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J90" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K90" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.3">
@@ -7188,6 +7359,9 @@
       <c r="H91" s="1">
         <v>0</v>
       </c>
+      <c r="I91" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J91" s="26">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -7220,15 +7394,18 @@
         <v>1.3613231552162852</v>
       </c>
       <c r="H92" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J92" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.27964376590330797</v>
       </c>
       <c r="K92" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>15.534211195928757</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
@@ -7254,15 +7431,18 @@
         <v>1.6666666666666665</v>
       </c>
       <c r="H93" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J93" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.56666666666666643</v>
       </c>
       <c r="K93" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>31.478333333333318</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
@@ -7288,16 +7468,237 @@
         <v>2.5987841945288759</v>
       </c>
       <c r="H94" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J94" s="26">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K94" s="27">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B95" s="3">
+        <v>91</v>
+      </c>
+      <c r="C95" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D95" s="7">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E95" s="80">
+        <f t="shared" si="46"/>
+        <v>0.86206896551724144</v>
+      </c>
+      <c r="F95" s="6">
+        <f t="shared" si="47"/>
+        <v>0.66206896551724137</v>
+      </c>
+      <c r="G95" s="52">
+        <f t="shared" si="53"/>
+        <v>1.5104166666666667</v>
+      </c>
+      <c r="J95" s="26">
+        <f t="shared" ref="J95:J101" si="54">IF(H95=0,0,IF(I95="WON",(G95*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="27">
+        <f t="shared" ref="K95:K101" si="55">J95*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B96" s="3">
+        <v>92</v>
+      </c>
+      <c r="C96" s="79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D96" s="7">
+        <v>1.19</v>
+      </c>
+      <c r="E96" s="80">
+        <f t="shared" si="46"/>
+        <v>0.84033613445378152</v>
+      </c>
+      <c r="F96" s="6">
+        <f t="shared" si="47"/>
+        <v>0.64033613445378146</v>
+      </c>
+      <c r="G96" s="52">
+        <f t="shared" si="53"/>
+        <v>1.5616797900262469</v>
+      </c>
+      <c r="J96" s="26">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="K96" s="27">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B97" s="3">
+        <v>93</v>
+      </c>
+      <c r="C97" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="D97" s="7">
+        <v>1.38</v>
+      </c>
+      <c r="E97" s="95">
+        <f t="shared" si="46"/>
+        <v>0.7246376811594204</v>
+      </c>
+      <c r="F97" s="6">
+        <f t="shared" si="47"/>
+        <v>0.52463768115942044</v>
+      </c>
+      <c r="G97" s="52">
+        <f t="shared" si="53"/>
+        <v>1.9060773480662978</v>
+      </c>
+      <c r="J97" s="26">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="K97" s="27">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B98" s="3">
+        <v>94</v>
+      </c>
+      <c r="C98" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="D98" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="E98" s="95">
+        <f t="shared" si="46"/>
+        <v>0.70422535211267612</v>
+      </c>
+      <c r="F98" s="6">
+        <f t="shared" si="47"/>
+        <v>0.50422535211267605</v>
+      </c>
+      <c r="G98" s="52">
+        <f t="shared" si="53"/>
+        <v>1.9832402234636872</v>
+      </c>
+      <c r="J98" s="26">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="K98" s="27">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B99" s="3">
+        <v>95</v>
+      </c>
+      <c r="C99" s="79" t="s">
+        <v>123</v>
+      </c>
+      <c r="D99" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="E99" s="95">
+        <f t="shared" si="46"/>
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="F99" s="6">
+        <f t="shared" si="47"/>
+        <v>0.54074074074074074</v>
+      </c>
+      <c r="G99" s="52">
+        <f t="shared" si="53"/>
+        <v>1.8493150684931507</v>
+      </c>
+      <c r="J99" s="26">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="K99" s="27">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B100" s="3">
+        <v>96</v>
+      </c>
+      <c r="C100" s="79" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="E100" s="95">
+        <f t="shared" si="46"/>
+        <v>0.63291139240506322</v>
+      </c>
+      <c r="F100" s="6">
+        <f t="shared" si="47"/>
+        <v>0.43291139240506321</v>
+      </c>
+      <c r="G100" s="52">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="J100" s="26">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="27">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B101" s="3">
+        <v>97</v>
+      </c>
+      <c r="C101" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="E101" s="95">
+        <f t="shared" si="46"/>
+        <v>0.64516129032258063</v>
+      </c>
+      <c r="F101" s="6">
+        <f t="shared" si="47"/>
+        <v>0.44516129032258062</v>
+      </c>
+      <c r="G101" s="52">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J101" s="26">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="K101" s="27">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G102" s="52"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Betfair-Volatility-Trading.xlsx
+++ b/Betfair-Volatility-Trading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timot\Downloads\BetfairExcel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C875868C-5CB4-4F8B-9332-14BBF871F63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642CA5FB-E66B-4CCE-92D0-AB452FF17141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{C475443F-0BD3-43A3-A939-51219F6DA813}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="132">
   <si>
     <t>ID</t>
   </si>
@@ -471,6 +471,27 @@
   </si>
   <si>
     <t>Tsitsipas</t>
+  </si>
+  <si>
+    <t>Eagles</t>
+  </si>
+  <si>
+    <t>Regime change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min </t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Svitolina</t>
+  </si>
+  <si>
+    <t>Berrettini</t>
+  </si>
+  <si>
+    <t>Chwalinska</t>
   </si>
 </sst>
 </file>
@@ -534,7 +555,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,6 +613,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,7 +754,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -994,22 +1021,31 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1352,7 +1388,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K81"/>
+  <dimension ref="B2:K82"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -3659,11 +3695,11 @@
         <v>1.62</v>
       </c>
       <c r="E66" s="40">
-        <f t="shared" ref="E66:E76" si="27">1/D66</f>
+        <f t="shared" ref="E66:E79" si="27">1/D66</f>
         <v>0.61728395061728392</v>
       </c>
       <c r="F66" s="58">
-        <f t="shared" ref="F66:F76" si="28">E66-0.2</f>
+        <f t="shared" ref="F66:F79" si="28">E66-0.2</f>
         <v>0.41728395061728391</v>
       </c>
       <c r="G66" s="87">
@@ -3945,161 +3981,285 @@
       <c r="B74" s="64">
         <v>70</v>
       </c>
-      <c r="C74" s="90" t="s">
+      <c r="C74" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="D74" s="76">
+      <c r="D74" s="1">
         <v>1.88</v>
       </c>
-      <c r="E74" s="42">
+      <c r="E74" s="41">
         <f t="shared" si="27"/>
         <v>0.53191489361702127</v>
       </c>
-      <c r="F74" s="59">
+      <c r="F74" s="54">
         <f t="shared" si="28"/>
         <v>0.33191489361702126</v>
       </c>
-      <c r="G74" s="91">
+      <c r="G74" s="86">
         <v>3.05</v>
       </c>
-      <c r="H74" s="9">
+      <c r="H74" s="51">
         <v>1</v>
       </c>
       <c r="I74" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J74" s="78">
+      <c r="J74" s="77">
         <f t="shared" si="30"/>
         <v>-1</v>
       </c>
-      <c r="K74" s="29">
+      <c r="K74" s="27">
         <f t="shared" si="31"/>
         <v>-55.55</v>
       </c>
     </row>
-    <row r="75" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="63">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B75" s="45">
         <v>71</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="92">
+      <c r="D75" s="75">
         <v>1.37</v>
       </c>
-      <c r="E75" s="41">
+      <c r="E75" s="40">
         <f t="shared" si="27"/>
         <v>0.72992700729927007</v>
       </c>
-      <c r="F75" s="93">
+      <c r="F75" s="58">
         <f t="shared" si="28"/>
         <v>0.52992700729927011</v>
       </c>
-      <c r="G75" s="91">
+      <c r="G75" s="87">
         <f>1/F75</f>
         <v>1.887052341597796</v>
       </c>
-      <c r="H75" s="94">
-        <v>0</v>
-      </c>
-      <c r="I75" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="J75" s="78">
+      <c r="H75" s="23">
+        <v>0</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" ref="J75:J81" si="32">IF(H75=0,0,IF(I75="WON",(G75-1)*0.94,-1))</f>
         <v>0</v>
       </c>
-      <c r="K75" s="29">
+      <c r="K75" s="25">
         <f t="shared" ref="K75:K81" si="33">J75*J$3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="64">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B76" s="46">
         <v>72</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="92">
+      <c r="D76" s="1">
         <v>1.29</v>
       </c>
       <c r="E76" s="41">
         <f t="shared" si="27"/>
         <v>0.77519379844961234</v>
       </c>
-      <c r="F76" s="93">
+      <c r="F76" s="54">
         <f t="shared" si="28"/>
         <v>0.57519379844961227</v>
       </c>
-      <c r="G76" s="91">
+      <c r="G76" s="86">
         <f>1/F76</f>
         <v>1.7385444743935314</v>
       </c>
-      <c r="J76" s="78">
+      <c r="H76" s="51">
+        <v>1</v>
+      </c>
+      <c r="I76" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" s="77">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K76" s="29">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="27">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="64">
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B77" s="46">
         <v>73</v>
       </c>
-      <c r="J77" s="78">
+      <c r="C77" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="E77" s="41">
+        <f t="shared" si="27"/>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="F77" s="54">
+        <f t="shared" si="28"/>
+        <v>0.75238095238095237</v>
+      </c>
+      <c r="G77" s="86">
+        <f>1/F77</f>
+        <v>1.3291139240506329</v>
+      </c>
+      <c r="H77" s="51">
+        <v>0</v>
+      </c>
+      <c r="I77" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="J77" s="77">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="K77" s="29">
+      <c r="K77" s="27">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="64">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B78" s="46">
         <v>74</v>
       </c>
-      <c r="J78" s="78">
+      <c r="C78" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="E78" s="41">
+        <f t="shared" si="27"/>
+        <v>0.59523809523809523</v>
+      </c>
+      <c r="F78" s="54">
+        <f t="shared" si="28"/>
+        <v>0.39523809523809522</v>
+      </c>
+      <c r="G78" s="86">
+        <v>2.54</v>
+      </c>
+      <c r="H78" s="51">
+        <v>1</v>
+      </c>
+      <c r="I78" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J78" s="77">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="29">
+        <v>-1</v>
+      </c>
+      <c r="K78" s="27">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="64">
+        <v>-55.55</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B79" s="46">
         <v>75</v>
       </c>
-      <c r="J79" s="78">
+      <c r="C79" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="E79" s="41">
+        <f t="shared" si="27"/>
+        <v>0.6211180124223602</v>
+      </c>
+      <c r="F79" s="54">
+        <f t="shared" si="28"/>
+        <v>0.42111801242236019</v>
+      </c>
+      <c r="G79" s="86">
+        <v>2.38</v>
+      </c>
+      <c r="H79" s="71">
+        <v>0</v>
+      </c>
+      <c r="I79" s="71" t="s">
+        <v>7</v>
+      </c>
+      <c r="J79" s="77">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="K79" s="29">
+      <c r="K79" s="27">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="64">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B80" s="46">
         <v>76</v>
       </c>
-      <c r="J80" s="78">
+      <c r="C80" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" s="41">
+        <f t="shared" ref="E80:E81" si="34">1/D80</f>
+        <v>0.5</v>
+      </c>
+      <c r="F80" s="54">
+        <f t="shared" ref="F80:F81" si="35">E80-0.2</f>
+        <v>0.3</v>
+      </c>
+      <c r="G80" s="86">
+        <f t="shared" ref="G80:G81" si="36">1/F80</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="H80" s="51">
+        <v>0</v>
+      </c>
+      <c r="I80" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="J80" s="77">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="K80" s="29">
+      <c r="K80" s="27">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="65">
+      <c r="B81" s="47">
         <v>77</v>
+      </c>
+      <c r="C81" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="D81" s="76">
+        <v>1.53</v>
+      </c>
+      <c r="E81" s="42">
+        <f t="shared" si="34"/>
+        <v>0.65359477124183007</v>
+      </c>
+      <c r="F81" s="59">
+        <f t="shared" si="35"/>
+        <v>0.45359477124183006</v>
+      </c>
+      <c r="G81" s="90">
+        <f t="shared" si="36"/>
+        <v>2.2046109510086453</v>
+      </c>
+      <c r="H81" s="9">
+        <v>0</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="J81" s="78">
         <f t="shared" si="32"/>
@@ -4108,6 +4268,17 @@
       <c r="K81" s="29">
         <f t="shared" si="33"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C82" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D82" t="s">
+        <v>128</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4118,7 +4289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CAAB2-0352-4756-9D08-D38A00F624F2}">
-  <dimension ref="B2:L102"/>
+  <dimension ref="B2:L109"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -6278,7 +6449,7 @@
         <v>1.78</v>
       </c>
       <c r="E62" s="80">
-        <f t="shared" ref="E62:E101" si="46">1/D62</f>
+        <f t="shared" ref="E62:E105" si="46">1/D62</f>
         <v>0.5617977528089888</v>
       </c>
       <c r="F62" s="6">
@@ -6912,7 +7083,7 @@
         <v>0.58125000000000004</v>
       </c>
       <c r="G79" s="52">
-        <f t="shared" ref="G79:G102" si="53">1/F79</f>
+        <f t="shared" ref="G79:G99" si="53">1/F79</f>
         <v>1.7204301075268815</v>
       </c>
       <c r="H79" s="1">
@@ -7504,6 +7675,12 @@
         <f t="shared" si="53"/>
         <v>1.5104166666666667</v>
       </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J95" s="26">
         <f t="shared" ref="J95:J101" si="54">IF(H95=0,0,IF(I95="WON",(G95*0.94-1),-1))</f>
         <v>0</v>
@@ -7535,6 +7712,12 @@
         <f t="shared" si="53"/>
         <v>1.5616797900262469</v>
       </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J96" s="26">
         <f t="shared" si="54"/>
         <v>0</v>
@@ -7554,7 +7737,7 @@
       <c r="D97" s="7">
         <v>1.38</v>
       </c>
-      <c r="E97" s="95">
+      <c r="E97" s="80">
         <f t="shared" si="46"/>
         <v>0.7246376811594204</v>
       </c>
@@ -7566,13 +7749,19 @@
         <f t="shared" si="53"/>
         <v>1.9060773480662978</v>
       </c>
+      <c r="H97" s="1">
+        <v>1</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="J97" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>0.79171270718231979</v>
       </c>
       <c r="K97" s="27">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>43.979640883977865</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.3">
@@ -7585,7 +7774,7 @@
       <c r="D98" s="7">
         <v>1.42</v>
       </c>
-      <c r="E98" s="95">
+      <c r="E98" s="80">
         <f t="shared" si="46"/>
         <v>0.70422535211267612</v>
       </c>
@@ -7597,13 +7786,19 @@
         <f t="shared" si="53"/>
         <v>1.9832402234636872</v>
       </c>
+      <c r="H98" s="1">
+        <v>1</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J98" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K98" s="27">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.3">
@@ -7616,7 +7811,7 @@
       <c r="D99" s="7">
         <v>1.35</v>
       </c>
-      <c r="E99" s="95">
+      <c r="E99" s="80">
         <f t="shared" si="46"/>
         <v>0.7407407407407407</v>
       </c>
@@ -7628,13 +7823,19 @@
         <f t="shared" si="53"/>
         <v>1.8493150684931507</v>
       </c>
+      <c r="H99" s="1">
+        <v>1</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J99" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K99" s="27">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.3">
@@ -7647,7 +7848,7 @@
       <c r="D100" s="7">
         <v>1.58</v>
       </c>
-      <c r="E100" s="95">
+      <c r="E100" s="80">
         <f t="shared" si="46"/>
         <v>0.63291139240506322</v>
       </c>
@@ -7658,13 +7859,19 @@
       <c r="G100" s="52">
         <v>2.3199999999999998</v>
       </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J100" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K100" s="27">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.3">
@@ -7677,7 +7884,7 @@
       <c r="D101" s="7">
         <v>1.55</v>
       </c>
-      <c r="E101" s="95">
+      <c r="E101" s="80">
         <f t="shared" si="46"/>
         <v>0.64516129032258063</v>
       </c>
@@ -7688,17 +7895,280 @@
       <c r="G101" s="52">
         <v>2.2599999999999998</v>
       </c>
+      <c r="H101" s="1">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J101" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K101" s="27">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-55.55</v>
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G102" s="52"/>
+      <c r="B102" s="93"/>
+      <c r="C102" s="79" t="s">
+        <v>126</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E102" s="94"/>
+      <c r="F102" s="95"/>
+      <c r="G102" s="52">
+        <v>2</v>
+      </c>
+      <c r="H102" s="96"/>
+      <c r="I102" s="96"/>
+      <c r="J102" s="97"/>
+      <c r="K102" s="98"/>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B103" s="3">
+        <v>98</v>
+      </c>
+      <c r="C103" s="79" t="s">
+        <v>109</v>
+      </c>
+      <c r="D103" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E103" s="80">
+        <f t="shared" si="46"/>
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="F103" s="6">
+        <f>MIN(E103-0.2,0.5)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G103" s="52">
+        <f>1/F103</f>
+        <v>2</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="J103" s="26">
+        <f t="shared" ref="J102:J105" si="56">IF(H103=0,0,IF(I103="WON",(G103*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K103" s="27">
+        <f t="shared" ref="K102:K105" si="57">J103*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B104" s="3">
+        <v>99</v>
+      </c>
+      <c r="C104" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D104" s="7">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E104" s="80">
+        <f t="shared" si="46"/>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="F104" s="6">
+        <f>MIN(E104-0.2,0.5)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G104" s="52">
+        <v>2</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+      <c r="I104" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="J104" s="26">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K104" s="27">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B105" s="3">
+        <v>100</v>
+      </c>
+      <c r="C105" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="D105" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="E105" s="80">
+        <f t="shared" si="46"/>
+        <v>0.625</v>
+      </c>
+      <c r="F105" s="6">
+        <f>MIN(E105-0.2,0.5)</f>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="G105" s="52">
+        <v>2.36</v>
+      </c>
+      <c r="H105" s="1">
+        <v>1</v>
+      </c>
+      <c r="I105" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="J105" s="26">
+        <f t="shared" si="56"/>
+        <v>1.2183999999999999</v>
+      </c>
+      <c r="K105" s="27">
+        <f t="shared" si="57"/>
+        <v>67.682119999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B106" s="3">
+        <v>101</v>
+      </c>
+      <c r="C106" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="D106" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="E106" s="80">
+        <f t="shared" ref="E106:E109" si="58">1/D106</f>
+        <v>0.58139534883720934</v>
+      </c>
+      <c r="F106" s="6">
+        <f t="shared" ref="F106:F109" si="59">MIN(E106-0.2,0.5)</f>
+        <v>0.38139534883720932</v>
+      </c>
+      <c r="G106" s="52">
+        <f>1/F106</f>
+        <v>2.6219512195121948</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="J106" s="26">
+        <f t="shared" ref="J106:J109" si="60">IF(H106=0,0,IF(I106="WON",(G106*0.94-1),-1))</f>
+        <v>0</v>
+      </c>
+      <c r="K106" s="27">
+        <f t="shared" ref="K106:K109" si="61">J106*J$3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B107" s="3">
+        <v>102</v>
+      </c>
+      <c r="C107" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107" s="7">
+        <v>2</v>
+      </c>
+      <c r="E107" s="80">
+        <f t="shared" si="58"/>
+        <v>0.5</v>
+      </c>
+      <c r="F107" s="6">
+        <f t="shared" si="59"/>
+        <v>0.3</v>
+      </c>
+      <c r="G107" s="52">
+        <v>3.35</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="J107" s="26">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="K107" s="27">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B108" s="3">
+        <v>103</v>
+      </c>
+      <c r="C108" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="D108" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="E108" s="80">
+        <f t="shared" si="58"/>
+        <v>0.64102564102564097</v>
+      </c>
+      <c r="F108" s="6">
+        <f t="shared" si="59"/>
+        <v>0.44102564102564096</v>
+      </c>
+      <c r="G108" s="52">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+      <c r="J108" s="26">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="K108" s="27">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B109" s="3">
+        <v>104</v>
+      </c>
+      <c r="C109" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D109" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="E109" s="80">
+        <f>1/D109</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F109" s="6">
+        <f>MIN(E109-0.2,0.5)</f>
+        <v>0.37142857142857139</v>
+      </c>
+      <c r="G109" s="52">
+        <v>2.7</v>
+      </c>
+      <c r="H109" s="1">
+        <v>1</v>
+      </c>
+      <c r="J109" s="26">
+        <f t="shared" si="60"/>
+        <v>-1</v>
+      </c>
+      <c r="K109" s="27">
+        <f t="shared" si="61"/>
+        <v>-55.55</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
